--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -2111,6 +2111,140 @@
       <c r="M25" s="17" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>漢神洲際開幕｜漸進鏡片9折+第2支75折</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/07</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/10</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>漢神洲際購物廣場店4/10開幕，配鏡升級日本製漸進鏡片9折，第2支眼鏡75折</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>日本製漸進鏡片9折 / 第2支75折</t>
+        </is>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
+        <is>
+          <t>門市（漢神洲際）</t>
+        </is>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>OD台中門市需留意客流分散；漸進鏡片9折對多焦市場有吸引力</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L26" s="17" t="inlineStr">
+        <is>
+          <t>關注開幕期間客流影響，強化OD台中門市服務差異化</t>
+        </is>
+      </c>
+      <c r="M26" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>滿額折扣+摺疊傘贈品</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/16</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/10</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>單筆消費滿$6,000折$600、滿$10,000折$1,000，贈摺疊傘</t>
+        </is>
+      </c>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
+          <t>滿$6,000折$600 / 滿$10,000折$1,000</t>
+        </is>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>門市</t>
+        </is>
+      </c>
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>OD目前無對標滿額折，需評估是否跟進</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低</t>
+        </is>
+      </c>
+      <c r="L27" s="17" t="inlineStr">
+        <is>
+          <t>觀察即可，4/16才開始</t>
+        </is>
+      </c>
+      <c r="M27" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -2512,6 +2646,53 @@
       <c r="I5" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69b125db355d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>公關危機</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Jins台日鏡片價差7倍爭議</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>網友發現Jins 1.76極薄鏡片台灣售價$15,000、日本僅￥11,000(約NT$2,200)，價差近7倍。社群輿論強烈，Jins發4點聲明稱因供應商海外定價規範，承諾積極爭取調整。</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>全客群</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>🔥 競品公關危機=OD機會。可透過社群/門市強調OD透明定價、性價比優勢，但不宜直接攻擊。</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ettoday.net/news/20260330/3141094.htm</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -2723,6 +2904,53 @@
       <c r="I4" s="17" t="inlineStr">
         <is>
           <t>Klassic本週抓取確認16間，較前次17間少1，持續追蹤</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>新開店</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>漢神洲際購物廣場店</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>台中市北屯區崇德路三段865號 漢神洲際購物廣場</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/10</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>台中新大型百貨進駐，Jins全台第91間JINS門市(+RIM 4=95)，台中市場競爭加劇</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -3219,6 +3447,118 @@
       <c r="F17" s="23" t="inlineStr">
         <is>
           <t>維持17間（含SON&amp;SUN, Room 41-21），本週無異動</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>全台78間，維持不變</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>91</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>漢神洲際購物廣場店4/10開幕（JINS 91+RIM 4=95間）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>維持35間</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>維持17間</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -3394,6 +3734,41 @@
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/06-04/12</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>1. Jins漢神洲際購物廣場店4/10台中開幕（JINS 91+RIM 4=95間）
+2. Jins台日鏡片價差7倍爭議爆發，官方4聲明承諾調價
+3. Jins漸進鏡片9折+第2支75折新促銷(4/7-5/10)
+門市數：OD 78 / Jins 95 / 眼鏡 35 / KC 17 = 225間（+1）</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中（Jins台中新店+價差爭議雙重關注）</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>關注Jins漢神洲際開幕對台中門市影響；善用Jins價差爭議做品牌溝通；把握4月競品促銷相對空窗期</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3427,7 +3802,7 @@
       </c>
       <c r="B1" s="17" t="inlineStr">
         <is>
-          <t>2026/03/30</t>
+          <t>2026/04/06</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3980,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>7</v>
@@ -3614,7 +3989,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="32" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="18">
@@ -3847,16 +4222,16 @@
         <v>78</v>
       </c>
       <c r="C21" s="34" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D21" s="34" t="n">
         <v>35</v>
       </c>
       <c r="E21" s="34" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F21" s="34" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -2115,136 +2115,203 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>2026/04/06</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>門市促銷</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>漢神洲際開幕｜漸進鏡片9折+第2支75折</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>日本製漸進鏡片9折（母親節鏡片優惠）</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>2026/04/07</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>2026/05/10</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>漢神洲際購物廣場店4/10開幕，配鏡升級日本製漸進鏡片9折，第2支眼鏡75折</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>日本製漸進鏡片9折 / 第2支75折</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>門市（漢神洲際）</t>
-        </is>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>OD台中門市需留意客流分散；漸進鏡片9折對多焦市場有吸引力</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>配鏡並升級日本製漸進鏡片享9折；加購濾藍光鏡片85折、調光鏡片8折</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>日本製漸進鏡片9折 / 濾藍光85折 / 調光8折</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>門市</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>OD多焦市場需留意；Jins鏡片升級折扣對價格敏感客群有吸引力</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>⚠️ 中</t>
         </is>
       </c>
-      <c r="L26" s="17" t="inlineStr">
-        <is>
-          <t>關注開幕期間客流影響，強化OD台中門市服務差異化</t>
-        </is>
-      </c>
-      <c r="M26" s="17" t="inlineStr">
-        <is>
-          <t>https://www.jins.com/tw/news</t>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>強化OD套餐制一價全包的價值溝通</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-69ca36fe489e3</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>2026/04/06</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>門市促銷</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>滿額折扣+摺疊傘贈品</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>第2支75折（兩波限時）</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026/04/12</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>買眼鏡或墨鏡第2支75折。第一波4/3-4/6、第二波4/10-4/12</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>第2支75折（週末限定兩波）</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>門市</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>限時週末活動，影響集中在清明連假+漢神洲際開幕週末</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>關注兩個週末門市客流變化</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-69ca36cf22069</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>母親節滿額折扣+贈折疊傘</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>2026/04/16</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>2026/05/10</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>單筆消費滿$6,000折$600、滿$10,000折$1,000，贈摺疊傘</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>滿$6,000折$600 / 滿$10,000折$1,000</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>當日單筆消費滿$6,000折$600、滿$10,000折$1,000；滿$5,200贈折疊傘（數量有限）</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>滿$6,000折$600 / 滿$10,000折$1,000 / 滿$5,200贈傘</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>門市</t>
         </is>
       </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>OD目前無對標滿額折，需評估是否跟進</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="inlineStr">
-        <is>
-          <t>🟢 低</t>
-        </is>
-      </c>
-      <c r="L27" s="17" t="inlineStr">
-        <is>
-          <t>觀察即可，4/16才開始</t>
-        </is>
-      </c>
-      <c r="M27" s="17" t="inlineStr">
-        <is>
-          <t>https://www.jins.com/tw/news</t>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>OD目前無對標母親節滿額折，需評估是否跟進</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>評估OD母親節檔期是否需要對應活動</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-69ca377bd183c</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -2951,6 +3018,53 @@
       <c r="I5" s="17" t="inlineStr">
         <is>
           <t>台中新大型百貨進駐，Jins全台第91間JINS門市(+RIM 4=95)，台中市場競爭加劇</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>新開店</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>南港中信店</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>台北市南港區經貿二路186-1號1樓</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026/04/02</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-69ca367f3b199</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Jins台北再+1，南港中信金融園區商圈，鄰近OD南港門市需留意</t>
         </is>
       </c>
     </row>
@@ -3490,19 +3604,19 @@
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D19" s="17" t="n">
         <v>90</v>
       </c>
       <c r="E19" s="17" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>漢神洲際購物廣場店4/10開幕（JINS 91+RIM 4=95間）</t>
+          <t>南港中信店4/2開幕 + 漢神洲際購物廣場店4/10開幕（JINS 92+RIM 4=96間）</t>
         </is>
       </c>
     </row>
@@ -3752,20 +3866,20 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>1. Jins漢神洲際購物廣場店4/10台中開幕（JINS 91+RIM 4=95間）
-2. Jins台日鏡片價差7倍爭議爆發，官方4聲明承諾調價
-3. Jins漸進鏡片9折+第2支75折新促銷(4/7-5/10)
-門市數：OD 78 / Jins 95 / 眼鏡 35 / KC 17 = 225間（+1）</t>
+          <t>1. Jins南港中信店4/2+漢神洲際4/10開幕（JINS 92+RIM 4=96間，本週+2）
+2. Jins台日鏡片價差7倍爭議，官方4聲明承諾調價
+3. Jins三大促銷：漸進鏡片9折(4/7-5/10)、第2支75折(4/3-4/6+4/10-4/12)、母親節滿額折(4/16-5/10)
+門市數：OD 78 / Jins 96 / 眼鏡 35 / KC 17 = 226間（+2）</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>⚠️ 中（Jins台中新店+價差爭議雙重關注）</t>
+          <t>⚠️ 中（Jins展店+價差爭議+三大促銷齊發）</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>關注Jins漢神洲際開幕對台中門市影響；善用Jins價差爭議做品牌溝通；把握4月競品促銷相對空窗期</t>
+          <t>善用Jins價差爭議做品牌溝通；關注漢神洲際+南港中信開幕影響；評估OD母親節檔期對應策略</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr">
@@ -3848,7 +3962,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="32" t="n">
         <v>6</v>
@@ -3857,7 +3971,7 @@
         <v>6</v>
       </c>
       <c r="F4" s="32" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="18">
@@ -4222,7 +4336,7 @@
         <v>78</v>
       </c>
       <c r="C21" s="34" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D21" s="34" t="n">
         <v>35</v>
@@ -4231,7 +4345,7 @@
         <v>16</v>
       </c>
       <c r="F21" s="34" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -118,6 +118,10 @@
       <color rgb="FFCC0000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -180,7 +184,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -283,6 +287,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -563,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -2115,203 +2122,337 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>2026/04/06</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>門市促銷</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>日本製漸進鏡片9折（母親節鏡片優惠）</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>2026/04/07</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>2026/05/10</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="17" t="inlineStr">
         <is>
           <t>配鏡並升級日本製漸進鏡片享9折；加購濾藍光鏡片85折、調光鏡片8折</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="17" t="inlineStr">
         <is>
           <t>日本製漸進鏡片9折 / 濾藍光85折 / 調光8折</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="17" t="inlineStr">
         <is>
           <t>門市</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="17" t="inlineStr">
         <is>
           <t>OD多焦市場需留意；Jins鏡片升級折扣對價格敏感客群有吸引力</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="17" t="inlineStr">
         <is>
           <t>⚠️ 中</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" s="17" t="inlineStr">
         <is>
           <t>強化OD套餐制一價全包的價值溝通</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69ca36fe489e3</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>2026/04/06</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>門市促銷</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>第2支75折（兩波限時）</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>2026/04/03</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>2026/04/12</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>買眼鏡或墨鏡第2支75折。第一波4/3-4/6、第二波4/10-4/12</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="17" t="inlineStr">
         <is>
           <t>第2支75折（週末限定兩波）</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="17" t="inlineStr">
         <is>
           <t>門市</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="17" t="inlineStr">
         <is>
           <t>限時週末活動，影響集中在清明連假+漢神洲際開幕週末</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="17" t="inlineStr">
         <is>
           <t>⚠️ 中</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L27" s="17" t="inlineStr">
         <is>
           <t>關注兩個週末門市客流變化</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M27" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69ca36cf22069</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>2026/04/06</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>門市促銷</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>母親節滿額折扣+贈折疊傘</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>2026/04/16</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>2026/05/10</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="17" t="inlineStr">
         <is>
           <t>當日單筆消費滿$6,000折$600、滿$10,000折$1,000；滿$5,200贈折疊傘（數量有限）</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>滿$6,000折$600 / 滿$10,000折$1,000 / 滿$5,200贈傘</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="17" t="inlineStr">
         <is>
           <t>門市</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="17" t="inlineStr">
         <is>
           <t>OD目前無對標母親節滿額折，需評估是否跟進</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="17" t="inlineStr">
         <is>
           <t>⚠️ 中</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L28" s="17" t="inlineStr">
         <is>
           <t>評估OD母親節檔期是否需要對應活動</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M28" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69ca377bd183c</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="35" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C29" s="35" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D29" s="35" t="inlineStr">
+        <is>
+          <t>春日SALE 第二副現折$300</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="inlineStr">
+        <is>
+          <t>2026/04/01</t>
+        </is>
+      </c>
+      <c r="F29" s="35" t="inlineStr">
+        <is>
+          <t>未定（配合母親節檔期）</t>
+        </is>
+      </c>
+      <c r="G29" s="35" t="inlineStr">
+        <is>
+          <t>全台門市配鏡第二副折$300。結束時間依各百貨/門市母親節檔期調整</t>
+        </is>
+      </c>
+      <c r="H29" s="35" t="inlineStr">
+        <is>
+          <t>第二副折$300</t>
+        </is>
+      </c>
+      <c r="I29" s="35" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J29" s="35" t="inlineStr">
+        <is>
+          <t>OD套餐制已含升級，但第二副折扣對家庭/朋友配鏡有吸引力</t>
+        </is>
+      </c>
+      <c r="K29" s="35" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="L29" s="35" t="inlineStr">
+        <is>
+          <t>關注全台門市客流變化，可考慮同期揪團配鏡優惠</t>
+        </is>
+      </c>
+      <c r="M29" s="35" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/175</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="35" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C30" s="35" t="inlineStr">
+        <is>
+          <t>區域促銷</t>
+        </is>
+      </c>
+      <c r="D30" s="35" t="inlineStr">
+        <is>
+          <t>中區限定購物節 滿$6,000折$666</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="inlineStr">
+        <is>
+          <t>2026/04/01</t>
+        </is>
+      </c>
+      <c r="F30" s="35" t="inlineStr">
+        <is>
+          <t>未定（配合母親節檔期）</t>
+        </is>
+      </c>
+      <c r="G30" s="35" t="inlineStr">
+        <is>
+          <t>台中/彰化/北屯 指定7家門市限定。①配鏡滿$6,000折$666 ②日本製極耐刮鏡片折$500</t>
+        </is>
+      </c>
+      <c r="H30" s="35" t="inlineStr">
+        <is>
+          <t>滿$6,000折$666 + 極耐刮鏡片折$500</t>
+        </is>
+      </c>
+      <c r="I30" s="35" t="inlineStr">
+        <is>
+          <t>台中/彰化/北屯 指定7家門市</t>
+        </is>
+      </c>
+      <c r="J30" s="35" t="inlineStr">
+        <is>
+          <t>直接衝擊OD台中門市，滿$6K折$666力道與6周年慶相同</t>
+        </is>
+      </c>
+      <c r="K30" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="L30" s="35" t="inlineStr">
+        <is>
+          <t>台中門市需密切關注業績，可考慮中部門市限定回應措施</t>
+        </is>
+      </c>
+      <c r="M30" s="35" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/174</t>
         </is>
       </c>
     </row>
@@ -3022,47 +3163,47 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>2026/04/06</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>新開店</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>南港中信店</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>台北市南港區經貿二路186-1號1樓</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>北部</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>2026/04/02</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69ca367f3b199</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Jins台北再+1，南港中信金融園區商圈，鄰近OD南港門市需留意</t>
         </is>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -2456,6 +2456,207 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>日本製漸進鏡片9折</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026/04/07</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026/05/10</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>配鏡升級日本製漸進鏡片享9折、濾藍光85折、調光8折</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>多焦9折/藍光85折/調光8折</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>門市</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Jins持續強打漸進鏡片優惠，OD套餐制優勢需持續溝通</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>強調OD套餐一價全包優勢</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>母親節滿額折</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026/04/16</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026/05/10</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>滿$6,000折$600、滿$10,000折$1,000、滿$5,200贈傘</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>滿額折$600-$1,000+贈傘</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>門市</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Jins母親節力道大，OD需評估是否推出對應檔期活動</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>規劃母親節對應促銷</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>春日優惠 光學眼鏡折$300+滿額折</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026/04/01</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>光學眼鏡系列折$300、單筆消費滿$5,500折$500</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>眼鏡折$300+滿$5,500折$500</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>門市</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Klassic空窗期結束，重新加入促銷戰局</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>關注Klassic客群反應</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -2470,7 +2671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -2597,6 +2798,63 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>鏡框新品</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Airframe 輕感舒壓系列</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026/04/02</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>$2,980</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>鎢金屬重心平衡技術，減輕鏡片前傾重量，舒適配戴</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>全客群</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>JINS持續在輕量舒適領域創新，OD可評估類似技術導入</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://www.stufftaiwan.com/2026/04/11/jins-airframe</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -2611,7 +2869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -2901,6 +3159,100 @@
       <c r="I6" s="17" t="inlineStr">
         <is>
           <t>https://www.ettoday.net/news/20260330/3141094.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>新品發表</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Airframe輕感舒壓系列 全新上市</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4/2全台門市+官方線上商城同步發售，採用鎢金屬重心平衡技術</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>全客群</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>輕量舒適為眼鏡市場重要差異化方向，OD可參考</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://www.stufftaiwan.com/2026/04/11/jins-airframe</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>展店</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>漢神洲際購物廣場店盛大開幕</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4/10開幕，開幕日湧入10萬人次。台中最大新百貨，JINS進駐。</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>漢神洲際</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>台中消費者</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>大型百貨進駐效應顯著，需關注台中門市客流分散</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.businessweekly.com.tw/focus/blog/3021087</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -3814,6 +4166,134 @@
       <c r="F21" s="17" t="inlineStr">
         <is>
           <t>維持17間</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>全台78間（±0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>全台JINS 92+RIM 4=96（±0）漢神洲際4/10已開幕（W16計入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>全台35間（±0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>全台17間（±0）</t>
         </is>
       </c>
     </row>
@@ -3830,7 +4310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -4024,6 +4504,70 @@
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026/04/06-04/12</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1. Jins漢神洲際4/10開幕(10萬人) 2. Jins Airframe新品上市(4/2) 3. Jins第2支75折第二波結束(4/12)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>⚠️ 中（母親節攻勢蓄勢待發）</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>善用Jins價差爭議做品牌溝通；關注漢神洲際對台中市場影響</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026/04/13-04/19</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1. Klassic春日優惠重啟 2. Jins母親節滿額折4/16啟動 3. 三品牌母親節檔期全數進入促銷攻勢</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>🔴 高（母親節大戰開打）</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>規劃母親節對應活動；關注三品牌促銷力道與客流影響</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -2457,203 +2457,240 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>2026/04/13</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>門市促銷</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>日本製漸進鏡片9折</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>2026/04/07</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="17" t="inlineStr">
         <is>
           <t>2026/05/10</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="17" t="inlineStr">
         <is>
           <t>配鏡升級日本製漸進鏡片享9折、濾藍光85折、調光8折</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="17" t="inlineStr">
         <is>
           <t>多焦9折/藍光85折/調光8折</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="17" t="inlineStr">
         <is>
           <t>門市</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="17" t="inlineStr">
         <is>
           <t>Jins持續強打漸進鏡片優惠，OD套餐制優勢需持續溝通</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="17" t="inlineStr">
         <is>
           <t>⚠️ 中</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" s="17" t="inlineStr">
         <is>
           <t>強調OD套餐一價全包優勢</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>2026/04/13</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>門市促銷</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>母親節滿額折</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>2026/04/16</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>2026/05/10</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="17" t="inlineStr">
         <is>
           <t>滿$6,000折$600、滿$10,000折$1,000、滿$5,200贈傘</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>滿額折$600-$1,000+贈傘</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>門市</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="17" t="inlineStr">
         <is>
           <t>Jins母親節力道大，OD需評估是否推出對應檔期活動</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="17" t="inlineStr">
         <is>
           <t>🔴 高</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" s="17" t="inlineStr">
         <is>
           <t>規劃母親節對應促銷</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>2026/04/13</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>Klassic</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>門市促銷</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>春日優惠 光學眼鏡折$300+滿額折</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>2026/04/01</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="17" t="inlineStr">
         <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="17" t="inlineStr">
         <is>
           <t>光學眼鏡系列折$300、單筆消費滿$5,500折$500</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="17" t="inlineStr">
         <is>
           <t>眼鏡折$300+滿$5,500折$500</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="17" t="inlineStr">
         <is>
           <t>門市</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="17" t="inlineStr">
         <is>
           <t>Klassic空窗期結束，重新加入促銷戰局</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="17" t="inlineStr">
         <is>
           <t>⚠️ 中</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" s="17" t="inlineStr">
         <is>
           <t>關注Klassic客群反應</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M33" s="17" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>品牌活動</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>動物平權《野餐我PET你》滾草皮音樂市集</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>4/18-4/19</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>台北華山大草原</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>品牌公關活動，非直接促銷但提升品牌好感度</t>
         </is>
       </c>
     </row>
@@ -2799,57 +2836,57 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>2026/04/13</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>鏡框新品</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>Airframe 輕感舒壓系列</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>2026/04/02</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>$2,980</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>鎢金屬重心平衡技術，減輕鏡片前傾重量，舒適配戴</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>全客群</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t>JINS持續在輕量舒適領域創新，OD可評估類似技術導入</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="17" t="inlineStr">
         <is>
           <t>https://www.stufftaiwan.com/2026/04/11/jins-airframe</t>
         </is>
@@ -3163,94 +3200,94 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>2026/04/13</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>新品發表</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>Airframe輕感舒壓系列 全新上市</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>4/2全台門市+官方線上商城同步發售，採用鎢金屬重心平衡技術</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>無</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>全客群</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>輕量舒適為眼鏡市場重要差異化方向，OD可參考</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>https://www.stufftaiwan.com/2026/04/11/jins-airframe</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>2026/04/13</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>展店</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>漢神洲際購物廣場店盛大開幕</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>4/10開幕，開幕日湧入10萬人次。台中最大新百貨，JINS進駐。</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>漢神洲際</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>台中消費者</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>大型百貨進駐效應顯著，需關注台中門市客流分散</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>https://www.businessweekly.com.tw/focus/blog/3021087</t>
         </is>
@@ -3270,7 +3307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -3558,6 +3595,154 @@
       <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Jins台北再+1，南港中信金融園區商圈，鄰近OD南港門市需留意</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>新開</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>JINS（台北新店）</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>台北市</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>Chrome抓取確認台北+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>新開</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Klassic 敦南旗艦店</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>台北市大安區</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>旗艦店型態</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>新開</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Klassic 西門誠品店</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>台北市萬華區</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>進駐誠品通路</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>新開</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>Klassic 文心秀泰店</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>台中市南屯區</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>台中第4店</t>
         </is>
       </c>
     </row>
@@ -4170,130 +4355,122 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>2026/04/13</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>OWNDAYS</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>全台78間（±0）</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>2026/04/13</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="C23" s="17" t="n">
+        <v>94</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>92</v>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>全台JINS 94+RIM 4=98（+2 vs W16）。Chrome實地抓取確認台北+1、台中漢神洲際+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>全台JINS 92+RIM 4=96（±0）漢神洲際4/10已開幕（W16計入）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>全台35間（±0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>2026/04/13</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>眼鏡市場</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>全台35間（±0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026/04/13</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>Klassic</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>全台17間（±0）</t>
+      <c r="C25" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>全台20間（+3）。新增：敦南旗艦店、西門誠品店（台北+2）、文心秀泰店（台中+1）。Chrome實地抓取確認</t>
         </is>
       </c>
     </row>
@@ -4510,64 +4687,64 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>W16</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>2026/04/06-04/12</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>1. Jins漢神洲際4/10開幕(10萬人) 2. Jins Airframe新品上市(4/2) 3. Jins第2支75折第二波結束(4/12)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>⚠️ 中（母親節攻勢蓄勢待發）</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>善用Jins價差爭議做品牌溝通；關注漢神洲際對台中市場影響</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>W17</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026/04/13-04/19</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>漢神洲際開幕(Jins+KC進駐)；Jins 94+RIM4=98(+2)；Klassic新開3店(17→20)；母親節大戰開打（Jins滿額折4/16啟動+眼鏡市場春日SALE+KC春日優惠）</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>1. Klassic春日優惠重啟 2. Jins母親節滿額折4/16啟動 3. 三品牌母親節檔期全數進入促銷攻勢</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>🔴 高（母親節大戰開打）</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>規劃母親節對應活動；關注三品牌促銷力道與客流影響</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4647,13 +4824,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="32" t="n">
         <v>6</v>
       </c>
       <c r="E4" s="32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" s="32" t="n">
         <v>53</v>
@@ -4779,13 +4956,13 @@
         <v>7</v>
       </c>
       <c r="C10" s="32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" s="32" t="n">
         <v>30</v>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -2251,7 +2251,7 @@
       </c>
       <c r="M27" s="17" t="inlineStr">
         <is>
-          <t>https://www.jins.com/tw/news/news-69ca36cf22069</t>
+          <t>https://www.jins.com/tw/news/news-69ca367f3b199</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="M31" s="17" t="inlineStr">
         <is>
-          <t>https://www.jins.com/tw/news</t>
+          <t>https://www.jins.com/tw/news/news-69ca36fe489e3</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="M32" s="17" t="inlineStr">
         <is>
-          <t>https://www.jins.com/tw/news</t>
+          <t>https://www.jins.com/tw/news/news-69ca377bd183c</t>
         </is>
       </c>
     </row>
@@ -2658,39 +2658,44 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>2026/04/13</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>品牌活動</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>動物平權《野餐我PET你》滾草皮音樂市集</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>4/18-4/19</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>台北華山大草原</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="17" t="inlineStr">
         <is>
           <t>品牌公關活動，非直接促銷但提升品牌好感度</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-69d4a2dd8376b</t>
         </is>
       </c>
     </row>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -2693,7 +2693,7 @@
           <t>品牌公關活動，非直接促銷但提升品牌好感度</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69d4a2dd8376b</t>
         </is>
@@ -3616,12 +3616,12 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>新開</t>
+          <t>待確認</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>JINS（台北新店）</t>
+          <t>台北市門市數 22→23（+1），具體店名待查</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>Chrome抓取確認台北+1</t>
+          <t>門市搜尋頁城市數量變化推算，非新聞公告來源</t>
         </is>
       </c>
     </row>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -3312,7 +3312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -3653,27 +3653,27 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>新開</t>
+          <t>新增（門市頁差異比對）</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>Klassic 敦南旗艦店</t>
+          <t>KlassiC. 台北敦南旗艦店</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>台北市大安區</t>
+          <t>台北市大安區忠孝東路四段175號</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>未公告</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>旗艦店型態</t>
+          <t>W16→W17門市頁新增，開幕日未揭露。來源：klassicglobal.com/pages/stores</t>
         </is>
       </c>
     </row>
@@ -3690,27 +3690,27 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>新開</t>
+          <t>新增（門市頁差異比對）</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>Klassic 西門誠品店</t>
+          <t>KlassiC. 台北誠品生活西門店</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>台北市萬華區</t>
+          <t>台北市萬華區峨眉街52號3樓</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>未公告</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>進駐誠品通路</t>
+          <t>W16→W17門市頁新增，開幕日未揭露。來源：klassicglobal.com/pages/stores</t>
         </is>
       </c>
     </row>
@@ -3727,30 +3727,32 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>新開</t>
+          <t>新增（門市頁差異比對）</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>Klassic 文心秀泰店</t>
+          <t>KlassIC. 台中文心秀泰門市</t>
         </is>
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>台中市南屯區</t>
+          <t>台中市南屯區文心南路289號2樓</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>未公告</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>台中第4店</t>
-        </is>
-      </c>
-    </row>
+          <t>W16→W17門市頁新增，開幕日未揭露。來源：klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12"/>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -2696,6 +2696,73 @@
       <c r="M34" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69d4a2dd8376b</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>【母親節~愛的感謝】</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026/04/14</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026/05/11</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>滿$5,000折$500 + 加贈 YOSISTAMP 聯名毛巾</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>滿$5,000現折$500（10%）+ 聯名毛巾</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>OD套餐制 vs 眼鏡市場 10%折扣 — 建議OD推出母親節專屬方案應對</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>W19前發布OD母親節檔期方案</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -3751,8 +3818,53 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>三品牌</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>穩定週（±0）</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Jins 94+RIM 4=98 / 眼鏡市場 35 / Klassic 20</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>全台</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Chrome 實地抓取 jins.com/tw, meganeichiba.com.tw, klassicglobal.com</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>W17 Jins+Klassic展店熱潮後進入消化期，本週三品牌門市數皆無變化。注意力從展店轉向促銷戰（母親節檔期）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -3767,7 +3879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -4478,6 +4590,118 @@
       <c r="F25" s="17" t="inlineStr">
         <is>
           <t>全台20間（+3）。新增：敦南旗艦店、西門誠品店（台北+2）、文心秀泰店（台中+1）。Chrome實地抓取確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>78</v>
+      </c>
+      <c r="D26" t="n">
+        <v>78</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>全台78間（±0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>94</v>
+      </c>
+      <c r="D27" t="n">
+        <v>94</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>全台JINS 94+RIM 4=98（±0 vs W17）。Chrome實地抓取確認，無新增/關閉</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>35</v>
+      </c>
+      <c r="D28" t="n">
+        <v>35</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>全台35間（±0）。Chrome實地抓取確認，無異動</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>20</v>
+      </c>
+      <c r="D29" t="n">
+        <v>20</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>全台20間（±0 vs W17）。W17新增3店後進入消化期，本週官網門市頁無變化</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -4752,6 +4976,40 @@
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026/04/20-04/26</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1. 眼鏡市場4/14發動母親節【滿5000折500+YOSISTAMP毛巾】
+2. Jins母親節滿額折(4/16啟動)+毛孩音樂市集4/18-19華山活動後記
+3. 門市數穩定：OD 78 / Jins 98 / 眼鏡 35 / KC 20 = 231間（±0 vs W17）</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>🔴 高（母親節檔期全面開戰）</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>OD母親節方案需最遲W19上半週(4/21-23)發布；持續追蹤漢神洲際第2週效應；評估台中防守方案；觀察Klassic是否跟進母親節</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4785,7 +5043,7 @@
       </c>
       <c r="B1" s="17" t="inlineStr">
         <is>
-          <t>2026/04/06</t>
+          <t>2026/04/20</t>
         </is>
       </c>
     </row>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -2700,67 +2700,201 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>2026/04/20</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="17" t="inlineStr">
         <is>
           <t>門市促銷</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>【母親節~愛的感謝】</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>2026/04/14</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="17" t="inlineStr">
         <is>
           <t>2026/05/11</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="17" t="inlineStr">
         <is>
           <t>滿$5,000折$500 + 加贈 YOSISTAMP 聯名毛巾</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="17" t="inlineStr">
         <is>
           <t>滿$5,000現折$500（10%）+ 聯名毛巾</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="17" t="inlineStr">
         <is>
           <t>全台門市</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="17" t="inlineStr">
         <is>
           <t>OD套餐制 vs 眼鏡市場 10%折扣 — 建議OD推出母親節專屬方案應對</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K35" s="17" t="inlineStr">
         <is>
           <t>🔴 高</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L35" s="17" t="inlineStr">
         <is>
           <t>W19前發布OD母親節檔期方案</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M35" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/27</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>母親節升級加碼：滿萬折千 + 日製漸進功能鏡片 8 折</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/10</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>Jins 4/23 在母親節主題加碼：母親節滿$10,000折$1,000維持，日製漸進功能鏡片由原9折升級至8折</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="inlineStr">
+        <is>
+          <t>滿$10,000折$1,000 + 漸進鏡片8折</t>
+        </is>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J36" s="17" t="inlineStr">
+        <is>
+          <t>漸進鏡片價格戰升溫，OD 套餐已含漸進升級需強調價值</t>
+        </is>
+      </c>
+      <c r="K36" s="17" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="L36" s="17" t="inlineStr">
+        <is>
+          <t>強化 OD 套餐含漸進升級的差異化敘事</t>
+        </is>
+      </c>
+      <c r="M36" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026/04/27</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>【太陽眼鏡優惠】指定鏡框 + 有度數鏡片 $3,000 起</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026/04/24</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>眼鏡市場 4/24 推出夏季墨鏡優惠，指定鏡框搭配有度數鏡片 $3,000 起</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>指定鏡框 + 有度數鏡片 $3,000 起</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>夏季墨鏡攻勢提早，OD 墨鏡品項可考慮類似入門價格帶推廣</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>評估墨鏡入門價格帶促銷</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news</t>
         </is>
@@ -3379,7 +3513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -3819,49 +3953,143 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>2026/04/20</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>三品牌</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>穩定週（±0）</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Jins 94+RIM 4=98 / 眼鏡市場 35 / Klassic 20</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>全台</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>Chrome 實地抓取 jins.com/tw, meganeichiba.com.tw, klassicglobal.com</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>W17 Jins+Klassic展店熱潮後進入消化期，本週三品牌門市數皆無變化。注意力從展店轉向促銷戰（母親節檔期）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/27</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>新開店（預公告）</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>JINS 楊梅梅獅店</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>桃園市楊梅區</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>桃園市場 JINS +1，OD 桃園門市需留意 4/30 開幕後客流變化</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026/04/27</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>新開店（預公告）</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>RIM FOCUS時尚流行館店</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>台南市中西區中山路166號1樓</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>南部</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>台南 RIM 第 1 間，全台第 5 間 RIM。RIM 副品牌（$1,980 起）下沉南部市場，需評估對 OD 台南門市影響</t>
         </is>
       </c>
     </row>
@@ -3879,7 +4107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -4594,114 +4822,226 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>2026/04/20</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>OWNDAYS</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="17" t="n">
         <v>78</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="17" t="n">
         <v>78</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>全台78間（±0）</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>2026/04/20</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="17" t="n">
         <v>94</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="17" t="n">
         <v>94</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>全台JINS 94+RIM 4=98（±0 vs W17）。Chrome實地抓取確認，無新增/關閉</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>2026/04/20</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="17" t="n">
         <v>35</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="17" t="n">
         <v>35</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>全台35間（±0）。Chrome實地抓取確認，無異動</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>2026/04/20</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>Klassic</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>全台20間（±0 vs W17）。W17新增3店後進入消化期，本週官網門市頁無變化</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/27</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>全台78間（±0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/27</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>98</v>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>Chrome實地抓取：北60+中17+南21+東2=100。新增 JINS楊梅梅獅店(4/30開幕,桃園)+RIM FOCUS時尚流行館店(4/30開幕,台南)。預公告中,4/30前開幕。JINS 95 + RIM 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/27</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>Chrome實地抓取：全台35間（±0）。新北5/桃園4/宜蘭1/新竹3/台北6/台中7/彰化1/台南3/高雄5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/27</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D33" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>Chrome實地抓取：全台20間（±0）</t>
         </is>
       </c>
     </row>
@@ -4718,7 +5058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -4982,34 +5322,69 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>W18</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>2026/04/20-04/26</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>1. 眼鏡市場4/14發動母親節【滿5000折500+YOSISTAMP毛巾】
 2. Jins母親節滿額折(4/16啟動)+毛孩音樂市集4/18-19華山活動後記
 3. 門市數穩定：OD 78 / Jins 98 / 眼鏡 35 / KC 20 = 231間（±0 vs W17）</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>🔴 高（母親節檔期全面開戰）</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>OD母親節方案需最遲W19上半週(4/21-23)發布；持續追蹤漢神洲際第2週效應；評估台中防守方案；觀察Klassic是否跟進母親節</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/27-05/03</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>1. 🔥 JINS 4/30 雙店齊開：楊梅梅獅店（桃園+1）+ RIM FOCUS時尚流行館店（台南，第5間RIM）— JINS 全台增至 100 間（+2 vs W18）
+2. JINS 4/23 母親節升級：母親節「滿萬折千」+ 日製漸進功能鏡片最高 8 折（原 9 折加碼）— 母親節檔期戰升溫
+3. 眼鏡市場 4/24 推【太陽眼鏡優惠】：指定鏡框搭配有度數鏡片 $3,000 起（夏季提早搶攻墨鏡客群）
+門市數：OD 78 / Jins 100 / 眼鏡 35 / KC 20 = 233 間（+2 vs W18）</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>🔴 高（JINS雙店開幕+母親節漸進加碼+眼鏡市場墨鏡攻勢）</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>優先：(a) 桃園 / 台南門市應對 4/30 開幕競爭 (b) 評估漸進鏡片價格戰策略 (c) 墨鏡品項是否需提早促銷因應</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5043,10 +5418,11 @@
       </c>
       <c r="B1" s="17" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-    </row>
+          <t>2026/04/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="18">
       <c r="A3" s="29" t="inlineStr">
         <is>
@@ -5155,7 +5531,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>4</v>
@@ -5164,7 +5540,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="18">
@@ -5309,7 +5685,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" s="32" t="n">
         <v>3</v>
@@ -5318,7 +5694,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="18">
@@ -5463,16 +5839,16 @@
         <v>78</v>
       </c>
       <c r="C21" s="34" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D21" s="34" t="n">
         <v>35</v>
       </c>
       <c r="E21" s="34" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F21" s="34" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -2829,74 +2829,74 @@
       </c>
       <c r="M36" s="17" t="inlineStr">
         <is>
-          <t>https://www.jins.com/tw/news</t>
+          <t>https://www.jins.com/tw/news/news-69e99ed82f2ac</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>2026/04/27</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>門市促銷</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>【太陽眼鏡優惠】指定鏡框 + 有度數鏡片 $3,000 起</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>2026/04/24</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="17" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場 4/24 推出夏季墨鏡優惠，指定鏡框搭配有度數鏡片 $3,000 起</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="17" t="inlineStr">
         <is>
           <t>指定鏡框 + 有度數鏡片 $3,000 起</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="17" t="inlineStr">
         <is>
           <t>全台門市</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="17" t="inlineStr">
         <is>
           <t>夏季墨鏡攻勢提早，OD 墨鏡品項可考慮類似入門價格帶推廣</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" s="17" t="inlineStr">
         <is>
           <t>⚠️ 中</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L37" s="17" t="inlineStr">
         <is>
           <t>評估墨鏡入門價格帶促銷</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>https://www.meganeichiba.com.tw/news</t>
+      <c r="M37" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/177</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>https://www.jins.com/tw/news</t>
+          <t>https://www.jins.com/tw/news/news-69e99f98417bf</t>
         </is>
       </c>
       <c r="I12" s="17" t="inlineStr">
@@ -4047,47 +4047,47 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>2026/04/27</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>新開店（預公告）</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>RIM FOCUS時尚流行館店</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>台南市中西區中山路166號1樓</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>南部</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://www.jins.com/tw/news</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-69e99fe247353</t>
+        </is>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>台南 RIM 第 1 間，全台第 5 間 RIM。RIM 副品牌（$1,980 起）下沉南部市場，需評估對 OD 台南門市影響</t>
         </is>
@@ -5422,7 +5422,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="18">
       <c r="A3" s="29" t="inlineStr">
         <is>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -2900,6 +2900,207 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/04</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>母親節【滿萬折千+漸進鏡片8折】最後一週倒數</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/10</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>母親節最後一週收官：滿$10,000折$1,000維持、日製漸進功能鏡片8折、加購濾藍光85折、加購調光8折，並有滿$5,200贈折疊傘</t>
+        </is>
+      </c>
+      <c r="H38" s="17" t="inlineStr">
+        <is>
+          <t>滿$10,000折$1,000 + 漸進8折 + 贈傘</t>
+        </is>
+      </c>
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J38" s="17" t="inlineStr">
+        <is>
+          <t>OD 套餐含漸進升級的差異化敘事最後衝刺；母親節週末客流關鍵</t>
+        </is>
+      </c>
+      <c r="K38" s="17" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="L38" s="17" t="inlineStr">
+        <is>
+          <t>5/8-5/10 周末客流監控、強化 OD 套餐含漸進升級的「一價全包」敘事</t>
+        </is>
+      </c>
+      <c r="M38" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-69e99ed82f2ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/04</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>【母親節~愛的感謝】最後一週</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/14</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/11</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="inlineStr">
+        <is>
+          <t>母親節最後一週：滿$5,000折$500（10%）+ 加贈 YOSISTAMP 聯名毛巾，5/11截止</t>
+        </is>
+      </c>
+      <c r="H39" s="17" t="inlineStr">
+        <is>
+          <t>滿$5,000折$500 + 聯名毛巾</t>
+        </is>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J39" s="17" t="inlineStr">
+        <is>
+          <t>OD 套餐制 vs 眼鏡市場 10% 折扣；母親節最後衝刺贈品力道強</t>
+        </is>
+      </c>
+      <c r="K39" s="17" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="L39" s="17" t="inlineStr">
+        <is>
+          <t>盤點門店母親節週末庫存與促銷話術</t>
+        </is>
+      </c>
+      <c r="M39" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/176</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/04</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>【太陽眼鏡優惠】持續中</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/24</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>夏季墨鏡攻勢持續：指定鏡框 + 有度數鏡片 $3,000 起。觀察母親節後是否強化</t>
+        </is>
+      </c>
+      <c r="H40" s="17" t="inlineStr">
+        <is>
+          <t>指定鏡框 + 有度數鏡片 $3,000 起</t>
+        </is>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J40" s="17" t="inlineStr">
+        <is>
+          <t>夏季墨鏡攻勢；OD 墨鏡套餐入門價格帶可比較</t>
+        </is>
+      </c>
+      <c r="K40" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L40" s="17" t="inlineStr">
+        <is>
+          <t>5/11 後若眼鏡市場加碼墨鏡，OD 需準備夏季墨鏡套餐話術</t>
+        </is>
+      </c>
+      <c r="M40" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/177</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -2914,7 +3115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -3095,6 +3296,63 @@
       <c r="K3" s="17" t="inlineStr">
         <is>
           <t>https://www.stufftaiwan.com/2026/04/11/jins-airframe</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026/05/04</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>產品線擴張</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AKILA 系列（多款 OPTIC / SUNGLASS）</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026/05 上架</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>$6,580 - $8,680</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AKILA 是來自洛杉磯的設計師眼鏡品牌，強調極簡與雕塑感。Klassic 為其台灣總代理</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>中高端設計師眼鏡愛好者</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Klassic 母親節空窗期改打新品線；OD 客群重疊度低但顯示中高端市場品牌推進</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -4090,6 +4348,53 @@
       <c r="I13" s="17" t="inlineStr">
         <is>
           <t>台南 RIM 第 1 間，全台第 5 間 RIM。RIM 副品牌（$1,980 起）下沉南部市場，需評估對 OD 台南門市影響</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/04</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>三品牌</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>穩定週（Chrome 實地抓取）</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>Jins 95+RIM 5=100 / 眼鏡市場 35 / Klassic 20</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>全台</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>Chrome 實地抓取確認：JINS 60+17+21+2=100、眼鏡市場 35、Klassic 20。三品牌官網 news 本週皆無新店公告</t>
+        </is>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>JINS 4/30 雙店開幕後第一個觀察週，重點轉向母親節最後一週收官效應</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -5042,6 +5347,118 @@
       <c r="F33" s="17" t="inlineStr">
         <is>
           <t>Chrome實地抓取：全台20間（±0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/04</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>全台78間（±0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/04</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D35" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>Chrome 實地抓取：北60+中17+南21+東2=100。JINS 95 + RIM 5（±0 vs W19）。本週無新店公告（最新 news 仍為 4/23 雙店預告）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/04</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D36" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>Chrome 實地抓取：全台35間（±0 vs W19）。本週無新店公告，最新 news 為 4/24 太陽眼鏡優惠</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/04</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>Chrome 實地抓取：全台20間（±0 vs W19）。注意：新增 AKILA 系列商品線（$6,580起，多款 OPTIC/SUNGLASS）— 本週新觀察</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -5385,6 +5802,41 @@
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/04-05/10</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>1. 母親節最後一週倒數（JINS 5/10 / 眼鏡市場 5/11 截止）— JINS「滿萬折千+漸進8折」、眼鏡市場「滿$5,000折$500+YOSISTAMP聯名毛巾」雙引擎收官
+2. JINS 4/30 雙店開幕後第一個觀察週（楊梅梅獅店+RIM FOCUS時尚流行館台南店）— 桃園/台南開幕後客流轉移影響觀察
+3. Klassic 上架 AKILA 新系列（多款 OPTIC/SUNGLASS $6,580 起）— 春日 SALE 4/30 結束後改打新品策略
+門市數（Chrome 實地抓取）：OD 78 / Jins 100 / 眼鏡 35 / KC 20 = 233 間（±0 vs W19）</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>🔴 高（母親節檔期收官週 + JINS 雙店開幕第二週效應）</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>優先：(a) 母親節最後三天促銷強度盤點 (b) 桃園/台南 OD 門市 4/30 後客流變化追蹤 (c) 5/11 後墨鏡夏季檔期準備</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5418,7 +5870,7 @@
       </c>
       <c r="B1" s="17" t="inlineStr">
         <is>
-          <t>2026/04/27</t>
+          <t>2026/05/04</t>
         </is>
       </c>
     </row>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -3101,6 +3101,207 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SUMMER SALE 指定眼鏡限時優惠 8折/9折</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>🔵藍圓標 8折、🟢綠圓標 9折，指定商品除外、不與其他折扣優惠併用。適用全台 JINS + RIM BY JINS 實體門市。光學眼鏡＋墨鏡皆入優惠範圍</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>指定眼鏡 8折/9折（6.5週檔期）</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>全台 JINS + RIM 門市</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>母親節剛結束（5/10、5/11）立即接檔，6.5週橫跨整個夏季前哨無空窗。OD 套餐制 vs JINS 折扣後實價需明確對比敘事</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>5/14-6/30 期間 OD 套餐價值溝通強化；門市試戴對比；評估墨鏡夏季方案是否提前推出</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>http://www.jins.com/tw/news/news-6a04355a0841c</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>【環球板橋店 + 家樂福彰化店】一週年祭限定優惠</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>兩間滿週年門市同步啟動一週年祭限定優惠，配鏡滿$3,000折$300+滿$5,000折$500（依官網 5/15 公告）</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>滿$3,000折$300、滿$5,000折$500</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>環球板橋店、家樂福彰化店</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>單店限定但板橋為新北重要商圈、彰化為中部周邊城市，OD 新北/中部門市需留意客流分流</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>新北板橋 + 彰化 OD 門市5/15-5/25 客流監控；觀察是否擴大至全台檔期</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>【太陽眼鏡優惠】指定鏡框+有度數鏡片 $3,000 起（持續中）</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026/04/24</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>夏季墨鏡攻勢持續：指定鏡框搭配有度數鏡片 $3,000 起。預期5月底前進入夏季旺季加碼</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>指定鏡框+有度數鏡片 $3,000起</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>OD 墨鏡套餐入門價格帶仍具優勢；但需準備夏季敘事</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>監看眼鏡市場是否在 5/25 後加碼墨鏡優惠</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/177</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -3115,7 +3316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -3300,57 +3501,228 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>2026/05/04</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Klassic</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>產品線擴張</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>AKILA 系列（多款 OPTIC / SUNGLASS）</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>2026/05 上架</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>$6,580 - $8,680</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>AKILA 是來自洛杉磯的設計師眼鏡品牌，強調極簡與雕塑感。Klassic 為其台灣總代理</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>中高端設計師眼鏡愛好者</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>Klassic 母親節空窗期改打新品線；OD 客群重疊度低但顯示中高端市場品牌推進</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>鏡片新品（病毒式爆紅）</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>腮紅鏡片 Blush Lens</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026年初已上市，5/14-15 媒體再行銷</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NT$2,000 升級費（含框+鏡片配製，客製約 2 週交期）</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>鏡片下半部漸層上色，臉頰呈現自然腮紅感；上半部透明，眼白不染色。三色：sweet pink / peach pink / wine red</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>年輕女性、上班族、約會出遊客群</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>JINS 持續在「鏡片美妝化」差異化路線；OD 可評估彩色鏡片或客製鏡片溝通</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>http://www.jins.com/tw/news/news-6a06972156308</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>品牌戰略升級</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>分眾化雙軌：RIM BY JINS（年輕，5店）+ 大人系店鋪（成熟世代）</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026/05/08 正式宣布</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>依品牌定位</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>RIM BY JINS 主打潮流年輕世代、獨家配件多風格；大人系店鋪針對成熟世代調整店裝、商品、服務模式</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>雙軌：年輕（RIM） + 成熟（大人系）</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>OD 客群分眾敘事需思考（單一品牌 vs 雙品牌雙軌）；OD 鎖定家庭+全客群可作為對比賣點</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>http://www.jins.com/tw/news/news-6a02eb93f00d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>聯名新品</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>KlassiC. x mEltEd potato 0度抗藍光無框眼鏡</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026/05 上架</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NT$3,680</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0度抗藍光功能、無框設計、潮流聯名</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>年輕族群、設計感愛好者</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Klassic 持續走「設計師聯名+差異化」路線，避開純價格戰。OD 可監看年輕族群品牌偏好變化</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/</t>
         </is>
@@ -3370,7 +3742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -3754,6 +4126,147 @@
       <c r="I8" s="17" t="inlineStr">
         <is>
           <t>https://www.businessweekly.com.tw/focus/blog/3021087</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>品牌里程碑/公關</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>JINS 台灣 5/8 百店歡慶記者會 + 分眾新戰略宣布</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>JINS 5/8 在統一時代百貨台北店召開「睛彩100百店歡慶記者會」，正式宣布在台達成 100 間門市，邀請 100 位 VIP 老客戶參加，致贈「睛彩100 VIP 禮盒」（價值約 $3,960）。現場抽 $200,000 現金大獎，一名 VIP 獨得 $100,000。同時宣布下一個十年「深耕在地永續」+ 分眾新戰略（RIM BY JINS + 大人系店鋪）</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鼓鼓 呂思緯、蕭秉治（藝人助陣）</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>全客群 + 老顧客</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>🔥 競品里程碑公關效應強大。OD 需強化品牌力敘事，並可借勢思考：(1) OD 自身百店里程碑是否可預備（OD 78 間，距離百店尚有 22 間） (2) 老顧客 CRM 經營深化</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>http://www.jins.com/tw/news/news-6a02eb93f00d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>產品話題行銷</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>「JINS 腮紅鏡片」女星認證燒進時尚圈</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5/14-15 蕃新聞等媒體報導 JINS 腮紅鏡片走紅，主打「懶人神器」自然腮紅感，三色（sweet pink / peach pink / wine red），升級費 NT$2,000，引發時尚圈與女星推薦</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>年輕女性、上班族、約會出遊客群</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>👀 JINS 持續經營「鏡片美妝化」差異化議題（前有彩色鏡片、後有腮紅鏡片）。OD 可評估彩色/客製鏡片溝通與品牌調性升級</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>http://www.jins.com/tw/news/news-6a06972156308</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>門市週年活動</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>環球板橋店 + 家樂福彰化店 一週年祭</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>兩間 2025/5 開幕門市同步啟動一週年祭限定優惠（5/15 起）。眼鏡市場 2025 起的展店週年活動持續推動</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>雙店所在商圈消費者</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>單店活動但形成「展店一週年 = 週年慶」公關節奏。OD 可借鑑：門市開幕一週年也可推出敘事活動</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
         </is>
       </c>
     </row>
@@ -3771,7 +4284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -4395,6 +4908,53 @@
       <c r="I14" s="17" t="inlineStr">
         <is>
           <t>JINS 4/30 雙店開幕後第一個觀察週，重點轉向母親節最後一週收官效應</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>三品牌</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>穩定週（W22 公開資料校正）</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Jins 95+RIM 5=100（5/8 百店記者會校驗）/ 眼鏡市場 35 / Klassic 20</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>全台</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>JINS 5/8 百店記者會明確宣告 100 間，眼鏡市場 35（5/15 兩店一週年祭啟動）、Klassic 20（X mEltEd potato 新品）</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>本週 Chrome 自動排程未連線，門市計數沿用 W21 並由 JINS 5/8 百店公告交叉確認；下週應恢復實地抓取</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -5459,6 +6019,118 @@
       <c r="F37" s="17" t="inlineStr">
         <is>
           <t>Chrome 實地抓取：全台20間（±0 vs W19）。注意：新增 AKILA 系列商品線（$6,580起，多款 OPTIC/SUNGLASS）— 本週新觀察</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>78</v>
+      </c>
+      <c r="D38" t="n">
+        <v>78</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>全台78間（±0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>100</v>
+      </c>
+      <c r="D39" t="n">
+        <v>100</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>W22 公開資料校正：JINS 5/8 召開百店記者會，正式宣布在台100間（JINS 95+RIM 5）。為在台最快達成百店規模的日系品牌。本週無新增門市公告（±0 vs W21）。註：本週 Chrome 自動排程未連線，門市計數沿用 W21 並交叉確認 JINS 官網百店公告</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>35</v>
+      </c>
+      <c r="D40" t="n">
+        <v>35</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>全台35間（±0 vs W21）。5/15 環球板橋+家樂福彰化店啟動一週年祭限定優惠，無新增門市</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>20</v>
+      </c>
+      <c r="D41" t="n">
+        <v>20</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>全台20間（±0 vs W21）。AKILA 系列與輕行者摺疊墨鏡持續推廣，新增 X mEltEd potato 0度抗藍光無框眼鏡 NT$3,680</t>
         </is>
       </c>
     </row>
@@ -5475,7 +6147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -5837,6 +6509,41 @@
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>W22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026/05/18-05/24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1. 🔥 JINS 5/8 百店里程碑 + 分眾新戰略 — 在台最快達100間日系品牌（10年服務250萬人次，自2025起18天/店），明確宣布 RIM BY JINS（年輕，5店）+「大人系店鋪」（成熟世代）雙軌分眾戰略
+2. 🆕 JINS 5/14-6/30 大型促銷接檔母親節：「指定眼鏡 8折/9折」(藍圓標8折、綠圓標9折)，6.5週橫跨整個夏季前哨，墨鏡+光學眼鏡皆入優惠範圍
+3. 🆕 眼鏡市場 5/15 環球板橋店+家樂福彰化店【一週年祭】限定優惠啟動 / 💄 JINS 5/14-15 腮紅鏡片病毒式爆紅（女星認證 sweet pink/peach pink/wine red 三色 +$2,000）
+門市數：OD 78 / Jins 100 / 眼鏡 35 / KC 20 = 233 間（±0 vs W21）</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>🔴 高（JINS 百店里程碑公關效應 + 6.5週 8折大促接檔 + 分眾戰略明確化）</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>優先：(a) JINS 5/14-6/30 8折期間 OD 套餐價值敘事強化（一價全包 vs JINS 折扣後實價對比） (b) 評估墨鏡夏季方案搶占 JINS 5/14 前空窗 (c) OD 客群分眾思考（呼應 JINS RIM vs 大人系明確分眾）</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5870,7 +6577,7 @@
       </c>
       <c r="B1" s="17" t="inlineStr">
         <is>
-          <t>2026/05/04</t>
+          <t>2026/05/18</t>
         </is>
       </c>
     </row>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -3102,203 +3102,538 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="17" t="inlineStr">
         <is>
           <t>門市促銷</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="17" t="inlineStr">
         <is>
           <t>SUMMER SALE 指定眼鏡限時優惠 8折/9折</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="17" t="inlineStr">
         <is>
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="17" t="inlineStr">
         <is>
           <t>2026/06/30</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="17" t="inlineStr">
         <is>
           <t>🔵藍圓標 8折、🟢綠圓標 9折，指定商品除外、不與其他折扣優惠併用。適用全台 JINS + RIM BY JINS 實體門市。光學眼鏡＋墨鏡皆入優惠範圍</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="17" t="inlineStr">
         <is>
           <t>指定眼鏡 8折/9折（6.5週檔期）</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="17" t="inlineStr">
         <is>
           <t>全台 JINS + RIM 門市</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="17" t="inlineStr">
         <is>
           <t>母親節剛結束（5/10、5/11）立即接檔，6.5週橫跨整個夏季前哨無空窗。OD 套餐制 vs JINS 折扣後實價需明確對比敘事</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" s="17" t="inlineStr">
         <is>
           <t>🔴 高</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L41" s="17" t="inlineStr">
         <is>
           <t>5/14-6/30 期間 OD 套餐價值溝通強化；門市試戴對比；評估墨鏡夏季方案是否提前推出</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M41" s="17" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a04355a0841c</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="17" t="inlineStr">
         <is>
           <t>門市促銷</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="17" t="inlineStr">
         <is>
           <t>【環球板橋店 + 家樂福彰化店】一週年祭限定優惠</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="17" t="inlineStr">
         <is>
           <t>2026/05/15</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="17" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="17" t="inlineStr">
         <is>
           <t>兩間滿週年門市同步啟動一週年祭限定優惠，配鏡滿$3,000折$300+滿$5,000折$500（依官網 5/15 公告）</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="17" t="inlineStr">
         <is>
           <t>滿$3,000折$300、滿$5,000折$500</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" s="17" t="inlineStr">
         <is>
           <t>環球板橋店、家樂福彰化店</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="17" t="inlineStr">
         <is>
           <t>單店限定但板橋為新北重要商圈、彰化為中部周邊城市，OD 新北/中部門市需留意客流分流</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" s="17" t="inlineStr">
         <is>
           <t>⚠️ 中</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L42" s="17" t="inlineStr">
         <is>
           <t>新北板橋 + 彰化 OD 門市5/15-5/25 客流監控；觀察是否擴大至全台檔期</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M42" s="17" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="17" t="inlineStr">
         <is>
           <t>門市促銷</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>【太陽眼鏡優惠】指定鏡框+有度數鏡片 $3,000 起（持續中）</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>2026/04/24</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="17" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="17" t="inlineStr">
         <is>
           <t>夏季墨鏡攻勢持續：指定鏡框搭配有度數鏡片 $3,000 起。預期5月底前進入夏季旺季加碼</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="17" t="inlineStr">
         <is>
           <t>指定鏡框+有度數鏡片 $3,000起</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="17" t="inlineStr">
         <is>
           <t>全台門市</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="17" t="inlineStr">
         <is>
           <t>OD 墨鏡套餐入門價格帶仍具優勢；但需準備夏季敘事</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="17" t="inlineStr">
         <is>
           <t>⚠️ 中</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L43" s="17" t="inlineStr">
         <is>
           <t>監看眼鏡市場是否在 5/25 後加碼墨鏡優惠</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M43" s="17" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/177</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>SUMMER SALE 指定眼鏡 8折/9折（第2週）</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="inlineStr">
+        <is>
+          <t>🔵藍圓標 8折、🟢綠圓標 9折持續，6.5週橫跨夏季</t>
+        </is>
+      </c>
+      <c r="H44" s="17" t="inlineStr">
+        <is>
+          <t>指定眼鏡 8折/9折</t>
+        </is>
+      </c>
+      <c r="I44" s="17" t="inlineStr">
+        <is>
+          <t>全台 JINS + RIM 門市</t>
+        </is>
+      </c>
+      <c r="J44" s="17" t="inlineStr">
+        <is>
+          <t>大促進入第2週，OD 套餐含鏡片實付價對標、門市試戴對比話術持續</t>
+        </is>
+      </c>
+      <c r="K44" s="17" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="L44" s="17" t="inlineStr">
+        <is>
+          <t>OD 夏季墨鏡方案 W23 落地、熱門款實價對標</t>
+        </is>
+      </c>
+      <c r="M44" s="17" t="inlineStr">
+        <is>
+          <t>http://www.jins.com/tw/news/news-6a04355a0841c</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>大全聯嘉義店開幕（5/29）</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場嘉義首店開幕，預期搭配開幕限定優惠</t>
+        </is>
+      </c>
+      <c r="H45" s="17" t="inlineStr">
+        <is>
+          <t>開幕優惠（細節待官網更新）</t>
+        </is>
+      </c>
+      <c r="I45" s="17" t="inlineStr">
+        <is>
+          <t>大全聯嘉義店</t>
+        </is>
+      </c>
+      <c r="J45" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場首度進軍嘉義，OD 嘉義 2 門市需留意客流分流</t>
+        </is>
+      </c>
+      <c r="K45" s="17" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="L45" s="17" t="inlineStr">
+        <is>
+          <t>嘉義 OD 門市 5/29 前後客流監控</t>
+        </is>
+      </c>
+      <c r="M45" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/180</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>【環球板橋+家樂福彰化】一週年祭（持續）</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>兩店一週年祭限定優惠持續</t>
+        </is>
+      </c>
+      <c r="H46" s="17" t="inlineStr">
+        <is>
+          <t>滿$3,000折$300、滿$5,000折$500</t>
+        </is>
+      </c>
+      <c r="I46" s="17" t="inlineStr">
+        <is>
+          <t>環球板橋店、家樂福彰化店</t>
+        </is>
+      </c>
+      <c r="J46" s="17" t="inlineStr">
+        <is>
+          <t>單店限定，OD 新北板橋/彰化門市持續留意</t>
+        </is>
+      </c>
+      <c r="K46" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L46" s="17" t="inlineStr">
+        <is>
+          <t>持續監控</t>
+        </is>
+      </c>
+      <c r="M46" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>【太陽眼鏡優惠】指定鏡框+有度數鏡片 $3,000 起（持續）</t>
+        </is>
+      </c>
+      <c r="E47" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/24</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="inlineStr">
+        <is>
+          <t>夏季墨鏡攻勢持續，與 JINS 8折同期</t>
+        </is>
+      </c>
+      <c r="H47" s="17" t="inlineStr">
+        <is>
+          <t>指定鏡框+有度數鏡片 $3,000起</t>
+        </is>
+      </c>
+      <c r="I47" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J47" s="17" t="inlineStr">
+        <is>
+          <t>OD 墨鏡套餐入門價格帶仍具優勢；夏季敘事需就位</t>
+        </is>
+      </c>
+      <c r="K47" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L47" s="17" t="inlineStr">
+        <is>
+          <t>OD 夏季墨鏡套餐話術與定價落地</t>
+        </is>
+      </c>
+      <c r="M47" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/177</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>聯名促銷</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC. x DAN DA DAN（膽大黨）滿額贈</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="inlineStr">
+        <is>
+          <t>動漫IP聯名，滿額贈限量周邊商品（隨機出貨）</t>
+        </is>
+      </c>
+      <c r="H48" s="17" t="inlineStr">
+        <is>
+          <t>滿額贈周邊</t>
+        </is>
+      </c>
+      <c r="I48" s="17" t="inlineStr">
+        <is>
+          <t>全通路</t>
+        </is>
+      </c>
+      <c r="J48" s="17" t="inlineStr">
+        <is>
+          <t>動漫IP聯名獲客，Klassic 鎖定年輕潮流客群，與OD重疊度低</t>
+        </is>
+      </c>
+      <c r="K48" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低</t>
+        </is>
+      </c>
+      <c r="L48" s="17" t="inlineStr">
+        <is>
+          <t>觀察</t>
+        </is>
+      </c>
+      <c r="M48" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/sale</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -3558,173 +3893,401 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>鏡片新品（病毒式爆紅）</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>腮紅鏡片 Blush Lens</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>2026年初已上市，5/14-15 媒體再行銷</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>NT$2,000 升級費（含框+鏡片配製，客製約 2 週交期）</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>鏡片下半部漸層上色，臉頰呈現自然腮紅感；上半部透明，眼白不染色。三色：sweet pink / peach pink / wine red</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>年輕女性、上班族、約會出遊客群</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t>JINS 持續在「鏡片美妝化」差異化路線；OD 可評估彩色鏡片或客製鏡片溝通</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="17" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a06972156308</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>品牌戰略升級</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>分眾化雙軌：RIM BY JINS（年輕，5店）+ 大人系店鋪（成熟世代）</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>2026/05/08 正式宣布</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>依品牌定位</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>RIM BY JINS 主打潮流年輕世代、獨家配件多風格；大人系店鋪針對成熟世代調整店裝、商品、服務模式</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>雙軌：年輕（RIM） + 成熟（大人系）</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>OD 客群分眾敘事需思考（單一品牌 vs 雙品牌雙軌）；OD 鎖定家庭+全客群可作為對比賣點</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="17" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a02eb93f00d1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Klassic</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>聯名新品</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>KlassiC. x mEltEd potato 0度抗藍光無框眼鏡</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>2026/05 上架</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>NT$3,680</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>0度抗藍光功能、無框設計、潮流聯名</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>年輕族群、設計感愛好者</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>Klassic 持續走「設計師聯名+差異化」路線，避開純價格戰。OD 可監看年輕族群品牌偏好變化</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="17" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>彩色鏡片行銷</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>RIM BY JINS 22色彩色鏡片（台南FOCUS強推）</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/21 行銷</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>升級費依色款</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>22色彩色鏡片+上百種濃淡漸層；Top3：OLIV橄欖棕/光彩橘GLOR/閃亮黃SPYL</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>年輕潮流客群</t>
+        </is>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
+        <is>
+          <t>JINS 續推「鏡片色彩」差異化，南台灣首間RIM。OD 可借勢 SEO/SEM 不正面對抗</t>
+        </is>
+      </c>
+      <c r="K8" s="17" t="inlineStr">
+        <is>
+          <t>http://www.jins.com/tw/news/news-6a0ec678a39d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>自有系列</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>archi by KlassiC. 臉上的微建築</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>2026/05 主打</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>依款式</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>頂級板料+專利技術，建築學結構注入經典框形，力學平衡舒適</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>設計感愛好者、中高端</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>Klassic 持續走設計師差異化路線，強調工藝結構美學</t>
+        </is>
+      </c>
+      <c r="K9" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/archi-by-klassic</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>聯名新品</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC. x DAN DA DAN（膽大黨）聯名</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>2026/05 上架</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>周邊$599起</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>動漫IP聯名，眼鏡+周邊（毛絨拖鞋等），滿額贈</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>年輕動漫/潮流客群</t>
+        </is>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>IP聯名獲客策略；OD 可評估適合的 IP 合作</t>
+        </is>
+      </c>
+      <c r="K10" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/dan-da-dan</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>墨鏡新品</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>輕行者摺疊墨鏡新款（F006/FS001/FM004）+ FUTURE FLEX 機能系列</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>2026/05 上架</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>$1,980-$2,580</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>輕量摺疊墨鏡持續擴款；FUTURE FLEX 主打機能</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>年輕族群、通勤族</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>Klassic 入門墨鏡價格帶（$1,980起）持續擴張，OD 墨鏡入門款需檢視</t>
+        </is>
+      </c>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/folding-sunglasses</t>
         </is>
       </c>
     </row>
@@ -3742,7 +4305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -4130,143 +4693,331 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>品牌里程碑/公關</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>JINS 台灣 5/8 百店歡慶記者會 + 分眾新戰略宣布</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>JINS 5/8 在統一時代百貨台北店召開「睛彩100百店歡慶記者會」，正式宣布在台達成 100 間門市，邀請 100 位 VIP 老客戶參加，致贈「睛彩100 VIP 禮盒」（價值約 $3,960）。現場抽 $200,000 現金大獎，一名 VIP 獨得 $100,000。同時宣布下一個十年「深耕在地永續」+ 分眾新戰略（RIM BY JINS + 大人系店鋪）</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>鼓鼓 呂思緯、蕭秉治（藝人助陣）</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>全客群 + 老顧客</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>🔥 競品里程碑公關效應強大。OD 需強化品牌力敘事，並可借勢思考：(1) OD 自身百店里程碑是否可預備（OD 78 間，距離百店尚有 22 間） (2) 老顧客 CRM 經營深化</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a02eb93f00d1</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>產品話題行銷</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>「JINS 腮紅鏡片」女星認證燒進時尚圈</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>5/14-15 蕃新聞等媒體報導 JINS 腮紅鏡片走紅，主打「懶人神器」自然腮紅感，三色（sweet pink / peach pink / wine red），升級費 NT$2,000，引發時尚圈與女星推薦</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>無</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>年輕女性、上班族、約會出遊客群</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>👀 JINS 持續經營「鏡片美妝化」差異化議題（前有彩色鏡片、後有腮紅鏡片）。OD 可評估彩色/客製鏡片溝通與品牌調性升級</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a06972156308</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>門市週年活動</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>環球板橋店 + 家樂福彰化店 一週年祭</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>兩間 2025/5 開幕門市同步啟動一週年祭限定優惠（5/15 起）。眼鏡市場 2025 起的展店週年活動持續推動</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>無</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>雙店所在商圈消費者</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>單店活動但形成「展店一週年 = 週年慶」公關節奏。OD 可借鑑：門市開幕一週年也可推出敘事活動</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>展店行銷/彩色鏡片</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>RIM BY JINS 進駐台南FOCUS — 南台灣首間RIM、第100間店</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>5/21 報導：RIM 台南FOCUS店同步日本新宿旗艦店裝、22色彩色鏡片牆，鎖定台南火車站精華商圈年輕客群，「霸氣取代原有的O牌競品位置」</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>年輕潮流客群</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>🔥 RIM「取代O牌位置」直接針對OD同類點位；OD 台南需強化年輕客群溝通與門市體驗差異化</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>http://www.jins.com/tw/news/news-6a0ec678a39d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>內容行銷</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>變色/調光鏡片內容雙發（含開車族選購指南）</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>5/19 連發兩篇：全視線/調光/可見光變色鏡片差異比較 + 開車族駕駛專用變色調光鏡片選購指南</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>開車族、戶外客群</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t>JINS 為 SUMMER SALE 墨鏡訴求鋪墊調光鏡片內容；OD 調光/墨鏡內容可同步出</t>
+        </is>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>http://www.jins.com/tw/news/news-6a0be91f59561</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>展店</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>大全聯嘉義店 5/29 開幕（眼鏡市場嘉義首店）</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 5/22 公告大全聯嘉義店 5/29(五)開幕，首度進軍嘉義市場</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>大全聯</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>嘉義消費者</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>🔥 眼鏡市場展店突破，自中部南下嘉義（眼鏡市場嘉義首店）。OD 嘉義門市需應對開幕競爭</t>
+        </is>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/180</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>IP聯名</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC. x DAN DA DAN（膽大黨）動漫聯名</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>動漫IP聯名眼鏡與周邊，滿額贈限量周邊（毛絨拖鞋等）</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>DAN DA DAN（膽大黨）</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>年輕動漫/潮流客群</t>
+        </is>
+      </c>
+      <c r="H15" s="17" t="inlineStr">
+        <is>
+          <t>IP聯名持續是競品獲客手法，OD 可評估 IP 合作切入年輕客群</t>
+        </is>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/dan-da-dan</t>
         </is>
       </c>
     </row>
@@ -4284,7 +5035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -4912,49 +5663,143 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>三品牌</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>穩定週（W22 公開資料校正）</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>Jins 95+RIM 5=100（5/8 百店記者會校驗）/ 眼鏡市場 35 / Klassic 20</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>全台</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>JINS 5/8 百店記者會明確宣告 100 間，眼鏡市場 35（5/15 兩店一週年祭啟動）、Klassic 20（X mEltEd potato 新品）</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="17" t="inlineStr">
         <is>
           <t>本週 Chrome 自動排程未連線，門市計數沿用 W21 並由 JINS 5/8 百店公告交叉確認；下週應恢復實地抓取</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>新開店（預公告）</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>大全聯嘉義店</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>嘉義市 大全聯</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>南部</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/180</t>
+        </is>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場嘉義首店，全台達36間。OD 嘉義門市需留意 5/29 開幕後客流</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>三品牌</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>穩定/異動週（公開來源）</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>JINS 95+RIM 5=100（±0）/ 眼鏡市場 35→36（5/29 嘉義+1）/ Klassic 20（±0）</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>全台</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>jins.com/tw, meganeichiba.com.tw, klassicglobal.com</t>
+        </is>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>本週 Chrome 自動排程未連線，採 web_fetch+WebSearch 公開來源。眼鏡市場嘉義開幕為本週最大展店訊號</t>
         </is>
       </c>
     </row>
@@ -4972,7 +5817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -6023,114 +6868,220 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>OWNDAYS</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="17" t="n">
         <v>78</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="17" t="n">
         <v>78</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="17" t="inlineStr">
         <is>
           <t>全台78間（±0）</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="17" t="inlineStr">
         <is>
           <t>W22 公開資料校正：JINS 5/8 召開百店記者會，正式宣布在台100間（JINS 95+RIM 5）。為在台最快達成百店規模的日系品牌。本週無新增門市公告（±0 vs W21）。註：本週 Chrome 自動排程未連線，門市計數沿用 W21 並交叉確認 JINS 官網百店公告</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="17" t="n">
         <v>35</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="17" t="n">
         <v>35</v>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="17" t="inlineStr">
         <is>
           <t>全台35間（±0 vs W21）。5/15 環球板橋+家樂福彰化店啟動一週年祭限定優惠，無新增門市</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>Klassic</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="17" t="inlineStr">
         <is>
           <t>全台20間（±0 vs W21）。AKILA 系列與輕行者摺疊墨鏡持續推廣，新增 X mEltEd potato 0度抗藍光無框眼鏡 NT$3,680</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>全台78間（±0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D43" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>全台100間（JINS 95+RIM 5，±0 vs W22）。RIM 台南FOCUS 5/21 推22色彩色鏡片行銷，門市數維持</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="D44" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>大全聯嘉義店 5/29(五)開幕（眼鏡市場嘉義首店），全台達36間</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D45" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>全台20間（±0 vs W22）。archi by KlassiC. 微建築系列 + x DAN DA DAN 膽大黨聯名主打</t>
         </is>
       </c>
     </row>
@@ -6147,7 +7098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -6515,17 +7466,17 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>W22</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>2026/05/18-05/24</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>1. 🔥 JINS 5/8 百店里程碑 + 分眾新戰略 — 在台最快達100間日系品牌（10年服務250萬人次，自2025起18天/店），明確宣布 RIM BY JINS（年輕，5店）+「大人系店鋪」（成熟世代）雙軌分眾戰略
 2. 🆕 JINS 5/14-6/30 大型促銷接檔母親節：「指定眼鏡 8折/9折」(藍圓標8折、綠圓標9折)，6.5週橫跨整個夏季前哨，墨鏡+光學眼鏡皆入優惠範圍
@@ -6533,17 +7484,49 @@
 門市數：OD 78 / Jins 100 / 眼鏡 35 / KC 20 = 233 間（±0 vs W21）</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>🔴 高（JINS 百店里程碑公關效應 + 6.5週 8折大促接檔 + 分眾戰略明確化）</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>優先：(a) JINS 5/14-6/30 8折期間 OD 套餐價值敘事強化（一價全包 vs JINS 折扣後實價對比） (b) 評估墨鏡夏季方案搶占 JINS 5/14 前空窗 (c) OD 客群分眾思考（呼應 JINS RIM vs 大人系明確分眾）</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>W23</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/25-05/31</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>1. 🆕 眼鏡市場大全聯嘉義店 5/29 開幕（嘉義首店，+1→36） 2. JINS RIM 台南FOCUS 22色彩色鏡片強推（5/21）+ SUMMER SALE 8折持續（5/14-6/30）第2週 3. Klassic archi 微建築系列 + x DAN DA DAN 聯名滿額贈</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>🔴 高（眼鏡市場展店突破嘉義 + JINS 夏季促銷續燒 + 彩色鏡片內容戰升溫）</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>優先：(a) 嘉義 OD 門市應對眼鏡市場 5/29 開幕 (b) JINS 8折期間 OD 夏季墨鏡方案落地 (c) 監看 JINS/Klassic 彩色鏡片與聯名話題</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6577,10 +7560,11 @@
       </c>
       <c r="B1" s="17" t="inlineStr">
         <is>
-          <t>2026/05/18</t>
-        </is>
-      </c>
-    </row>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="18">
       <c r="A3" s="29" t="inlineStr">
         <is>
@@ -6824,13 +7808,13 @@
         <v>2</v>
       </c>
       <c r="D13" s="32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="18">
@@ -7000,13 +7984,13 @@
         <v>96</v>
       </c>
       <c r="D21" s="34" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21" s="34" t="n">
         <v>20</v>
       </c>
       <c r="F21" s="34" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -3637,6 +3637,542 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>EC促銷</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="inlineStr">
+        <is>
+          <t>JINS官方商城 618 年中慶 年度限時搶購</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="inlineStr">
+        <is>
+          <t>618年中慶年度限時搶購開跑，接檔夏季促銷</t>
+        </is>
+      </c>
+      <c r="H49" s="17" t="inlineStr">
+        <is>
+          <t>年度限時搶購優惠</t>
+        </is>
+      </c>
+      <c r="I49" s="17" t="inlineStr">
+        <is>
+          <t>JINS官方商城(EC)</t>
+        </is>
+      </c>
+      <c r="J49" s="17" t="inlineStr">
+        <is>
+          <t>OD EC/官網 618檔期對標，套餐一價全包敘事</t>
+        </is>
+      </c>
+      <c r="K49" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L49" s="17" t="inlineStr">
+        <is>
+          <t>OD 618/年中檔期方案盤點</t>
+        </is>
+      </c>
+      <c r="M49" s="17" t="inlineStr">
+        <is>
+          <t>http://www.jins.com/tw/news/news-6a18f3b36de34</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>夏日出遊必備 限時3天 買2支眼鏡或墨鏡現折$666</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/31</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr">
+        <is>
+          <t>限時3天 買2支(眼鏡或墨鏡)現折$666，搶攻夏季出遊雙副客群</t>
+        </is>
+      </c>
+      <c r="H50" s="17" t="inlineStr">
+        <is>
+          <t>買2支現折$666</t>
+        </is>
+      </c>
+      <c r="I50" s="17" t="inlineStr">
+        <is>
+          <t>全台JINS門市</t>
+        </is>
+      </c>
+      <c r="J50" s="17" t="inlineStr">
+        <is>
+          <t>短期高強度促銷，OD 雙副/家庭配鏡方案可對標</t>
+        </is>
+      </c>
+      <c r="K50" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L50" s="17" t="inlineStr">
+        <is>
+          <t>OD 多副/家庭配鏡優惠檢視</t>
+        </is>
+      </c>
+      <c r="M50" s="17" t="inlineStr">
+        <is>
+          <t>http://www.jins.com/tw/news/news-6a17b396acf4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>SUMMER SALE 指定眼鏡 8折/9折（第3週）</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="F51" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="inlineStr">
+        <is>
+          <t>🔵藍圓標8折、🟢綠圓標9折持續，橫跨整個夏季</t>
+        </is>
+      </c>
+      <c r="H51" s="17" t="inlineStr">
+        <is>
+          <t>指定眼鏡8折/9折</t>
+        </is>
+      </c>
+      <c r="I51" s="17" t="inlineStr">
+        <is>
+          <t>全台JINS+RIM門市</t>
+        </is>
+      </c>
+      <c r="J51" s="17" t="inlineStr">
+        <is>
+          <t>大促進入第3週，OD套餐含鏡片實付價對標、門市試戴對比話術持續</t>
+        </is>
+      </c>
+      <c r="K51" s="17" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="L51" s="17" t="inlineStr">
+        <is>
+          <t>OD夏季墨鏡方案+熱門款實價對標持續</t>
+        </is>
+      </c>
+      <c r="M51" s="17" t="inlineStr">
+        <is>
+          <t>http://www.jins.com/tw/news/news-6a04355a0841c</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>門市活動</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>比漾廣場永和店 6/1 改裝開幕慶</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>永和店移櫃至5F改裝開幕，當日單筆滿3,000送JINS眼鏡造型折疊提袋</t>
+        </is>
+      </c>
+      <c r="H52" s="17" t="inlineStr">
+        <is>
+          <t>滿3,000元贈折疊提袋</t>
+        </is>
+      </c>
+      <c r="I52" s="17" t="inlineStr">
+        <is>
+          <t>比漾廣場永和店</t>
+        </is>
+      </c>
+      <c r="J52" s="17" t="inlineStr">
+        <is>
+          <t>非新增門市(移櫃改裝)；OD新北永和門市留意短期客流</t>
+        </is>
+      </c>
+      <c r="K52" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低</t>
+        </is>
+      </c>
+      <c r="L52" s="17" t="inlineStr">
+        <is>
+          <t>觀察</t>
+        </is>
+      </c>
+      <c r="M52" s="17" t="inlineStr">
+        <is>
+          <t>http://www.jins.com/tw/news/news-6a17b4645f1d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="inlineStr">
+        <is>
+          <t>2026 SUMMER SALE 眼鏡第二副折300元</t>
+        </is>
+      </c>
+      <c r="E53" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/27</t>
+        </is>
+      </c>
+      <c r="F53" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G53" s="17" t="inlineStr">
+        <is>
+          <t>夏日大作戰，眼鏡第二副折300元</t>
+        </is>
+      </c>
+      <c r="H53" s="17" t="inlineStr">
+        <is>
+          <t>第二副折$300</t>
+        </is>
+      </c>
+      <c r="I53" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J53" s="17" t="inlineStr">
+        <is>
+          <t>與JINS買2支$666同期搶雙副客群；OD多副方案對標</t>
+        </is>
+      </c>
+      <c r="K53" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L53" s="17" t="inlineStr">
+        <is>
+          <t>OD多副配鏡優惠檢視</t>
+        </is>
+      </c>
+      <c r="M53" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/181</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>【太陽眼鏡優惠】指定鏡框+有度數鏡片 $3,000 起（持續）</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>2026/04/24</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>夏季墨鏡攻勢持續，與JINS 8折/夏促同期</t>
+        </is>
+      </c>
+      <c r="H54" s="17" t="inlineStr">
+        <is>
+          <t>指定鏡框+有度數鏡片 $3,000起</t>
+        </is>
+      </c>
+      <c r="I54" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J54" s="17" t="inlineStr">
+        <is>
+          <t>OD 墨鏡套餐入門價格帶仍具優勢；夏季敘事需就位</t>
+        </is>
+      </c>
+      <c r="K54" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L54" s="17" t="inlineStr">
+        <is>
+          <t>OD 夏季墨鏡套餐話術與定價落地</t>
+        </is>
+      </c>
+      <c r="M54" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/177</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>聯名促銷/新品</t>
+        </is>
+      </c>
+      <c r="D55" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC. x 我獨自升級 Solo Leveling 聯名系列上架</t>
+        </is>
+      </c>
+      <c r="E55" s="17" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="inlineStr">
+        <is>
+          <t>動漫IP聯名：限定款威靈頓/多角圓/眉框眼鏡($3,580)、摺疊墨鏡($2,280)、全套周邊(T恤/毛巾/馬克杯/抱枕等)</t>
+        </is>
+      </c>
+      <c r="H55" s="17" t="inlineStr">
+        <is>
+          <t>聯名鏡框$3,580/墨鏡$2,280/周邊$280起</t>
+        </is>
+      </c>
+      <c r="I55" s="17" t="inlineStr">
+        <is>
+          <t>全通路(官網/門市)</t>
+        </is>
+      </c>
+      <c r="J55" s="17" t="inlineStr">
+        <is>
+          <t>大型IP聯名擴張(繼DAN DA DAN後再加碼)，鎖定年輕動漫客群，與OD重疊度低</t>
+        </is>
+      </c>
+      <c r="K55" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低</t>
+        </is>
+      </c>
+      <c r="L55" s="17" t="inlineStr">
+        <is>
+          <t>觀察年輕客群IP聯名熱度</t>
+        </is>
+      </c>
+      <c r="M55" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/klassic-solo-leveling</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>聯名促銷</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC. x DAN DA DAN（膽大黨）滿額贈（持續）</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>動漫IP聯名，滿額贈限量周邊商品（隨機出貨）</t>
+        </is>
+      </c>
+      <c r="H56" s="17" t="inlineStr">
+        <is>
+          <t>滿額贈周邊</t>
+        </is>
+      </c>
+      <c r="I56" s="17" t="inlineStr">
+        <is>
+          <t>全通路</t>
+        </is>
+      </c>
+      <c r="J56" s="17" t="inlineStr">
+        <is>
+          <t>動漫IP聯名獲客，與OD重疊度低</t>
+        </is>
+      </c>
+      <c r="K56" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低</t>
+        </is>
+      </c>
+      <c r="L56" s="17" t="inlineStr">
+        <is>
+          <t>觀察</t>
+        </is>
+      </c>
+      <c r="M56" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/sale</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -3651,7 +4187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -4291,6 +4827,63 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>聯名新品</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC. x 我獨自升級 Solo Leveling 系列</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>2026/06 上架</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>鏡框$3,580/摺疊墨鏡$2,280/周邊$280起</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>人氣動漫IP聯名：限定款威靈頓框/多角圓框/眉框眼鏡+摺疊墨鏡+全套周邊(T恤/毛巾/馬克杯/抱枕/頸枕)</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>年輕動漫/潮流客群</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>Klassic 繼 DAN DA DAN 後再推大型IP聯名，IP獲客策略持續加碼；OD可評估合適IP合作</t>
+        </is>
+      </c>
+      <c r="K12" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/klassic-solo-leveling</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -4305,7 +4898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -5018,6 +5611,147 @@
       <c r="I15" s="17" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/dan-da-dan</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>產品/重要公告</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>【公告】極薄鏡片(折射率1.76)暫停販售與保固</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>5/11公告：JINS 暫停販售折射率1.76極薄鏡片並暫停其保固服務</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>高度數客群</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>👀 競品高折射率(1.76)鏡片退場 — OD 可強化高折射率/高階鏡片供應穩定度與保固敘事，承接JINS流失的高度數客群</t>
+        </is>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>http://www.jins.com/tw/news/news-6a018c67c248d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>IP聯名</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC. x 我獨自升級 Solo Leveling 動漫聯名</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>人氣網漫/動畫IP聯名，限定款眼鏡+墨鏡+全套周邊商品上架(6月)</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>我獨自升級 Solo Leveling</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>年輕動漫/潮流客群</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>IP聯名持續是競品獲客主力(DAN DA DAN→Solo Leveling)，OD可評估IP切入年輕客群</t>
+        </is>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/klassic-solo-leveling</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>EC檔期行銷</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>JINS官方商城 618 年中慶</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>5/29 啟動 618 年中慶年度限時搶購，接檔夏季促銷</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>EC/全客群</t>
+        </is>
+      </c>
+      <c r="H18" s="17" t="inlineStr">
+        <is>
+          <t>JINS 強化EC檔期經營；OD官網618/年中檔期敘事可同步</t>
+        </is>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>http://www.jins.com/tw/news/news-6a18f3b36de34</t>
         </is>
       </c>
     </row>
@@ -5035,7 +5769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -5800,6 +6534,53 @@
       <c r="I17" s="17" t="inlineStr">
         <is>
           <t>本週 Chrome 自動排程未連線，採 web_fetch+WebSearch 公開來源。眼鏡市場嘉義開幕為本週最大展店訊號</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>三品牌</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>穩定週（公開來源）</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>JINS 95+RIM 5=100（±0）/ 眼鏡市場 36（±0）/ Klassic 20（±0）</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>全台</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="17" t="inlineStr">
+        <is>
+          <t>jins.com/tw, meganeichiba.com.tw, klassicglobal.com</t>
+        </is>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>本週無新增門市。JINS 永和比漾店6/1改裝移櫃5F(非新店)；眼鏡市場嘉義店已於5/29計入。三品牌本週轉向促銷/IP聯名競爭</t>
         </is>
       </c>
     </row>
@@ -5817,7 +6598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -7082,6 +7863,112 @@
       <c r="F45" s="17" t="inlineStr">
         <is>
           <t>全台20間（±0 vs W22）。archi by KlassiC. 微建築系列 + x DAN DA DAN 膽大黨聯名主打</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D46" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（校正補列：新店家樂福店/新北 + 潮州車站店/屏東，先前漏算；非本週新開）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D47" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="17" t="inlineStr">
+        <is>
+          <t>全台100間（JINS 95+RIM 5，±0 vs W23）。永和比漾廣場店 6/1 改裝移櫃至5F（非新增門市）；618年中慶啟動</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>全台36間（±0 vs W23）。嘉義店已於5/29計入；本週推 2026 SUMMER SALE 第二副折300</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D49" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>全台20間（±0 vs W23）。新上架「我獨自升級 Solo Leveling」動漫聯名系列（鏡框/摺疊墨鏡/周邊）</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -7527,6 +8414,42 @@
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>W24</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01-06/07</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>1. 🆕 Klassic 上架「我獨自升級 Solo Leveling」大型動漫IP聯名（限定鏡框$3,580/摺疊墨鏡$2,280+全套周邊）— 繼DAN DA DAN後IP聯名再加碼
+2. 🆕 JINS 618年中慶啟動(5/29)+限時3天買2支現折$666(5/29-31)+SUMMER SALE 8折持續(5/14-6/30)第3週；永和比漾店6/1改裝移櫃5F
+3. 🆕 眼鏡市場 2026 SUMMER SALE 第二副折300(5/27起)
+⚠️ JINS 5/11公告 1.76極薄鏡片暫停販售與保固
+門市數：OD 80（校正78→80：補列新店家樂福/新北+潮州車站/屏東）/ Jins 100 / 眼鏡 36 / KC 20 = 236間</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>🔴 高（JINS 618+夏促三檔齊發 + Klassic新IP聯名擴張 + 競品高折射率鏡片退場）</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>優先：(a) JINS 618/買2折$666期間 OD 套餐一價全包價值對標 (b) 借勢 JINS 1.76鏡片退場，強化 OD 高折射率/高階鏡片供應穩定度與保固溝通，承接高度數客群 (c) 監看 Klassic Solo Leveling 聯名年輕客群熱度</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7560,7 +8483,7 @@
       </c>
       <c r="B1" s="17" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/06/01</t>
         </is>
       </c>
     </row>
@@ -7626,7 +8549,7 @@
         </is>
       </c>
       <c r="B5" s="32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="32" t="n">
         <v>19</v>
@@ -7638,7 +8561,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="18">
@@ -7868,7 +8791,7 @@
         </is>
       </c>
       <c r="B16" s="32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="32" t="n">
         <v>1</v>
@@ -7880,7 +8803,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="18">
@@ -7978,7 +8901,7 @@
         </is>
       </c>
       <c r="B21" s="34" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C21" s="34" t="n">
         <v>96</v>
@@ -7990,7 +8913,7 @@
         <v>20</v>
       </c>
       <c r="F21" s="34" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -4168,6 +4168,207 @@
         </is>
       </c>
       <c r="M56" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/06</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
+        <is>
+          <t>【年中慶】年中大感謝 滿額折 + 指定太陽眼鏡最高50% OFF</t>
+        </is>
+      </c>
+      <c r="E57" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="F57" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G57" s="17" t="inlineStr">
+        <is>
+          <t>年中慶滿額折，指定太陽眼鏡最高5折，接檔 SUMMER SALE</t>
+        </is>
+      </c>
+      <c r="H57" s="17" t="inlineStr">
+        <is>
+          <t>滿額折 + 指定太陽眼鏡最高50% OFF</t>
+        </is>
+      </c>
+      <c r="I57" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J57" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場墨鏡5折力道大，OD夏季墨鏡套餐價值對標需強化</t>
+        </is>
+      </c>
+      <c r="K57" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L57" s="17" t="inlineStr">
+        <is>
+          <t>OD夏季墨鏡方案緊盯眼鏡市場太陽眼鏡5折</t>
+        </is>
+      </c>
+      <c r="M57" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/182</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/06</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>【台北市限定】台北市民配鏡現折300元</t>
+        </is>
+      </c>
+      <c r="E58" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="inlineStr">
+        <is>
+          <t>出示台北市居民有效證件，配鏡現折$300（指定商品除外）</t>
+        </is>
+      </c>
+      <c r="H58" s="17" t="inlineStr">
+        <is>
+          <t>台北市民配鏡現折$300</t>
+        </is>
+      </c>
+      <c r="I58" s="17" t="inlineStr">
+        <is>
+          <t>台北市JINS門市</t>
+        </is>
+      </c>
+      <c r="J58" s="17" t="inlineStr">
+        <is>
+          <t>地域性精準促銷搶台北市民；OD台北門市留意在地客分流</t>
+        </is>
+      </c>
+      <c r="K58" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L58" s="17" t="inlineStr">
+        <is>
+          <t>OD台北門市留意在地客；可評估會員/在地優惠回應</t>
+        </is>
+      </c>
+      <c r="M58" s="17" t="inlineStr">
+        <is>
+          <t>http://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/06</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>聯名/促銷</t>
+        </is>
+      </c>
+      <c r="D59" s="17" t="inlineStr">
+        <is>
+          <t>我獨自升級滿額贈限量盲卡包 + 輕行者摺疊墨鏡兩件85折</t>
+        </is>
+      </c>
+      <c r="E59" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="inlineStr">
+        <is>
+          <t>Solo Leveling 聯名滿額贈限量盲卡包；輕行者摺疊墨鏡系列兩件85折</t>
+        </is>
+      </c>
+      <c r="H59" s="17" t="inlineStr">
+        <is>
+          <t>滿額贈盲卡包 / 摺疊墨鏡2件85折</t>
+        </is>
+      </c>
+      <c r="I59" s="17" t="inlineStr">
+        <is>
+          <t>全通路</t>
+        </is>
+      </c>
+      <c r="J59" s="17" t="inlineStr">
+        <is>
+          <t>Klassic以IP聯名滿額贈+墨鏡組合折扣拉客單，與OD重疊低</t>
+        </is>
+      </c>
+      <c r="K59" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低</t>
+        </is>
+      </c>
+      <c r="L59" s="17" t="inlineStr">
+        <is>
+          <t>觀察</t>
+        </is>
+      </c>
+      <c r="M59" s="17" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/categories/sale</t>
         </is>
@@ -6598,7 +6799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -7969,6 +8170,110 @@
       <c r="F49" s="17" t="inlineStr">
         <is>
           <t>全台20間（±0 vs W23）。新上架「我獨自升級 Solo Leveling」動漫聯名系列（鏡框/摺疊墨鏡/周邊）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/06</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/06</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D51" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="17" t="inlineStr">
+        <is>
+          <t>全台100間（JINS 95+RIM 5，±0 vs 6/1）。本週推台北市民配鏡現折$300地域促銷</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/06</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="D52" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>全台36間（±0）。年中慶 6/1 接檔 SUMMER SALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/06</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D53" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="17" t="inlineStr">
+        <is>
+          <t>全台20間（±0）。Solo Leveling 滿額贈盲卡包 + 摺疊墨鏡2件85折</t>
         </is>
       </c>
     </row>
@@ -7985,7 +8290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -8450,6 +8755,41 @@
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>W24-週四</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/06（週四更新）</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>1. 🆕 眼鏡市場【年中慶】滿額折 + 指定太陽眼鏡最高50% OFF（6/1）接檔 SUMMER SALE
+2. 🆕 JINS【台北市限定】台北市民配鏡現折$300（6/1-6/30，地域精準促銷）
+3. 🆕 Klassic 我獨自升級滿額贈限量盲卡包 + 輕行者摺疊墨鏡兩件85折
+門市數：OD 80 / Jins 100 / 眼鏡 36 / KC 20 = 236間（±0 vs 6/1）</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>🟠 中（純促銷加碼、無展店；眼鏡市場太陽眼鏡5折力道較大）</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>(a) OD夏季墨鏡方案對標眼鏡市場太陽眼鏡最高5折 (b) OD台北門市留意 JINS 台北市民現折$300 在地促銷 (c) 持續監看 Klassic Solo Leveling IP 聯名熱度</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8483,11 +8823,10 @@
       </c>
       <c r="B1" s="17" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>2026/06/06</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="15" customHeight="1" s="18">
       <c r="A3" s="29" t="inlineStr">
         <is>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -4374,6 +4374,73 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>週末限定 買2支眼鏡或墨鏡現折$666（再現）</t>
+        </is>
+      </c>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>週末限定</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t>5/29限時3天檔期後，6月首週末再開買2支現折$666</t>
+        </is>
+      </c>
+      <c r="H60" s="17" t="inlineStr">
+        <is>
+          <t>買2支現折$666</t>
+        </is>
+      </c>
+      <c r="I60" s="17" t="inlineStr">
+        <is>
+          <t>全台JINS門市</t>
+        </is>
+      </c>
+      <c r="J60" s="17" t="inlineStr">
+        <is>
+          <t>JINS將「雙副折666」轉為週末例行武器，與眼鏡市場第二副折300同打雙副客群</t>
+        </is>
+      </c>
+      <c r="K60" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L60" s="17" t="inlineStr">
+        <is>
+          <t>OD多副/家庭配鏡方案常態化對標</t>
+        </is>
+      </c>
+      <c r="M60" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -4388,7 +4455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -5085,6 +5152,120 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>聯名墨鏡新品</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>Barbie x JINS 聯名墨鏡系列</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>2026/06 上市</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>限量上市（價格待查）</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>芭比同款貓眼框，Barbie core 夏季時尚訴求，限量配件</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t>年輕女性、潮流客群</t>
+        </is>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="17" t="inlineStr">
+        <is>
+          <t>JINS 暑期再添大型IP聯名（繼吉伊卡哇後），搶夏季墨鏡聲量；OD夏季墨鏡行銷需同步發力</t>
+        </is>
+      </c>
+      <c r="K13" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>機能新品</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>JINS 高機能運動系列（攜手奧運滑板金牌堀米雄斗）</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>2026/06 上市</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>價格待查</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>可調式鼻墊+鏡腳完美包覆，運動機能訴求，奧運金牌選手代言</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>運動族群、年輕男性</t>
+        </is>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="17" t="inlineStr">
+        <is>
+          <t>JINS切入運動眼鏡分眾市場；OD可檢視運動/機能款產品線與溝通</t>
+        </is>
+      </c>
+      <c r="K14" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -5099,7 +5280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -5953,6 +6134,53 @@
       <c r="I18" s="17" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a18f3b36de34</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>展店</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>JINS 高雄大遠百店 6/11 盛大開幕</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>官網門市頁6/8上架「JINS 高雄大遠百店(2026/6/11 盛大開幕)」，高雄第10間、全台第101間</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>大遠百</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>高雄消費者</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>🔥 JINS百店後展店未停步（101間）。OD高雄門市需留意6/11開幕檔期促銷與客流</t>
+        </is>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
         </is>
       </c>
     </row>
@@ -5970,7 +6198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -6782,6 +7010,100 @@
       <c r="I18" s="17" t="inlineStr">
         <is>
           <t>本週無新增門市。JINS 永和比漾店6/1改裝移櫃5F(非新店)；眼鏡市場嘉義店已於5/29計入。三品牌本週轉向促銷/IP聯名競爭</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>新開店（預公告）</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>JINS 高雄大遠百店</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>高雄市 大遠百</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>南部</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores（門市頁6/8上架，店名註記6/11盛大開幕）</t>
+        </is>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>高雄JINS第10間（全台101）。OD高雄門市需留意6/11開幕後客流，尤其大遠百商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>疑似關閉</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>台南門市 -1（店名待確認）</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>南部</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/08發現</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>官網門市頁台南由3間減為2間（剩新光三越小北門店、新光新天地店），下次更新覆核</t>
         </is>
       </c>
     </row>
@@ -6799,7 +7121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -8274,6 +8596,134 @@
       <c r="F53" s="17" t="inlineStr">
         <is>
           <t>全台20間（±0）。Solo Leveling 滿額贈盲卡包 + 摺疊墨鏡2件85折</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D55" s="17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E55" s="17" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>🔥 JINS 高雄大遠百店 6/11 盛大開幕（官網門市頁 6/8 已上架）。JINS 96+RIM 5=101，高雄 9→10</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>全台36間（±0）。年中慶（太陽眼鏡最高5折）持續，無新店公告</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E57" s="17" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F57" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 官網門市頁本週列19間：台南 3→2（僅剩小北門+新天地），疑似關閉/下架1間，店名待確認</t>
         </is>
       </c>
     </row>
@@ -8290,7 +8740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -8790,6 +9240,40 @@
         </is>
       </c>
       <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>W25</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/08-06/14</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>1. 🔥 JINS 高雄大遠百店 6/11 開幕（高雄+1，全台101間，百店後展店續行）
+2. 🆕 JINS 雙IP/分眾新品齊發：Barbie聯名墨鏡 + 堀米雄斗運動系列
+3. ⚠️ Klassic 官網門市頁 20→19（台南-1，疑似關店待確認）；眼鏡市場年中慶太陽眼鏡5折持續</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>🔴 高（JINS高雄開幕+夏季IP新品攻勢；眼鏡市場墨鏡5折續燒）</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>(a) OD高雄門市6/11前後客流監測與對應 (b) OD夏季墨鏡對標眼鏡市場5折+JINS Barbie聯名聲量 (c) 覆核Klassic台南關店與其南部布局收縮訊號</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8823,7 +9307,7 @@
       </c>
       <c r="B1" s="17" t="inlineStr">
         <is>
-          <t>2026/06/06</t>
+          <t>2026/06/08</t>
         </is>
       </c>
     </row>
@@ -8868,8 +9352,10 @@
       <c r="B4" s="32" t="n">
         <v>19</v>
       </c>
-      <c r="C4" s="32" t="n">
-        <v>23</v>
+      <c r="C4" s="32" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="D4" s="32" t="n">
         <v>6</v>
@@ -8877,8 +9363,10 @@
       <c r="E4" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="32" t="n">
-        <v>53</v>
+      <c r="F4" s="32" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="18">
@@ -8890,8 +9378,10 @@
       <c r="B5" s="32" t="n">
         <v>18</v>
       </c>
-      <c r="C5" s="32" t="n">
-        <v>19</v>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="D5" s="32" t="n">
         <v>5</v>
@@ -8899,8 +9389,10 @@
       <c r="E5" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="32" t="n">
-        <v>42</v>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="18">
@@ -8912,8 +9404,10 @@
       <c r="B6" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="32" t="n">
-        <v>1</v>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D6" s="32" t="n">
         <v>0</v>
@@ -8921,8 +9415,10 @@
       <c r="E6" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="32" t="n">
-        <v>2</v>
+      <c r="F6" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="18">
@@ -8934,8 +9430,10 @@
       <c r="B7" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="C7" s="32" t="n">
-        <v>9</v>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="D7" s="32" t="n">
         <v>4</v>
@@ -8943,8 +9441,10 @@
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="32" t="n">
-        <v>23</v>
+      <c r="F7" s="32" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="18">
@@ -8956,8 +9456,10 @@
       <c r="B8" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="32" t="n">
-        <v>4</v>
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D8" s="32" t="n">
         <v>3</v>
@@ -8965,8 +9467,10 @@
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="32" t="n">
-        <v>12</v>
+      <c r="F8" s="32" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="18">
@@ -8978,8 +9482,10 @@
       <c r="B9" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="32" t="n">
-        <v>1</v>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D9" s="32" t="n">
         <v>0</v>
@@ -8987,8 +9493,10 @@
       <c r="E9" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="32" t="n">
-        <v>2</v>
+      <c r="F9" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="18">
@@ -9000,8 +9508,10 @@
       <c r="B10" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="32" t="n">
-        <v>15</v>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="D10" s="32" t="n">
         <v>7</v>
@@ -9009,8 +9519,10 @@
       <c r="E10" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="32" t="n">
-        <v>30</v>
+      <c r="F10" s="32" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="18">
@@ -9022,8 +9534,10 @@
       <c r="B11" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="32" t="n">
-        <v>0</v>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D11" s="32" t="n">
         <v>1</v>
@@ -9031,8 +9545,10 @@
       <c r="E11" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="32" t="n">
-        <v>2</v>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="18">
@@ -9044,8 +9560,10 @@
       <c r="B12" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="32" t="n">
-        <v>2</v>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D12" s="32" t="n">
         <v>0</v>
@@ -9053,8 +9571,10 @@
       <c r="E12" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="32" t="n">
-        <v>2</v>
+      <c r="F12" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="18">
@@ -9066,8 +9586,10 @@
       <c r="B13" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="32" t="n">
-        <v>2</v>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D13" s="32" t="n">
         <v>1</v>
@@ -9075,8 +9597,10 @@
       <c r="E13" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="32" t="n">
-        <v>5</v>
+      <c r="F13" s="32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="18">
@@ -9088,17 +9612,23 @@
       <c r="B14" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="32" t="n">
-        <v>8</v>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="D14" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="32" t="n">
-        <v>17</v>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="18">
@@ -9110,8 +9640,10 @@
       <c r="B15" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="32" t="n">
-        <v>9</v>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D15" s="32" t="n">
         <v>5</v>
@@ -9119,8 +9651,10 @@
       <c r="E15" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="32" t="n">
-        <v>26</v>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="18">
@@ -9132,8 +9666,10 @@
       <c r="B16" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="32" t="n">
-        <v>1</v>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D16" s="32" t="n">
         <v>0</v>
@@ -9141,8 +9677,10 @@
       <c r="E16" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="32" t="n">
-        <v>3</v>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="18">
@@ -9154,8 +9692,10 @@
       <c r="B17" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="32" t="n">
-        <v>1</v>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D17" s="32" t="n">
         <v>1</v>
@@ -9163,8 +9703,10 @@
       <c r="E17" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="32" t="n">
-        <v>3</v>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="18">
@@ -9176,8 +9718,10 @@
       <c r="B18" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="32" t="n">
-        <v>1</v>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D18" s="32" t="n">
         <v>0</v>
@@ -9185,8 +9729,10 @@
       <c r="E18" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="32" t="n">
-        <v>2</v>
+      <c r="F18" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="18">
@@ -9198,8 +9744,10 @@
       <c r="B19" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="32" t="n">
-        <v>0</v>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D19" s="32" t="n">
         <v>0</v>
@@ -9207,8 +9755,10 @@
       <c r="E19" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="32" t="n">
-        <v>1</v>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="18">
@@ -9220,8 +9770,10 @@
       <c r="B20" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="32" t="n">
-        <v>0</v>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D20" s="32" t="n">
         <v>0</v>
@@ -9229,8 +9781,10 @@
       <c r="E20" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="32" t="n">
-        <v>1</v>
+      <c r="F20" s="32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="18">
@@ -9239,20 +9793,30 @@
           <t>店鋪數</t>
         </is>
       </c>
-      <c r="B21" s="34" t="n">
-        <v>80</v>
-      </c>
-      <c r="C21" s="34" t="n">
-        <v>96</v>
-      </c>
-      <c r="D21" s="34" t="n">
-        <v>36</v>
-      </c>
-      <c r="E21" s="34" t="n">
-        <v>20</v>
-      </c>
-      <c r="F21" s="34" t="n">
-        <v>232</v>
+      <c r="B21" s="34" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="C21" s="34" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D21" s="34" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E21" s="34" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F21" s="34" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -122,6 +122,10 @@
       <name val="Microsoft JhengHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -184,7 +188,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -291,6 +295,17 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -570,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -714,7 +729,7 @@
           <t>強化套餐組合價值溝通</t>
         </is>
       </c>
-      <c r="M2" s="21" t="inlineStr">
+      <c r="M2" s="36" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news</t>
         </is>
@@ -781,7 +796,7 @@
           <t>維持現有EC策略</t>
         </is>
       </c>
-      <c r="M3" s="21" t="inlineStr">
+      <c r="M3" s="36" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news</t>
         </is>
@@ -823,7 +838,7 @@
           <t>滿$6,000折$666</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="H4" s="36" t="inlineStr">
         <is>
           <t>https://meganeichiba.com.tw/news/170</t>
         </is>
@@ -848,7 +863,7 @@
           <t>觀察即可</t>
         </is>
       </c>
-      <c r="M4" s="21" t="inlineStr">
+      <c r="M4" s="36" t="inlineStr">
         <is>
           <t>https://meganeichiba.com.tw/news/170</t>
         </is>
@@ -890,7 +905,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69bbd0d86594a</t>
         </is>
@@ -937,7 +952,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69b79ee18887f</t>
         </is>
@@ -984,7 +999,7 @@
           <t>低</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="37" t="inlineStr">
         <is>
           <t>https://meganeichiba.com.tw/news/173</t>
         </is>
@@ -1031,7 +1046,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="37" t="inlineStr">
         <is>
           <t>https://meganeichiba.com.tw/news/171</t>
         </is>
@@ -1078,7 +1093,7 @@
           <t>低</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="37" t="inlineStr">
         <is>
           <t>https://meganeichiba.com.tw/news/170</t>
         </is>
@@ -1125,7 +1140,7 @@
           <t>低</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
@@ -1172,7 +1187,7 @@
           <t>低</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
@@ -1244,7 +1259,7 @@
           <t>監控週末業績變化</t>
         </is>
       </c>
-      <c r="M12" s="17" t="inlineStr">
+      <c r="M12" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69bbd0d86594a</t>
         </is>
@@ -1311,7 +1326,7 @@
           <t>持續觀察</t>
         </is>
       </c>
-      <c r="M13" s="17" t="inlineStr">
+      <c r="M13" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69b79ee18887f</t>
         </is>
@@ -1378,7 +1393,7 @@
           <t>評估類似回收計畫可行性</t>
         </is>
       </c>
-      <c r="M14" s="17" t="inlineStr">
+      <c r="M14" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69b125db355d0</t>
         </is>
@@ -1445,7 +1460,7 @@
           <t>觀察活動結束後客流變化</t>
         </is>
       </c>
-      <c r="M15" s="17" t="inlineStr">
+      <c r="M15" s="37" t="inlineStr">
         <is>
           <t>https://meganeichiba.com.tw/news/170</t>
         </is>
@@ -1512,7 +1527,7 @@
           <t>注意台中/南港門市客流</t>
         </is>
       </c>
-      <c r="M16" s="17" t="inlineStr">
+      <c r="M16" s="37" t="inlineStr">
         <is>
           <t>https://meganeichiba.com.tw/news/171</t>
         </is>
@@ -1579,7 +1594,7 @@
           <t>持續觀察</t>
         </is>
       </c>
-      <c r="M17" s="17" t="inlineStr">
+      <c r="M17" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
@@ -1646,7 +1661,7 @@
           <t>持續觀察</t>
         </is>
       </c>
-      <c r="M18" s="17" t="inlineStr">
+      <c r="M18" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
@@ -1713,7 +1728,7 @@
           <t>觀察客流是否下降</t>
         </is>
       </c>
-      <c r="M19" s="17" t="inlineStr">
+      <c r="M19" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69bbd0d86594a</t>
         </is>
@@ -1780,7 +1795,7 @@
           <t>觀察4月新EC活動</t>
         </is>
       </c>
-      <c r="M20" s="17" t="inlineStr">
+      <c r="M20" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69b79ee18887f</t>
         </is>
@@ -1847,7 +1862,7 @@
           <t>持續監控</t>
         </is>
       </c>
-      <c r="M21" s="17" t="inlineStr">
+      <c r="M21" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69b125db355d0</t>
         </is>
@@ -1914,7 +1929,7 @@
           <t>觀察4月新活動</t>
         </is>
       </c>
-      <c r="M22" s="17" t="inlineStr">
+      <c r="M22" s="37" t="inlineStr">
         <is>
           <t>https://meganeichiba.com.tw/news/170</t>
         </is>
@@ -1981,7 +1996,7 @@
           <t>持續觀察</t>
         </is>
       </c>
-      <c r="M23" s="17" t="inlineStr">
+      <c r="M23" s="37" t="inlineStr">
         <is>
           <t>https://meganeichiba.com.tw/news/171</t>
         </is>
@@ -2048,7 +2063,7 @@
           <t>觀察4月新活動</t>
         </is>
       </c>
-      <c r="M24" s="17" t="inlineStr">
+      <c r="M24" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
@@ -2115,7 +2130,7 @@
           <t>觀察</t>
         </is>
       </c>
-      <c r="M25" s="17" t="inlineStr">
+      <c r="M25" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
@@ -2182,7 +2197,7 @@
           <t>強化OD套餐制一價全包的價值溝通</t>
         </is>
       </c>
-      <c r="M26" s="17" t="inlineStr">
+      <c r="M26" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69ca36fe489e3</t>
         </is>
@@ -2249,7 +2264,7 @@
           <t>關注兩個週末門市客流變化</t>
         </is>
       </c>
-      <c r="M27" s="17" t="inlineStr">
+      <c r="M27" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69ca367f3b199</t>
         </is>
@@ -2316,7 +2331,7 @@
           <t>評估OD母親節檔期是否需要對應活動</t>
         </is>
       </c>
-      <c r="M28" s="17" t="inlineStr">
+      <c r="M28" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69ca377bd183c</t>
         </is>
@@ -2383,7 +2398,7 @@
           <t>關注全台門市客流變化，可考慮同期揪團配鏡優惠</t>
         </is>
       </c>
-      <c r="M29" s="35" t="inlineStr">
+      <c r="M29" s="38" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/175</t>
         </is>
@@ -2450,7 +2465,7 @@
           <t>台中門市需密切關注業績，可考慮中部門市限定回應措施</t>
         </is>
       </c>
-      <c r="M30" s="35" t="inlineStr">
+      <c r="M30" s="38" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/174</t>
         </is>
@@ -2517,7 +2532,7 @@
           <t>強調OD套餐一價全包優勢</t>
         </is>
       </c>
-      <c r="M31" s="17" t="inlineStr">
+      <c r="M31" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69ca36fe489e3</t>
         </is>
@@ -2584,7 +2599,7 @@
           <t>規劃母親節對應促銷</t>
         </is>
       </c>
-      <c r="M32" s="17" t="inlineStr">
+      <c r="M32" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69ca377bd183c</t>
         </is>
@@ -2651,7 +2666,7 @@
           <t>關注Klassic客群反應</t>
         </is>
       </c>
-      <c r="M33" s="17" t="inlineStr">
+      <c r="M33" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com</t>
         </is>
@@ -2693,7 +2708,7 @@
           <t>品牌公關活動，非直接促銷但提升品牌好感度</t>
         </is>
       </c>
-      <c r="M34" s="17" t="inlineStr">
+      <c r="M34" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69d4a2dd8376b</t>
         </is>
@@ -2760,7 +2775,7 @@
           <t>W19前發布OD母親節檔期方案</t>
         </is>
       </c>
-      <c r="M35" s="17" t="inlineStr">
+      <c r="M35" s="37" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news</t>
         </is>
@@ -2827,7 +2842,7 @@
           <t>強化 OD 套餐含漸進升級的差異化敘事</t>
         </is>
       </c>
-      <c r="M36" s="17" t="inlineStr">
+      <c r="M36" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69e99ed82f2ac</t>
         </is>
@@ -2894,7 +2909,7 @@
           <t>評估墨鏡入門價格帶促銷</t>
         </is>
       </c>
-      <c r="M37" s="17" t="inlineStr">
+      <c r="M37" s="37" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/177</t>
         </is>
@@ -2961,7 +2976,7 @@
           <t>5/8-5/10 周末客流監控、強化 OD 套餐含漸進升級的「一價全包」敘事</t>
         </is>
       </c>
-      <c r="M38" s="17" t="inlineStr">
+      <c r="M38" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69e99ed82f2ac</t>
         </is>
@@ -3028,7 +3043,7 @@
           <t>盤點門店母親節週末庫存與促銷話術</t>
         </is>
       </c>
-      <c r="M39" s="17" t="inlineStr">
+      <c r="M39" s="37" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/176</t>
         </is>
@@ -3095,7 +3110,7 @@
           <t>5/11 後若眼鏡市場加碼墨鏡，OD 需準備夏季墨鏡套餐話術</t>
         </is>
       </c>
-      <c r="M40" s="17" t="inlineStr">
+      <c r="M40" s="37" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/177</t>
         </is>
@@ -3162,7 +3177,7 @@
           <t>5/14-6/30 期間 OD 套餐價值溝通強化；門市試戴對比；評估墨鏡夏季方案是否提前推出</t>
         </is>
       </c>
-      <c r="M41" s="17" t="inlineStr">
+      <c r="M41" s="37" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a04355a0841c</t>
         </is>
@@ -3229,7 +3244,7 @@
           <t>新北板橋 + 彰化 OD 門市5/15-5/25 客流監控；觀察是否擴大至全台檔期</t>
         </is>
       </c>
-      <c r="M42" s="17" t="inlineStr">
+      <c r="M42" s="37" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news</t>
         </is>
@@ -3296,7 +3311,7 @@
           <t>監看眼鏡市場是否在 5/25 後加碼墨鏡優惠</t>
         </is>
       </c>
-      <c r="M43" s="17" t="inlineStr">
+      <c r="M43" s="37" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/177</t>
         </is>
@@ -3363,7 +3378,7 @@
           <t>OD 夏季墨鏡方案 W23 落地、熱門款實價對標</t>
         </is>
       </c>
-      <c r="M44" s="17" t="inlineStr">
+      <c r="M44" s="37" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a04355a0841c</t>
         </is>
@@ -3430,7 +3445,7 @@
           <t>嘉義 OD 門市 5/29 前後客流監控</t>
         </is>
       </c>
-      <c r="M45" s="17" t="inlineStr">
+      <c r="M45" s="37" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/180</t>
         </is>
@@ -3497,7 +3512,7 @@
           <t>持續監控</t>
         </is>
       </c>
-      <c r="M46" s="17" t="inlineStr">
+      <c r="M46" s="37" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news</t>
         </is>
@@ -3564,7 +3579,7 @@
           <t>OD 夏季墨鏡套餐話術與定價落地</t>
         </is>
       </c>
-      <c r="M47" s="17" t="inlineStr">
+      <c r="M47" s="37" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/177</t>
         </is>
@@ -3631,7 +3646,7 @@
           <t>觀察</t>
         </is>
       </c>
-      <c r="M48" s="17" t="inlineStr">
+      <c r="M48" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/categories/sale</t>
         </is>
@@ -3698,7 +3713,7 @@
           <t>OD 618/年中檔期方案盤點</t>
         </is>
       </c>
-      <c r="M49" s="17" t="inlineStr">
+      <c r="M49" s="37" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a18f3b36de34</t>
         </is>
@@ -3765,7 +3780,7 @@
           <t>OD 多副/家庭配鏡優惠檢視</t>
         </is>
       </c>
-      <c r="M50" s="17" t="inlineStr">
+      <c r="M50" s="37" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a17b396acf4c</t>
         </is>
@@ -3832,7 +3847,7 @@
           <t>OD夏季墨鏡方案+熱門款實價對標持續</t>
         </is>
       </c>
-      <c r="M51" s="17" t="inlineStr">
+      <c r="M51" s="37" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a04355a0841c</t>
         </is>
@@ -3899,7 +3914,7 @@
           <t>觀察</t>
         </is>
       </c>
-      <c r="M52" s="17" t="inlineStr">
+      <c r="M52" s="37" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a17b4645f1d9</t>
         </is>
@@ -3966,7 +3981,7 @@
           <t>OD多副配鏡優惠檢視</t>
         </is>
       </c>
-      <c r="M53" s="17" t="inlineStr">
+      <c r="M53" s="37" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/181</t>
         </is>
@@ -4033,7 +4048,7 @@
           <t>OD 夏季墨鏡套餐話術與定價落地</t>
         </is>
       </c>
-      <c r="M54" s="17" t="inlineStr">
+      <c r="M54" s="37" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/177</t>
         </is>
@@ -4100,7 +4115,7 @@
           <t>觀察年輕客群IP聯名熱度</t>
         </is>
       </c>
-      <c r="M55" s="17" t="inlineStr">
+      <c r="M55" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/klassic-solo-leveling</t>
         </is>
@@ -4167,7 +4182,7 @@
           <t>觀察</t>
         </is>
       </c>
-      <c r="M56" s="17" t="inlineStr">
+      <c r="M56" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/categories/sale</t>
         </is>
@@ -4234,7 +4249,7 @@
           <t>OD夏季墨鏡方案緊盯眼鏡市場太陽眼鏡5折</t>
         </is>
       </c>
-      <c r="M57" s="17" t="inlineStr">
+      <c r="M57" s="37" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/182</t>
         </is>
@@ -4301,9 +4316,9 @@
           <t>OD台北門市留意在地客；可評估會員/在地優惠回應</t>
         </is>
       </c>
-      <c r="M58" s="17" t="inlineStr">
-        <is>
-          <t>http://www.jins.com/tw/news</t>
+      <c r="M58" s="37" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a1e4dc57fe5a</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4383,7 @@
           <t>觀察</t>
         </is>
       </c>
-      <c r="M59" s="17" t="inlineStr">
+      <c r="M59" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/categories/sale</t>
         </is>
@@ -4392,7 +4407,7 @@
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
-          <t>週末限定 買2支眼鏡或墨鏡現折$666（再現）</t>
+          <t>週末限定 買2支眼鏡或墨鏡現折$666（五六日限定，6月連檔）</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
@@ -4402,12 +4417,12 @@
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>週末限定</t>
+          <t>2026/06/21</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>5/29限時3天檔期後，6月首週末再開買2支現折$666</t>
+          <t>五六日限定：6/5-6/7、6/12-6/14、6/19-6/21，購買2支(眼鏡或墨鏡)現折$666（指定商品除外，不與其他折扣併用）</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
@@ -4435,14 +4450,348 @@
           <t>OD多副/家庭配鏡方案常態化對標</t>
         </is>
       </c>
-      <c r="M60" s="17" t="inlineStr">
-        <is>
-          <t>https://www.jins.com/tw/news</t>
+      <c r="M60" s="37" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a212b4367aaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="inlineStr">
+        <is>
+          <t>自有款折扣</t>
+        </is>
+      </c>
+      <c r="D61" s="17" t="inlineStr">
+        <is>
+          <t>LOVA / BELLA 自有款 9折（SALE專區）</t>
+        </is>
+      </c>
+      <c r="E61" s="17" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G61" s="17" t="inlineStr">
+        <is>
+          <t>LOVA $3,980→$3,582、BELLA $2,980→$2,682，自有設計款進 SALE 專區9折（vs 6/1 新增）</t>
+        </is>
+      </c>
+      <c r="H61" s="17" t="inlineStr">
+        <is>
+          <t>自有款9折</t>
+        </is>
+      </c>
+      <c r="I61" s="17" t="inlineStr">
+        <is>
+          <t>全通路</t>
+        </is>
+      </c>
+      <c r="J61" s="17" t="inlineStr">
+        <is>
+          <t>Klassic 除IP聯名外，自有設計款也加入折扣戰拉動買氣；OD重疊度仍低</t>
+        </is>
+      </c>
+      <c r="K61" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低</t>
+        </is>
+      </c>
+      <c r="L61" s="17" t="inlineStr">
+        <is>
+          <t>觀察</t>
+        </is>
+      </c>
+      <c r="M61" s="37" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>聯名周邊組合促銷</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC. x DAN DA DAN 周邊組合下殺</t>
+        </is>
+      </c>
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G62" s="17" t="inlineStr">
+        <is>
+          <t>拖鞋+毛巾/毛毯/收納盒/帽子等組合約85-9折（如拖鞋+毛巾組$998→$848），vs 6/1 新增</t>
+        </is>
+      </c>
+      <c r="H62" s="17" t="inlineStr">
+        <is>
+          <t>組合約85-9折</t>
+        </is>
+      </c>
+      <c r="I62" s="17" t="inlineStr">
+        <is>
+          <t>全通路</t>
+        </is>
+      </c>
+      <c r="J62" s="17" t="inlineStr">
+        <is>
+          <t>IP聯名從「滿額贈」延伸到「組合折扣」清庫存+拉客單；與OD重疊低</t>
+        </is>
+      </c>
+      <c r="K62" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低</t>
+        </is>
+      </c>
+      <c r="L62" s="17" t="inlineStr">
+        <is>
+          <t>觀察</t>
+        </is>
+      </c>
+      <c r="M62" s="37" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>墨鏡擴款</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr">
+        <is>
+          <t>輕行者摺疊墨鏡 SALE 專區擴款（FM003/FM004/F006/F007）</t>
+        </is>
+      </c>
+      <c r="E63" s="17" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="F63" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G63" s="17" t="inlineStr">
+        <is>
+          <t>輕行者摺疊墨鏡入門款（全$1,980）於SALE專區大幅擴款，vs 6/1（FS001/FM004）新增多款</t>
+        </is>
+      </c>
+      <c r="H63" s="17" t="inlineStr">
+        <is>
+          <t>$1,980入門墨鏡擴款</t>
+        </is>
+      </c>
+      <c r="I63" s="17" t="inlineStr">
+        <is>
+          <t>全通路</t>
+        </is>
+      </c>
+      <c r="J63" s="17" t="inlineStr">
+        <is>
+          <t>Klassic 入門摺疊墨鏡價格帶($1,980)持續擴張，OD墨鏡入門款需檢視</t>
+        </is>
+      </c>
+      <c r="K63" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L63" s="17" t="inlineStr">
+        <is>
+          <t>OD墨鏡入門款價格帶檢視</t>
+        </is>
+      </c>
+      <c r="M63" s="37" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>（無新動態）</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr">
+        <is>
+          <t>vs 6/1 無新促銷 — 年中慶（太陽眼鏡最高5折）持續</t>
+        </is>
+      </c>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>官網 news 最新仍為 6/1 年中慶，6/1以來無新檔期；太陽眼鏡最高5折+滿額折持續</t>
+        </is>
+      </c>
+      <c r="H64" s="17" t="inlineStr">
+        <is>
+          <t>滿額折+太陽眼鏡最高50% OFF（持續）</t>
+        </is>
+      </c>
+      <c r="I64" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J64" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場本週無新動作，墨鏡5折持續，OD夏季墨鏡敘事需持續對標</t>
+        </is>
+      </c>
+      <c r="K64" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L64" s="17" t="inlineStr">
+        <is>
+          <t>OD夏季墨鏡持續對標眼鏡市場5折</t>
+        </is>
+      </c>
+      <c r="M64" s="37" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/182</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId64"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4576,7 +4925,7 @@
           <t>OD可考慮IP聯名策略</t>
         </is>
       </c>
-      <c r="K2" s="21" t="inlineStr">
+      <c r="K2" s="36" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/page/Chiikawa/</t>
         </is>
@@ -4633,7 +4982,7 @@
           <t>JINS持續在輕量舒適領域創新，OD可評估類似技術導入</t>
         </is>
       </c>
-      <c r="K3" s="17" t="inlineStr">
+      <c r="K3" s="37" t="inlineStr">
         <is>
           <t>https://www.stufftaiwan.com/2026/04/11/jins-airframe</t>
         </is>
@@ -4690,7 +5039,7 @@
           <t>Klassic 母親節空窗期改打新品線；OD 客群重疊度低但顯示中高端市場品牌推進</t>
         </is>
       </c>
-      <c r="K4" s="17" t="inlineStr">
+      <c r="K4" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/</t>
         </is>
@@ -4747,7 +5096,7 @@
           <t>JINS 持續在「鏡片美妝化」差異化路線；OD 可評估彩色鏡片或客製鏡片溝通</t>
         </is>
       </c>
-      <c r="K5" s="17" t="inlineStr">
+      <c r="K5" s="37" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a06972156308</t>
         </is>
@@ -4804,7 +5153,7 @@
           <t>OD 客群分眾敘事需思考（單一品牌 vs 雙品牌雙軌）；OD 鎖定家庭+全客群可作為對比賣點</t>
         </is>
       </c>
-      <c r="K6" s="17" t="inlineStr">
+      <c r="K6" s="37" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a02eb93f00d1</t>
         </is>
@@ -4861,7 +5210,7 @@
           <t>Klassic 持續走「設計師聯名+差異化」路線，避開純價格戰。OD 可監看年輕族群品牌偏好變化</t>
         </is>
       </c>
-      <c r="K7" s="17" t="inlineStr">
+      <c r="K7" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/</t>
         </is>
@@ -4918,7 +5267,7 @@
           <t>JINS 續推「鏡片色彩」差異化，南台灣首間RIM。OD 可借勢 SEO/SEM 不正面對抗</t>
         </is>
       </c>
-      <c r="K8" s="17" t="inlineStr">
+      <c r="K8" s="37" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a0ec678a39d4</t>
         </is>
@@ -4975,7 +5324,7 @@
           <t>Klassic 持續走設計師差異化路線，強調工藝結構美學</t>
         </is>
       </c>
-      <c r="K9" s="17" t="inlineStr">
+      <c r="K9" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/archi-by-klassic</t>
         </is>
@@ -5032,7 +5381,7 @@
           <t>IP聯名獲客策略；OD 可評估適合的 IP 合作</t>
         </is>
       </c>
-      <c r="K10" s="17" t="inlineStr">
+      <c r="K10" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/dan-da-dan</t>
         </is>
@@ -5089,7 +5438,7 @@
           <t>Klassic 入門墨鏡價格帶（$1,980起）持續擴張，OD 墨鏡入門款需檢視</t>
         </is>
       </c>
-      <c r="K11" s="17" t="inlineStr">
+      <c r="K11" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/categories/folding-sunglasses</t>
         </is>
@@ -5146,7 +5495,7 @@
           <t>Klassic 繼 DAN DA DAN 後再推大型IP聯名，IP獲客策略持續加碼；OD可評估合適IP合作</t>
         </is>
       </c>
-      <c r="K12" s="17" t="inlineStr">
+      <c r="K12" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/klassic-solo-leveling</t>
         </is>
@@ -5203,9 +5552,9 @@
           <t>JINS 暑期再添大型IP聯名（繼吉伊卡哇後），搶夏季墨鏡聲量；OD夏季墨鏡行銷需同步發力</t>
         </is>
       </c>
-      <c r="K13" s="17" t="inlineStr">
-        <is>
-          <t>https://www.jins.com/tw/news</t>
+      <c r="K13" s="37" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a20eb987fd0f</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5609,29 @@
           <t>JINS切入運動眼鏡分眾市場；OD可檢視運動/機能款產品線與溝通</t>
         </is>
       </c>
-      <c r="K14" s="17" t="inlineStr">
-        <is>
-          <t>https://www.jins.com/tw/news</t>
+      <c r="K14" s="37" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a1ea583854aa</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5379,7 +5743,7 @@
           <t>結合運動賽事+名人效應，OD可評估類似合作</t>
         </is>
       </c>
-      <c r="I2" s="21" t="inlineStr">
+      <c r="I2" s="36" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69b28e2568f84</t>
         </is>
@@ -5426,7 +5790,7 @@
           <t>IP聯名策略值得參考，可評估適合OD的IP合作</t>
         </is>
       </c>
-      <c r="I3" s="21" t="inlineStr">
+      <c r="I3" s="36" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/page/Chiikawa/</t>
         </is>
@@ -5473,7 +5837,7 @@
           <t>名人代言+產品耐用性展示，可考慮類似合作</t>
         </is>
       </c>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="I4" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69b28e2568f84</t>
         </is>
@@ -5520,7 +5884,7 @@
           <t>ESG+獲客策略結合，回收競品眼鏡轉換客戶，值得參考</t>
         </is>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69b125db355d0</t>
         </is>
@@ -5567,7 +5931,7 @@
           <t>🔥 競品公關危機=OD機會。可透過社群/門市強調OD透明定價、性價比優勢，但不宜直接攻擊。</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="37" t="inlineStr">
         <is>
           <t>https://www.ettoday.net/news/20260330/3141094.htm</t>
         </is>
@@ -5614,7 +5978,7 @@
           <t>輕量舒適為眼鏡市場重要差異化方向，OD可參考</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="37" t="inlineStr">
         <is>
           <t>https://www.stufftaiwan.com/2026/04/11/jins-airframe</t>
         </is>
@@ -5661,7 +6025,7 @@
           <t>大型百貨進駐效應顯著，需關注台中門市客流分散</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I8" s="37" t="inlineStr">
         <is>
           <t>https://www.businessweekly.com.tw/focus/blog/3021087</t>
         </is>
@@ -5708,7 +6072,7 @@
           <t>🔥 競品里程碑公關效應強大。OD 需強化品牌力敘事，並可借勢思考：(1) OD 自身百店里程碑是否可預備（OD 78 間，距離百店尚有 22 間） (2) 老顧客 CRM 經營深化</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I9" s="37" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a02eb93f00d1</t>
         </is>
@@ -5755,7 +6119,7 @@
           <t>👀 JINS 持續經營「鏡片美妝化」差異化議題（前有彩色鏡片、後有腮紅鏡片）。OD 可評估彩色/客製鏡片溝通與品牌調性升級</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I10" s="37" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a06972156308</t>
         </is>
@@ -5802,7 +6166,7 @@
           <t>單店活動但形成「展店一週年 = 週年慶」公關節奏。OD 可借鑑：門市開幕一週年也可推出敘事活動</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I11" s="37" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news</t>
         </is>
@@ -5849,7 +6213,7 @@
           <t>🔥 RIM「取代O牌位置」直接針對OD同類點位；OD 台南需強化年輕客群溝通與門市體驗差異化</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I12" s="37" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a0ec678a39d4</t>
         </is>
@@ -5896,7 +6260,7 @@
           <t>JINS 為 SUMMER SALE 墨鏡訴求鋪墊調光鏡片內容；OD 調光/墨鏡內容可同步出</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I13" s="37" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a0be91f59561</t>
         </is>
@@ -5943,7 +6307,7 @@
           <t>🔥 眼鏡市場展店突破，自中部南下嘉義（眼鏡市場嘉義首店）。OD 嘉義門市需應對開幕競爭</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I14" s="37" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/180</t>
         </is>
@@ -5990,7 +6354,7 @@
           <t>IP聯名持續是競品獲客手法，OD 可評估 IP 合作切入年輕客群</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I15" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/dan-da-dan</t>
         </is>
@@ -6037,7 +6401,7 @@
           <t>👀 競品高折射率(1.76)鏡片退場 — OD 可強化高折射率/高階鏡片供應穩定度與保固敘事，承接JINS流失的高度數客群</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I16" s="37" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a018c67c248d</t>
         </is>
@@ -6084,7 +6448,7 @@
           <t>IP聯名持續是競品獲客主力(DAN DA DAN→Solo Leveling)，OD可評估IP切入年輕客群</t>
         </is>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I17" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/klassic-solo-leveling</t>
         </is>
@@ -6131,7 +6495,7 @@
           <t>JINS 強化EC檔期經營；OD官網618/年中檔期敘事可同步</t>
         </is>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="I18" s="37" t="inlineStr">
         <is>
           <t>http://www.jins.com/tw/news/news-6a18f3b36de34</t>
         </is>
@@ -6178,7 +6542,7 @@
           <t>🔥 JINS百店後展店未停步（101間）。OD高雄門市需留意6/11開幕檔期促銷與客流</t>
         </is>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="I19" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/stores</t>
         </is>
@@ -6186,6 +6550,26 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -6290,7 +6674,7 @@
           <t>2026/03/17</t>
         </is>
       </c>
-      <c r="H2" s="21" t="inlineStr">
+      <c r="H2" s="36" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69b124cc4fbd9</t>
         </is>
@@ -6337,7 +6721,7 @@
           <t>2026/03/25</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="37" t="inlineStr">
         <is>
           <t>https://meganeichiba.com.tw/news/173</t>
         </is>
@@ -6384,7 +6768,7 @@
           <t>2026/03/26</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="37" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
@@ -6431,7 +6815,7 @@
           <t>2026/04/10</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news</t>
         </is>
@@ -6478,7 +6862,7 @@
           <t>2026/04/02</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69ca367f3b199</t>
         </is>
@@ -6720,7 +7104,7 @@
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69e99f98417bf</t>
         </is>
@@ -6767,7 +7151,7 @@
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-69e99fe247353</t>
         </is>
@@ -6908,7 +7292,7 @@
           <t>2026/05/29</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H16" s="37" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/180</t>
         </is>
@@ -7049,7 +7433,7 @@
           <t>2026/06/11</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H19" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/stores（門市頁6/8上架，店名註記6/11盛大開幕）</t>
         </is>
@@ -7078,12 +7462,12 @@
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>台南門市 -1（店名待確認）</t>
+          <t>KlassiC. 台南新光三越中山店（關閉/撤櫃）</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>台南 新光三越中山店</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
@@ -7096,19 +7480,31 @@
           <t>2026/06/08發現</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>https://www.klassicglobal.com/pages/stores</t>
+      <c r="H20" s="37" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores ＋ https://www.skm.com.tw/brand/3219（新光三越 KlassiC 專櫃頁台南僅剩新天地5F+小北門2F，中山店已不在列）</t>
         </is>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
-          <t>官網門市頁台南由3間減為2間（剩新光三越小北門店、新光新天地店），下次更新覆核</t>
+          <t>Klassic 台南 3→2（剩小北門、新天地），新光中山店撤櫃。Klassic 全台 20→19，4月快速展店後首見收縮。OD 台南門市可留意此商圈競爭減弱</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId10"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -7121,7 +7517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -7129,6 +7525,7 @@
     <col width="12" customWidth="1" style="17" min="3" max="4"/>
     <col width="10" customWidth="1" style="17" min="5" max="5"/>
     <col width="30" customWidth="1" style="17" min="6" max="6"/>
+    <col width="42" customWidth="1" style="18" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="18">
@@ -7162,6 +7559,11 @@
           <t>異動說明</t>
         </is>
       </c>
+      <c r="G1" s="39" t="inlineStr">
+        <is>
+          <t>來源連結</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="18">
       <c r="A2" s="26" t="inlineStr">
@@ -7190,6 +7592,11 @@
           <t>全台78間</t>
         </is>
       </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="18">
       <c r="A3" s="26" t="inlineStr">
@@ -7218,6 +7625,11 @@
           <t>台南 MITSUI OUTLET PARK 3/17開幕</t>
         </is>
       </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="26" t="inlineStr">
@@ -7246,6 +7658,11 @@
           <t>台南南紡購物中心店 3/25開幕</t>
         </is>
       </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="26" t="inlineStr">
@@ -7274,6 +7691,11 @@
           <t>維持18間（含SON&amp;SUN副牌）</t>
         </is>
       </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="17" t="inlineStr">
@@ -7302,6 +7724,11 @@
           <t>全台78間</t>
         </is>
       </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="18">
       <c r="A7" s="17" t="inlineStr">
@@ -7330,6 +7757,11 @@
           <t>全台94間（含RIM），較上次+3（可能為上次未完整掃描）</t>
         </is>
       </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="18">
       <c r="A8" s="17" t="inlineStr">
@@ -7358,6 +7790,11 @@
           <t>維持35間，南紡購物中心店今日開幕已計入上週</t>
         </is>
       </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="18">
       <c r="A9" s="17" t="inlineStr">
@@ -7386,6 +7823,11 @@
           <t>全台17間（含SON&amp;SUN, Room 41-21），較前次少1間待確認</t>
         </is>
       </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="18">
       <c r="A10" s="17" t="inlineStr">
@@ -7414,6 +7856,11 @@
           <t>全台78間，本週無異動</t>
         </is>
       </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="18">
       <c r="A11" s="17" t="inlineStr">
@@ -7442,6 +7889,11 @@
           <t>本週抓取90間；上週記錄94間（含RIM口徑差異，下週確認）</t>
         </is>
       </c>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="18">
       <c r="A12" s="17" t="inlineStr">
@@ -7470,6 +7922,11 @@
           <t>維持35間，南紡開幕已計入</t>
         </is>
       </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="18">
       <c r="A13" s="17" t="inlineStr">
@@ -7498,6 +7955,11 @@
           <t>Klassic本週抓取確認16間，較上次17間減少1</t>
         </is>
       </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="18">
       <c r="A14" s="17" t="inlineStr">
@@ -7524,6 +7986,11 @@
           <t>全台78間，本週無異動</t>
         </is>
       </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="18">
       <c r="A15" s="17" t="inlineStr">
@@ -7550,6 +8017,11 @@
           <t>JINS 90 + RIM 4 = 94間，本週無異動。2026年Q1已新開3店（東湖、樹林、台南MITSUI）</t>
         </is>
       </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="18">
       <c r="A16" s="17" t="inlineStr">
@@ -7576,6 +8048,11 @@
           <t>維持35間，本週無異動</t>
         </is>
       </c>
+      <c r="G16" s="40" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="18">
       <c r="A17" s="17" t="inlineStr">
@@ -7602,6 +8079,11 @@
           <t>維持17間（含SON&amp;SUN, Room 41-21），本週無異動</t>
         </is>
       </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
@@ -7630,6 +8112,11 @@
           <t>全台78間，維持不變</t>
         </is>
       </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
@@ -7658,6 +8145,11 @@
           <t>南港中信店4/2開幕 + 漢神洲際購物廣場店4/10開幕（JINS 92+RIM 4=96間）</t>
         </is>
       </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
@@ -7686,6 +8178,11 @@
           <t>維持35間</t>
         </is>
       </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
@@ -7714,6 +8211,11 @@
           <t>維持17間</t>
         </is>
       </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
@@ -7746,6 +8248,11 @@
           <t>全台78間（±0）</t>
         </is>
       </c>
+      <c r="G22" s="40" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
@@ -7774,6 +8281,11 @@
           <t>全台JINS 94+RIM 4=98（+2 vs W16）。Chrome實地抓取確認台北+1、台中漢神洲際+1</t>
         </is>
       </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
@@ -7806,6 +8318,11 @@
           <t>全台35間（±0）</t>
         </is>
       </c>
+      <c r="G24" s="40" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
@@ -7834,6 +8351,11 @@
           <t>全台20間（+3）。新增：敦南旗艦店、西門誠品店（台北+2）、文心秀泰店（台中+1）。Chrome實地抓取確認</t>
         </is>
       </c>
+      <c r="G25" s="40" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
@@ -7862,6 +8384,11 @@
           <t>全台78間（±0）</t>
         </is>
       </c>
+      <c r="G26" s="40" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
@@ -7890,6 +8417,11 @@
           <t>全台JINS 94+RIM 4=98（±0 vs W17）。Chrome實地抓取確認，無新增/關閉</t>
         </is>
       </c>
+      <c r="G27" s="40" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
@@ -7918,6 +8450,11 @@
           <t>全台35間（±0）。Chrome實地抓取確認，無異動</t>
         </is>
       </c>
+      <c r="G28" s="40" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
@@ -7946,6 +8483,11 @@
           <t>全台20間（±0 vs W17）。W17新增3店後進入消化期，本週官網門市頁無變化</t>
         </is>
       </c>
+      <c r="G29" s="40" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
@@ -7974,6 +8516,11 @@
           <t>全台78間（±0）</t>
         </is>
       </c>
+      <c r="G30" s="40" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
@@ -8002,6 +8549,11 @@
           <t>Chrome實地抓取：北60+中17+南21+東2=100。新增 JINS楊梅梅獅店(4/30開幕,桃園)+RIM FOCUS時尚流行館店(4/30開幕,台南)。預公告中,4/30前開幕。JINS 95 + RIM 5</t>
         </is>
       </c>
+      <c r="G31" s="40" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
@@ -8030,6 +8582,11 @@
           <t>Chrome實地抓取：全台35間（±0）。新北5/桃園4/宜蘭1/新竹3/台北6/台中7/彰化1/台南3/高雄5</t>
         </is>
       </c>
+      <c r="G32" s="40" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
@@ -8058,6 +8615,11 @@
           <t>Chrome實地抓取：全台20間（±0）</t>
         </is>
       </c>
+      <c r="G33" s="40" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
@@ -8086,6 +8648,11 @@
           <t>全台78間（±0）</t>
         </is>
       </c>
+      <c r="G34" s="40" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
@@ -8114,6 +8681,11 @@
           <t>Chrome 實地抓取：北60+中17+南21+東2=100。JINS 95 + RIM 5（±0 vs W19）。本週無新店公告（最新 news 仍為 4/23 雙店預告）</t>
         </is>
       </c>
+      <c r="G35" s="40" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
@@ -8142,6 +8714,11 @@
           <t>Chrome 實地抓取：全台35間（±0 vs W19）。本週無新店公告，最新 news 為 4/24 太陽眼鏡優惠</t>
         </is>
       </c>
+      <c r="G36" s="40" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
@@ -8170,6 +8747,11 @@
           <t>Chrome 實地抓取：全台20間（±0 vs W19）。注意：新增 AKILA 系列商品線（$6,580起，多款 OPTIC/SUNGLASS）— 本週新觀察</t>
         </is>
       </c>
+      <c r="G37" s="40" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
@@ -8198,6 +8780,11 @@
           <t>全台78間（±0）</t>
         </is>
       </c>
+      <c r="G38" s="40" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
@@ -8226,6 +8813,11 @@
           <t>W22 公開資料校正：JINS 5/8 召開百店記者會，正式宣布在台100間（JINS 95+RIM 5）。為在台最快達成百店規模的日系品牌。本週無新增門市公告（±0 vs W21）。註：本週 Chrome 自動排程未連線，門市計數沿用 W21 並交叉確認 JINS 官網百店公告</t>
         </is>
       </c>
+      <c r="G39" s="40" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
@@ -8254,6 +8846,11 @@
           <t>全台35間（±0 vs W21）。5/15 環球板橋+家樂福彰化店啟動一週年祭限定優惠，無新增門市</t>
         </is>
       </c>
+      <c r="G40" s="40" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
@@ -8282,6 +8879,11 @@
           <t>全台20間（±0 vs W21）。AKILA 系列與輕行者摺疊墨鏡持續推廣，新增 X mEltEd potato 0度抗藍光無框眼鏡 NT$3,680</t>
         </is>
       </c>
+      <c r="G41" s="40" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
@@ -8308,6 +8910,11 @@
           <t>全台78間（±0）</t>
         </is>
       </c>
+      <c r="G42" s="40" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="inlineStr">
@@ -8334,6 +8941,11 @@
           <t>全台100間（JINS 95+RIM 5，±0 vs W22）。RIM 台南FOCUS 5/21 推22色彩色鏡片行銷，門市數維持</t>
         </is>
       </c>
+      <c r="G43" s="40" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
@@ -8362,6 +8974,11 @@
           <t>大全聯嘉義店 5/29(五)開幕（眼鏡市場嘉義首店），全台達36間</t>
         </is>
       </c>
+      <c r="G44" s="40" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
@@ -8388,6 +9005,11 @@
           <t>全台20間（±0 vs W22）。archi by KlassiC. 微建築系列 + x DAN DA DAN 膽大黨聯名主打</t>
         </is>
       </c>
+      <c r="G45" s="40" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
@@ -8416,6 +9038,11 @@
           <t>全台80間（校正補列：新店家樂福店/新北 + 潮州車站店/屏東，先前漏算；非本週新開）</t>
         </is>
       </c>
+      <c r="G46" s="40" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
@@ -8442,6 +9069,11 @@
           <t>全台100間（JINS 95+RIM 5，±0 vs W23）。永和比漾廣場店 6/1 改裝移櫃至5F（非新增門市）；618年中慶啟動</t>
         </is>
       </c>
+      <c r="G47" s="40" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
@@ -8468,6 +9100,11 @@
           <t>全台36間（±0 vs W23）。嘉義店已於5/29計入；本週推 2026 SUMMER SALE 第二副折300</t>
         </is>
       </c>
+      <c r="G48" s="40" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
@@ -8494,6 +9131,11 @@
           <t>全台20間（±0 vs W23）。新上架「我獨自升級 Solo Leveling」動漫聯名系列（鏡框/摺疊墨鏡/周邊）</t>
         </is>
       </c>
+      <c r="G49" s="40" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
@@ -8520,6 +9162,11 @@
           <t>全台80間（±0）</t>
         </is>
       </c>
+      <c r="G50" s="40" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
@@ -8546,6 +9193,11 @@
           <t>全台100間（JINS 95+RIM 5，±0 vs 6/1）。本週推台北市民配鏡現折$300地域促銷</t>
         </is>
       </c>
+      <c r="G51" s="40" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="17" t="inlineStr">
@@ -8572,6 +9224,11 @@
           <t>全台36間（±0）。年中慶 6/1 接檔 SUMMER SALE</t>
         </is>
       </c>
+      <c r="G52" s="40" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
@@ -8598,6 +9255,11 @@
           <t>全台20間（±0）。Solo Leveling 滿額贈盲卡包 + 摺疊墨鏡2件85折</t>
         </is>
       </c>
+      <c r="G53" s="40" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="17" t="inlineStr">
@@ -8630,6 +9292,11 @@
           <t>全台80間（±0）</t>
         </is>
       </c>
+      <c r="G54" s="40" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="inlineStr">
@@ -8662,6 +9329,11 @@
           <t>🔥 JINS 高雄大遠百店 6/11 盛大開幕（官網門市頁 6/8 已上架）。JINS 96+RIM 5=101，高雄 9→10</t>
         </is>
       </c>
+      <c r="G55" s="40" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
@@ -8694,6 +9366,11 @@
           <t>全台36間（±0）。年中慶（太陽眼鏡最高5折）持續，無新店公告</t>
         </is>
       </c>
+      <c r="G56" s="40" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
@@ -8723,11 +9400,74 @@
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>⚠️ 官網門市頁本週列19間：台南 3→2（僅剩小北門+新天地），疑似關閉/下架1間，店名待確認</t>
+          <t>全台19間（-1）。台南新光三越中山店撤櫃（台南3→2，剩小北門+新天地），經 klassicglobal.com/pages/stores 與 skm.com.tw/brand/3219 交叉確認</t>
+        </is>
+      </c>
+      <c r="G57" s="40" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId56"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -8740,7 +9480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -8749,6 +9489,9 @@
     <col width="12" customWidth="1" style="17" min="4" max="4"/>
     <col width="30" customWidth="1" style="17" min="5" max="5"/>
     <col width="12" customWidth="1" style="17" min="6" max="6"/>
+    <col width="14" customWidth="1" style="18" min="7" max="7"/>
+    <col width="16" customWidth="1" style="18" min="8" max="8"/>
+    <col width="12" customWidth="1" style="18" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="18">
@@ -8782,6 +9525,11 @@
           <t>負責追蹤人</t>
         </is>
       </c>
+      <c r="G1" s="39" t="inlineStr">
+        <is>
+          <t>來源連結</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="23.85" customHeight="1" s="18">
       <c r="A2" s="21" t="inlineStr">
@@ -8814,6 +9562,21 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H2" s="40" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I2" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="18">
       <c r="A3" s="17" t="inlineStr">
@@ -8836,6 +9599,21 @@
           <t>南部市場競爭加劇（Jins台南MITSUI+眼鏡市場南紡同期開店）、Jins ESG回收活動為獲客新策略</t>
         </is>
       </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H3" s="40" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I3" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="17" t="inlineStr">
@@ -8866,6 +9644,21 @@
       <c r="F4" s="17" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H4" s="40" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I4" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
         </is>
       </c>
     </row>
@@ -8903,6 +9696,21 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H5" s="40" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I5" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
@@ -8938,6 +9746,21 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H6" s="40" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I6" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
@@ -8970,6 +9793,21 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H7" s="40" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I7" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
@@ -9000,6 +9838,21 @@
       <c r="F8" s="17" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H8" s="40" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I8" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
         </is>
       </c>
     </row>
@@ -9034,6 +9887,21 @@
       <c r="F9" s="17" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H9" s="40" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I9" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
         </is>
       </c>
     </row>
@@ -9071,6 +9939,21 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H10" s="40" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I10" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
@@ -9106,6 +9989,21 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H11" s="40" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I11" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
@@ -9141,6 +10039,21 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H12" s="40" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I12" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
@@ -9171,6 +10084,21 @@
       <c r="F13" s="17" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H13" s="40" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I13" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
         </is>
       </c>
     </row>
@@ -9209,6 +10137,21 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H14" s="40" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I14" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
@@ -9244,6 +10187,21 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H15" s="40" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I15" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -9258,9 +10216,9 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>1. 🔥 JINS 高雄大遠百店 6/11 開幕（高雄+1，全台101間，百店後展店續行）
-2. 🆕 JINS 雙IP/分眾新品齊發：Barbie聯名墨鏡 + 堀米雄斗運動系列
-3. ⚠️ Klassic 官網門市頁 20→19（台南-1，疑似關店待確認）；眼鏡市場年中慶太陽眼鏡5折持續</t>
+          <t>1. 🔥 JINS 高雄大遠百店 6/11 開幕（高雄+1，全台101間）
+2. 🆕 JINS 4 新活動：Barbie聯名墨鏡／堀米雄斗運動系列／週末買2支$666(6/5-6/7,6/12-6/14,6/19-6/21)／台北市民現折$300(6/1-30)
+3. ⚠️ Klassic 台南新光中山店撤櫃(20→19)；眼鏡市場 vs 6/1 無新動態(年中慶太陽眼鏡5折持續)</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
@@ -9278,8 +10236,70 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G16" s="40" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H16" s="40" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I16" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId45"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -9292,7 +10312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -9819,7 +10839,53 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>資料來源</t>
+        </is>
+      </c>
+      <c r="B23" s="40" t="inlineStr">
+        <is>
+          <t>OWNDAYS 門市</t>
+        </is>
+      </c>
+      <c r="C23" s="40" t="inlineStr">
+        <is>
+          <t>JINS 門市</t>
+        </is>
+      </c>
+      <c r="D23" s="40" t="inlineStr">
+        <is>
+          <t>眼鏡市場 門市</t>
+        </is>
+      </c>
+      <c r="E23" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC 門市</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>台南中山店撤櫃交叉確認</t>
+        </is>
+      </c>
+      <c r="B24" s="40" t="inlineStr">
+        <is>
+          <t>新光三越 KlassiC 專櫃頁</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId5"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -4721,6 +4721,207 @@
       <c r="M64" s="37" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/182</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>開幕促銷</t>
+        </is>
+      </c>
+      <c r="D65" s="17" t="inlineStr">
+        <is>
+          <t>RIM FOCUS時尚流行館店(台南) 開幕慶：限定款鏡框配到好$980起</t>
+        </is>
+      </c>
+      <c r="E65" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/10</t>
+        </is>
+      </c>
+      <c r="F65" s="17" t="inlineStr">
+        <is>
+          <t>數量有限為止</t>
+        </is>
+      </c>
+      <c r="G65" s="17" t="inlineStr">
+        <is>
+          <t>RIM BY JINS FOCUS時尚流行館店歡慶開幕，限定款鏡框配到好$980元起（光澤板料/方框圓框/多配色），數量有限</t>
+        </is>
+      </c>
+      <c r="H65" s="17" t="inlineStr">
+        <is>
+          <t>限定款配到好$980起</t>
+        </is>
+      </c>
+      <c r="I65" s="17" t="inlineStr">
+        <is>
+          <t>RIM 台南FOCUS店</t>
+        </is>
+      </c>
+      <c r="J65" s="17" t="inlineStr">
+        <is>
+          <t>RIM以$980超低開幕價切入台南年輕客群，遠低於OD最低套餐價格帶，正面價格攻擊</t>
+        </is>
+      </c>
+      <c r="K65" s="17" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="L65" s="17" t="inlineStr">
+        <is>
+          <t>OD台南門市監測FOCUS商圈客流；以鏡片品質/保固對比$980限定款價值差異</t>
+        </is>
+      </c>
+      <c r="M65" s="37" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a291d15e29ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>（無新動態）</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>vs 6/8 無新促銷 — 年中慶（太陽眼鏡最高5折）持續</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>官網news最新仍為6/1年中慶，無新檔期</t>
+        </is>
+      </c>
+      <c r="H66" s="17" t="inlineStr">
+        <is>
+          <t>滿額折+太陽眼鏡最高50% OFF（持續）</t>
+        </is>
+      </c>
+      <c r="I66" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J66" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場連兩次抓取無新動作，夏季主軸維持墨鏡5折</t>
+        </is>
+      </c>
+      <c r="K66" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L66" s="17" t="inlineStr">
+        <is>
+          <t>OD夏季墨鏡持續對標</t>
+        </is>
+      </c>
+      <c r="M66" s="37" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>（無新動態）</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t>vs 6/8 無新促銷 — Solo Leveling聯名+SALE專區三項加碼持續</t>
+        </is>
+      </c>
+      <c r="E67" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="F67" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="inlineStr">
+        <is>
+          <t>新品/SALE專區內容與6/8相同（LOVA/BELLA 9折、DAN DA DAN組合、輕行者$1,980擴款）</t>
+        </is>
+      </c>
+      <c r="H67" s="17" t="inlineStr">
+        <is>
+          <t>同6/8</t>
+        </is>
+      </c>
+      <c r="I67" s="17" t="inlineStr">
+        <is>
+          <t>全通路</t>
+        </is>
+      </c>
+      <c r="J67" s="17" t="inlineStr">
+        <is>
+          <t>Klassic本次無新動作</t>
+        </is>
+      </c>
+      <c r="K67" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低</t>
+        </is>
+      </c>
+      <c r="L67" s="17" t="inlineStr">
+        <is>
+          <t>觀察</t>
+        </is>
+      </c>
+      <c r="M67" s="37" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/sale</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -7488,6 +7689,53 @@
       <c r="I20" s="17" t="inlineStr">
         <is>
           <t>Klassic 台南 3→2（剩小北門、新天地），新光中山店撤櫃。Klassic 全台 20→19，4月快速展店後首見收縮。OD 台南門市可留意此商圈競爭減弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>正式開幕（追蹤確認）</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>JINS 高雄大遠百店（今日開幕）</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>高雄市 大遠百</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>南部</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="H21" s="37" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a28b6da0b140</t>
+        </is>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>6/8預公告之高雄大遠百店今日正式開幕（高雄第10間，全台101）。開幕疊加SUMMER SALE 8折+週末買2支折$666(6/12-14)，OD高雄門市本週末為客流觀測關鍵窗口</t>
         </is>
       </c>
     </row>
@@ -7517,7 +7765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -9404,6 +9652,154 @@
         </is>
       </c>
       <c r="G57" s="40" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E58" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0）</t>
+        </is>
+      </c>
+      <c r="G58" s="40" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D59" s="17" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E59" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>全台101間（±0，JINS 96+RIM 5）。高雄大遠百店今日(6/11)正式開幕（6/8已計入）；RIM FOCUS時尚流行館店(台南)6/10起開幕慶</t>
+        </is>
+      </c>
+      <c r="G59" s="40" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>全台36間（±0）。官網news最新仍為6/1年中慶，無新店/新檔期</t>
+        </is>
+      </c>
+      <c r="G60" s="40" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D61" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E61" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>全台19間（±0）。台北8/桃園1/新竹1/台中4/台南2/高雄3</t>
+        </is>
+      </c>
+      <c r="G61" s="40" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
@@ -9480,7 +9876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -10247,6 +10643,56 @@
         </is>
       </c>
       <c r="I16" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>W25-週四</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/11（週四更新）</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>1. 🔥 JINS 高雄大遠百店今日(6/11)正式開幕，週末接買2支折$666(6/12-14)
+2. 🆕 RIM FOCUS時尚流行館店(台南)開幕慶：限定款配到好$980起(6/10，數量有限)
+3. 眼鏡市場/Klassic 無新動態（年中慶太陽眼鏡5折、Solo Leveling聯名持續）
+門市數：OD 80 / Jins 101 / 眼鏡 36 / KC 19 = 236間（±0 vs 6/8）</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>🟠 中→高（無展店異動，但JINS高雄開幕日+RIM $980開幕價屬區域性高強度攻擊）</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>(a) OD高雄門市6/11-6/14開幕週末客流監測 (b) OD台南門市對RIM $980開幕價：強調驗光服務/鏡片等級/保固價值差 (c) 持續監看眼鏡市場年中慶是否6月中接新檔</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H17" s="40" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I17" s="40" t="inlineStr">
         <is>
           <t>KlassiC</t>
         </is>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -4920,6 +4920,207 @@
         </is>
       </c>
       <c r="M67" s="37" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>促銷加碼</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>週末買2支眼鏡或墨鏡現折$777</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026/06/11</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>週末限定</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>雙副促銷由$666加碼至$777，週末武器再升級</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>買2支現折$777</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>JINS雙副折扣加碼（$666→$777），持續主打多副入手對標OD</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>OD套餐「一價全包」對標JINS雙副實付價</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a2a6c4172cc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>開幕（展店）</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>屏東店6/18開幕</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026/06/12</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026/06/18起</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>眼鏡市場屏東店6/18(四)開幕，首度進駐屏東</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>開幕（門市展店）</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>屏東</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>眼鏡市場展店切入屏東，直接進入OD屏東地盤（OD原有2間）</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>OD屏東門市留意6/18開幕客流，強化在地服務與套餐價值</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>（延續）</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>夏季摺疊墨鏡兩件85折＋聯名滿額贈</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>優惠專區：輕行者摺疊墨鏡系列兩件85折、我獨自升級滿額贈盲卡包、DAN DA DAN滿額贈周邊</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>摺疊墨鏡買2件85折</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>全通路</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Klassic夏季主打摺疊墨鏡組合折扣＋IP聯名滿額贈，無新展店</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>🟢 低</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>觀察</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/categories/sale</t>
         </is>
@@ -6783,7 +6984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -7736,6 +7937,53 @@
       <c r="I21" s="17" t="inlineStr">
         <is>
           <t>6/8預公告之高雄大遠百店今日正式開幕（高雄第10間，全台101）。開幕疊加SUMMER SALE 8折+週末買2支折$666(6/12-14)，OD高雄門市本週末為客流觀測關鍵窗口</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026/06/12</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>新開店（預公告）</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>眼鏡市場屏東店</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>屏東</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>南部</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location（news 6/12公告，location已上架）</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>眼鏡市場首度進駐屏東（全台37間）。屏東原僅OWNDAYS 2間，眼鏡市場6/18切入；OD屏東門市需留意開幕客流</t>
         </is>
       </c>
     </row>
@@ -7765,7 +8013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -9800,6 +10048,154 @@
         </is>
       </c>
       <c r="G61" s="40" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>全台80間（±0）</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>全台101間（±0，JINS 96+RIM 5）。高雄大遠百已開幕計入，news無新店；週末買2支現折加碼至$777</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>🔥 屏東店6/18(四)開幕，官網location已上架，眼鏡市場首度進駐屏東</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>全台19間（±0）。台北8/桃園1/新竹1/台中4/台南2/高雄3（19間逐店核對一致）</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
@@ -9876,7 +10272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -10693,6 +11089,55 @@
         </is>
       </c>
       <c r="I17" s="40" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>W26-週一</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026/06/15（週一更新）</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1. 🔥 眼鏡市場屏東店6/18(四)開幕，首度進駐屏東（眼鏡市場36→37，全台237間）
+2. 🆕 JINS 週末買2支現折$777（6/11加碼，較前波$666再升級）
+3. Klassic無展店異動(19間)，夏季摺疊墨鏡2件85折+我獨自升級/DAN DA DAN滿額贈持續</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>🔴 高（眼鏡市場首度展店屏東直插OD地盤；JINS雙副促銷加碼）</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>(a) OD屏東門市留意眼鏡市場6/18開幕客流，強化在地服務 (b) OD套餐一價全包對標JINS買2支$777雙副實付價 (c) 持續監看眼鏡市場年中慶是否6月中接新檔</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>KlassiC</t>
         </is>
@@ -10773,7 +11218,7 @@
       </c>
       <c r="B1" s="17" t="inlineStr">
         <is>
-          <t>2026/06/08</t>
+          <t>2026/06/15</t>
         </is>
       </c>
     </row>
@@ -11138,14 +11583,14 @@
         </is>
       </c>
       <c r="D16" s="32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11716,7 @@
       </c>
       <c r="D21" s="34" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E21" s="34" t="inlineStr">
@@ -11281,7 +11726,7 @@
       </c>
       <c r="F21" s="34" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>237</t>
         </is>
       </c>
     </row>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -4926,203 +4926,404 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="17" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="17" t="inlineStr">
         <is>
           <t>促銷加碼</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="17" t="inlineStr">
         <is>
           <t>週末買2支眼鏡或墨鏡現折$777</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="17" t="inlineStr">
         <is>
           <t>2026/06/11</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="17" t="inlineStr">
         <is>
           <t>週末限定</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="17" t="inlineStr">
         <is>
           <t>雙副促銷由$666加碼至$777，週末武器再升級</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H68" s="17" t="inlineStr">
         <is>
           <t>買2支現折$777</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I68" s="17" t="inlineStr">
         <is>
           <t>全台門市</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J68" s="17" t="inlineStr">
         <is>
           <t>JINS雙副折扣加碼（$666→$777），持續主打多副入手對標OD</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K68" s="17" t="inlineStr">
         <is>
           <t>⚠️ 中</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="L68" s="17" t="inlineStr">
         <is>
           <t>OD套餐「一價全包」對標JINS雙副實付價</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="M68" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-6a2a6c4172cc7</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="17" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="17" t="inlineStr">
         <is>
           <t>開幕（展店）</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
         <is>
           <t>屏東店6/18開幕</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="17" t="inlineStr">
         <is>
           <t>2026/06/12</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="17" t="inlineStr">
         <is>
           <t>2026/06/18起</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場屏東店6/18(四)開幕，首度進駐屏東</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" s="17" t="inlineStr">
         <is>
           <t>開幕（門市展店）</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I69" s="17" t="inlineStr">
         <is>
           <t>屏東</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J69" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場展店切入屏東，直接進入OD屏東地盤（OD原有2間）</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="K69" s="17" t="inlineStr">
         <is>
           <t>🔴 高</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="L69" s="17" t="inlineStr">
         <is>
           <t>OD屏東門市留意6/18開幕客流，強化在地服務與套餐價值</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="M69" s="17" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="17" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="17" t="inlineStr">
         <is>
           <t>Klassic</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="17" t="inlineStr">
         <is>
           <t>（延續）</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="17" t="inlineStr">
         <is>
           <t>夏季摺疊墨鏡兩件85折＋聯名滿額贈</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="17" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" s="17" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="17" t="inlineStr">
         <is>
           <t>優惠專區：輕行者摺疊墨鏡系列兩件85折、我獨自升級滿額贈盲卡包、DAN DA DAN滿額贈周邊</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H70" s="17" t="inlineStr">
         <is>
           <t>摺疊墨鏡買2件85折</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I70" s="17" t="inlineStr">
         <is>
           <t>全通路</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J70" s="17" t="inlineStr">
         <is>
           <t>Klassic夏季主打摺疊墨鏡組合折扣＋IP聯名滿額贈，無新展店</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="K70" s="17" t="inlineStr">
         <is>
           <t>🟢 低</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="L70" s="17" t="inlineStr">
         <is>
           <t>觀察</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="M70" s="17" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/categories/sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C71" s="17" t="inlineStr">
+        <is>
+          <t>年中慶（延續+展店同步）</t>
+        </is>
+      </c>
+      <c r="D71" s="17" t="inlineStr">
+        <is>
+          <t>【年中慶】太陽眼鏡最高5折+滿額折（屏東店開幕同步）</t>
+        </is>
+      </c>
+      <c r="E71" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/06</t>
+        </is>
+      </c>
+      <c r="F71" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="G71" s="17" t="inlineStr">
+        <is>
+          <t>年中慶6/6-6/24進行中；屏東店今日開幕，南部促銷+展店雙引擎</t>
+        </is>
+      </c>
+      <c r="H71" s="17" t="inlineStr">
+        <is>
+          <t>滿額折+指定太陽眼鏡最高50% OFF</t>
+        </is>
+      </c>
+      <c r="I71" s="17" t="inlineStr">
+        <is>
+          <t>全台門市+屏東新店</t>
+        </is>
+      </c>
+      <c r="J71" s="17" t="inlineStr">
+        <is>
+          <t>OD夏季墨鏡須對標眼鏡市場太陽眼鏡5折（6/24截止）；屏東地區疊加開幕效應</t>
+        </is>
+      </c>
+      <c r="K71" s="17" t="inlineStr">
+        <is>
+          <t>🔴 高｜強度4/5</t>
+        </is>
+      </c>
+      <c r="L71" s="17" t="inlineStr">
+        <is>
+          <t>OD屏東門市對標開幕+5折，強化在地服務</t>
+        </is>
+      </c>
+      <c r="M71" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C72" s="17" t="inlineStr">
+        <is>
+          <t>促銷（延續）+公關風險</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>週末買2支現折$777（6/19-21檔）；1.76鏡片台日價差爭議</t>
+        </is>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/21</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>本週末買2支$777延續；同時1.76極薄鏡片台日價差近7倍遭媒體續報（TVBS/Yahoo），JINS稱爭取調價</t>
+        </is>
+      </c>
+      <c r="H72" s="17" t="inlineStr">
+        <is>
+          <t>買2支現折$777</t>
+        </is>
+      </c>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J72" s="17" t="inlineStr">
+        <is>
+          <t>JINS雙副促銷續打；台日價差負面聲量為OD借勢點——強化價格透明/一價全包/在地保固</t>
+        </is>
+      </c>
+      <c r="K72" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中｜強度3/5</t>
+        </is>
+      </c>
+      <c r="L72" s="17" t="inlineStr">
+        <is>
+          <t>OD套餐一價全包對標$777雙副；公關面凸顯價格透明</t>
+        </is>
+      </c>
+      <c r="M72" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C73" s="17" t="inlineStr">
+        <is>
+          <t>618 SALE（延續）</t>
+        </is>
+      </c>
+      <c r="D73" s="17" t="inlineStr">
+        <is>
+          <t>618年中慶：摺疊墨鏡2件85折＋IP聯名滿額贈</t>
+        </is>
+      </c>
+      <c r="E73" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="F73" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G73" s="17" t="inlineStr">
+        <is>
+          <t>618 SALE持續：輕行者摺疊墨鏡2件85折、我獨自升級/DAN DA DAN滿額贈；new arrival擴增聯名(FUTURE FLEX、x Baby Milo、x GQ×Cody Sanderson等)</t>
+        </is>
+      </c>
+      <c r="H73" s="17" t="inlineStr">
+        <is>
+          <t>摺疊墨鏡2件85折</t>
+        </is>
+      </c>
+      <c r="I73" s="17" t="inlineStr">
+        <is>
+          <t>全通路</t>
+        </is>
+      </c>
+      <c r="J73" s="17" t="inlineStr">
+        <is>
+          <t>Klassic無展店，續打摺疊墨鏡+IP聯名年輕客群；對OD直接威脅低</t>
+        </is>
+      </c>
+      <c r="K73" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低｜強度2/5</t>
+        </is>
+      </c>
+      <c r="L73" s="17" t="inlineStr">
+        <is>
+          <t>觀察IP聯名年輕客群熱度</t>
+        </is>
+      </c>
+      <c r="M73" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/new-arrival</t>
         </is>
       </c>
     </row>
@@ -6984,7 +7185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -7941,49 +8142,96 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>2026/06/12</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>新開店（預公告）</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場屏東店</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>屏東</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>南部</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="17" t="inlineStr">
         <is>
           <t>2026/06/18</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/location（news 6/12公告，location已上架）</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場首度進駐屏東（全台37間）。屏東原僅OWNDAYS 2間，眼鏡市場6/18切入；OD屏東門市需留意開幕客流</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>正式開幕（追蹤確認）</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場屏東店</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>屏東</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>南部</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news（6/12公告，6/18開幕）／location已上架</t>
+        </is>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場屏東店今日正式開幕，品牌首度進駐屏東（全台37間）。屏東原僅OWNDAYS 2間；OD屏東門市今起為客流觀測關鍵窗口，需強化在地驗光/服務/一價全包敘事</t>
         </is>
       </c>
     </row>
@@ -8013,7 +8261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -10054,148 +10302,296 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="17" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="17" t="inlineStr">
         <is>
           <t>OWNDAYS</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="17" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="17" t="inlineStr">
         <is>
           <t>全台80間（±0）</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="17" t="inlineStr">
         <is>
           <t>https://www.owndays.com/tw/zh_tw/shops</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="17" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="17" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="17" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="17" t="inlineStr">
         <is>
           <t>全台101間（±0，JINS 96+RIM 5）。高雄大遠百已開幕計入，news無新店；週末買2支現折加碼至$777</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/stores</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="17" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="17" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="17" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="17" t="inlineStr">
         <is>
           <t>🔥 屏東店6/18(四)開幕，官網location已上架，眼鏡市場首度進駐屏東</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="17" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/location</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="17" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="17" t="inlineStr">
         <is>
           <t>Klassic</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="17" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="17" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="17" t="inlineStr">
         <is>
           <t>全台19間（±0）。台北8/桃園1/新竹1/台中4/台南2/高雄3（19間逐店核對一致）</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0）</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E67" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F67" s="17" t="inlineStr">
+        <is>
+          <t>全台101間（±0，JINS 96+RIM 5）。news無新店；本週末6/19-21買2支現折$777檔；1.76極薄鏡片台日價差爭議延燒（媒體續報）</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>🔥屏東店今日6/18(四)正式開幕（首度進駐屏東，門市數6/15已計入）；【年中慶】6/6-6/24持續（太陽眼鏡最高5折）</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D69" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E69" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F69" s="17" t="inlineStr">
+        <is>
+          <t>全台19間（±0）。台北8/桃園1/新竹1/台中4/台南2/高雄3；618 SALE持續</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
@@ -10272,7 +10668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -11095,49 +11491,99 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>W26-週一</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>2026/06/15（週一更新）</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>1. 🔥 眼鏡市場屏東店6/18(四)開幕，首度進駐屏東（眼鏡市場36→37，全台237間）
 2. 🆕 JINS 週末買2支現折$777（6/11加碼，較前波$666再升級）
 3. Klassic無展店異動(19間)，夏季摺疊墨鏡2件85折+我獨自升級/DAN DA DAN滿額贈持續</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>🔴 高（眼鏡市場首度展店屏東直插OD地盤；JINS雙副促銷加碼）</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>(a) OD屏東門市留意眼鏡市場6/18開幕客流，強化在地服務 (b) OD套餐一價全包對標JINS買2支$777雙副實付價 (c) 持續監看眼鏡市場年中慶是否6月中接新檔</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>JINS news</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場 news</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>W26-週四</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/18（週四更新）</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>1. 🔥 眼鏡市場屏東店今日6/18(四)正式開幕 — 品牌首度進駐屏東（門市數6/15已計入37間），直插OD屏東地盤（OD原有2間）
+2. ⚠️ JINS 1.76極薄鏡片「台日價差近7倍」爭議延燒（TVBS/Yahoo續報），JINS稱將爭取調價 — 對JINS品牌負面公關、OD可借勢；本週末6/19-21買2支$777檔持續
+3. 眼鏡市場【年中慶】6/6-6/24（太陽眼鏡最高5折）持續；Klassic 618 SALE摺疊墨鏡2件85折+IP聯名滿額贈持續，無展店
+門市數：OD 80 / Jins 101 / 眼鏡 37 / KC 19 = 237間（±0 vs 6/15）</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>🟠 中→高（屏東店實際開幕直插OD地盤，但門市數已計入；JINS台日價差爭議＝OD借勢窗口）｜本期最高威脅分：眼鏡市場屏東開幕（鄰近×展店權重×高）</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>(a) OD屏東2門市今起客流監測，強化在地驗光/服務與「一價全包」價值溝通 (b) 借勢JINS台日價差爭議，凸顯OD價格透明、一價全包、在地保固 (c) OD夏季墨鏡對標眼鏡市場年中慶太陽眼鏡5折(6/24截止)</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>KlassiC</t>
         </is>
@@ -11218,7 +11664,7 @@
       </c>
       <c r="B1" s="17" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
+          <t>2026/06/18</t>
         </is>
       </c>
     </row>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -5324,6 +5324,408 @@
       <c r="M73" s="17" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/categories/new-arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/21</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>新促銷（暑期學生檔）</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr">
+        <is>
+          <t>暑假學生優惠：憑學生證配鏡現折$300、升級濾藍光再折$100</t>
+        </is>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/21</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>暑假期間</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>鎖定暑假/開學學生族群；JINS啟動季節性學生檔，疊加夏日$777雙副</t>
+        </is>
+      </c>
+      <c r="H74" s="17" t="inlineStr">
+        <is>
+          <t>學生證現折$300＋濾藍光-$100</t>
+        </is>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J74" s="17" t="inlineStr">
+        <is>
+          <t>OD應同步備妥暑期學生/開學方案對標，凸顯一價全包＋免費鏡片升級</t>
+        </is>
+      </c>
+      <c r="K74" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中｜強度3/5</t>
+        </is>
+      </c>
+      <c r="L74" s="17" t="inlineStr">
+        <is>
+          <t>OD搶在開學季前推學生方案（含免費抗藍光升級話術），對標JINS學生檔</t>
+        </is>
+      </c>
+      <c r="M74" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/21</t>
+        </is>
+      </c>
+      <c r="B75" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C75" s="17" t="inlineStr">
+        <is>
+          <t>檔期到期雷達+接檔推估</t>
+        </is>
+      </c>
+      <c r="D75" s="17" t="inlineStr">
+        <is>
+          <t>【年中慶】6/24(三)截止倒數3天；太陽眼鏡最高5折+滿額折</t>
+        </is>
+      </c>
+      <c r="E75" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/06</t>
+        </is>
+      </c>
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="G75" s="17" t="inlineStr">
+        <is>
+          <t>年中慶進入最後一週（6/24截止）。接檔推估：6/24後恐無縫接「暑期/開學檔」延續太陽眼鏡折扣</t>
+        </is>
+      </c>
+      <c r="H75" s="17" t="inlineStr">
+        <is>
+          <t>滿額折+指定太陽眼鏡最高50% OFF</t>
+        </is>
+      </c>
+      <c r="I75" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J75" s="17" t="inlineStr">
+        <is>
+          <t>⏰到期雷達：OD須在6/24截止前後卡位夏季墨鏡，並預判眼鏡市場暑期接檔</t>
+        </is>
+      </c>
+      <c r="K75" s="17" t="inlineStr">
+        <is>
+          <t>🟠 中｜強度4/5</t>
+        </is>
+      </c>
+      <c r="L75" s="17" t="inlineStr">
+        <is>
+          <t>6/24前OD夏季墨鏡強打；6/25起觀察眼鏡市場是否接暑期檔，提前備戰</t>
+        </is>
+      </c>
+      <c r="M75" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/21</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
+        <is>
+          <t>618 SALE（延續）</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>618年中慶延續：摺疊墨鏡2件85折＋IP聯名滿額贈</t>
+        </is>
+      </c>
+      <c r="E76" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G76" s="17" t="inlineStr">
+        <is>
+          <t>618 SALE續打：輕行者摺疊墨鏡2件85折、x我獨自升級/DAN DA DAN滿額贈。無展店</t>
+        </is>
+      </c>
+      <c r="H76" s="17" t="inlineStr">
+        <is>
+          <t>摺疊墨鏡2件85折</t>
+        </is>
+      </c>
+      <c r="I76" s="17" t="inlineStr">
+        <is>
+          <t>全通路</t>
+        </is>
+      </c>
+      <c r="J76" s="17" t="inlineStr">
+        <is>
+          <t>Klassic維持促銷常態、無新動作；IP聯名持續吸年輕客群</t>
+        </is>
+      </c>
+      <c r="K76" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低｜強度2/5</t>
+        </is>
+      </c>
+      <c r="L76" s="17" t="inlineStr">
+        <is>
+          <t>觀察即可</t>
+        </is>
+      </c>
+      <c r="M76" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/new-arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C77" s="17" t="inlineStr">
+        <is>
+          <t>檔期到期雷達+接檔推估</t>
+        </is>
+      </c>
+      <c r="D77" s="17" t="inlineStr">
+        <is>
+          <t>【年中慶】6/24(三)截止倒數2天；太陽眼鏡最高5折+滿額折</t>
+        </is>
+      </c>
+      <c r="E77" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/06</t>
+        </is>
+      </c>
+      <c r="F77" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="G77" s="17" t="inlineStr">
+        <is>
+          <t>年中慶進入最後2天（6/24截止）。接檔推估：高機率無縫接「暑期/開學檔」延續太陽眼鏡折扣（日本母集團6/26多店改裝，台灣端尚無對應）</t>
+        </is>
+      </c>
+      <c r="H77" s="17" t="inlineStr">
+        <is>
+          <t>滿額折+指定太陽眼鏡最高50% OFF</t>
+        </is>
+      </c>
+      <c r="I77" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J77" s="17" t="inlineStr">
+        <is>
+          <t>⏰到期雷達：OD須在6/24截止前後卡位夏季墨鏡，並預判眼鏡市場暑期接檔</t>
+        </is>
+      </c>
+      <c r="K77" s="17" t="inlineStr">
+        <is>
+          <t>🟠 中｜強度4/5</t>
+        </is>
+      </c>
+      <c r="L77" s="17" t="inlineStr">
+        <is>
+          <t>6/24前OD夏季墨鏡強打；6/25起緊盯是否接暑期檔，提前備戰</t>
+        </is>
+      </c>
+      <c r="M77" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
+        <is>
+          <t>促銷（延續·暑期學生檔）</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>暑假學生優惠延續＋夏日節氣新品</t>
+        </is>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/21</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>暑假期間</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="inlineStr">
+        <is>
+          <t>學生證現折$300＋升級濾藍光-$100延續；夏日節氣新品立夏/芒種$2,980持續；news無新展店訊號</t>
+        </is>
+      </c>
+      <c r="H78" s="17" t="inlineStr">
+        <is>
+          <t>學生證現折$300＋濾藍光-$100</t>
+        </is>
+      </c>
+      <c r="I78" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J78" s="17" t="inlineStr">
+        <is>
+          <t>OD維持暑期學生/開學方案對標，凸顯一價全包＋免費鏡片升級（含抗藍光）</t>
+        </is>
+      </c>
+      <c r="K78" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中｜強度3.5/5</t>
+        </is>
+      </c>
+      <c r="L78" s="17" t="inlineStr">
+        <is>
+          <t>OD開學季前持續推學生方案（含免費抗藍光升級話術）</t>
+        </is>
+      </c>
+      <c r="M78" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C79" s="17" t="inlineStr">
+        <is>
+          <t>618 SALE（延續）＋名人聯名</t>
+        </is>
+      </c>
+      <c r="D79" s="17" t="inlineStr">
+        <is>
+          <t>618延續＋坤達Kunda BY KlassiC名人代言聯名浮現</t>
+        </is>
+      </c>
+      <c r="E79" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="F79" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G79" s="17" t="inlineStr">
+        <is>
+          <t>618 SALE摺疊墨鏡2件85折持續；本期浮現「坤達Kunda BY KlassiC」名人代言聯名線（繼DAN DA DAN/我獨自升級IP聯名後加入藝人代言打法）；無展店</t>
+        </is>
+      </c>
+      <c r="H79" s="17" t="inlineStr">
+        <is>
+          <t>摺疊墨鏡2件85折</t>
+        </is>
+      </c>
+      <c r="I79" s="17" t="inlineStr">
+        <is>
+          <t>全通路</t>
+        </is>
+      </c>
+      <c r="J79" s="17" t="inlineStr">
+        <is>
+          <t>Klassic由IP聯名擴及藝人代言；對OD直接威脅低，OD可評估在地藝人/KOL合作</t>
+        </is>
+      </c>
+      <c r="K79" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低｜強度2/5</t>
+        </is>
+      </c>
+      <c r="L79" s="17" t="inlineStr">
+        <is>
+          <t>觀察名人聯名（坤達）年輕客群熱度</t>
+        </is>
+      </c>
+      <c r="M79" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/kunda-oshare</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -6215,6 +6617,63 @@
       <c r="K14" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-6a1ea583854aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/21</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>鏡框新品（夏日系列）</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>夏日系列「立夏」「芒種」</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>2026/06 上架</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>$2,980</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>以節氣為主題的夏日限定款，延續JINS季節性新品節奏</t>
+        </is>
+      </c>
+      <c r="H15" s="17" t="inlineStr">
+        <is>
+          <t>全客群/年輕族群</t>
+        </is>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="17" t="inlineStr">
+        <is>
+          <t>JINS持續以節氣/季節主題快速翻新產品線，OD可評估季節限定敘事</t>
+        </is>
+      </c>
+      <c r="K15" s="37" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/collections</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -7148,6 +7607,53 @@
       <c r="I19" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>名人代言聯名</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>坤達 Kunda BY KlassiC 聯名眼鏡墨鏡</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>本期浮現藝人坤達（Kunda）代言聯名線，主打年輕精緻設計眼鏡/墨鏡；繼DAN DA DAN、我獨自升級動漫IP聯名後，Klassic加入「藝人代言」獲客打法</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>坤達 Kunda</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>年輕潮流客群/藝人粉絲</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>Klassic獲客手法由動漫IP擴及藝人代言；OD可評估在地藝人/KOL合作切入年輕客群、強化社群聲量</t>
+        </is>
+      </c>
+      <c r="I20" s="37" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/kunda-oshare</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -10592,6 +11098,302 @@
         </is>
       </c>
       <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/21</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0）。新北18、屏東2（已校正）</t>
+        </is>
+      </c>
+      <c r="G70" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/21</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C71" s="17" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D71" s="17" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E71" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F71" s="17" t="inlineStr">
+        <is>
+          <t>全台101間（±0，JINS 96+RIM 5）。news無新展店訊號</t>
+        </is>
+      </c>
+      <c r="G71" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/21</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C72" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>全台37間（±0）。屏東店6/18已開幕計入，本期無新展店</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/21</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C73" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D73" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E73" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F73" s="17" t="inlineStr">
+        <is>
+          <t>全台19間（±0）。沿用6/15逐店核對清單，本期無展店訊號</t>
+        </is>
+      </c>
+      <c r="G73" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0）。新北18、屏東2（已校正）</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B75" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C75" s="17" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D75" s="17" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E75" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>全台101間（±0，JINS 96+RIM 5）。news無新展店訊號（連續第三個±0週）</t>
+        </is>
+      </c>
+      <c r="G75" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E76" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>全台37間（±0）。年中慶6/24截止剩2天；日本母集團6/26多店改裝重開（台灣端無對應動作）</t>
+        </is>
+      </c>
+      <c r="G76" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C77" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D77" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E77" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F77" s="17" t="inlineStr">
+        <is>
+          <t>全台19間（±0）。浮現坤達Kunda名人代言聯名線；618 SALE持續</t>
+        </is>
+      </c>
+      <c r="G77" s="17" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
@@ -10668,7 +11470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -11584,6 +12386,103 @@
         </is>
       </c>
       <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>W26-週日</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/21（週日補跑）</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>1. 🆕 JINS暑假學生優惠（現折$300+濾藍光-$100）啟動暑期檔 2. ⏰ 眼鏡市場年中慶6/24截止倒數、接檔推估暑期檔 3. 🆕 JINS夏日節氣新品「立夏/芒種」$2,980</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低→中（門市數全品牌±0、無展店；以季節性促銷/新品動態為主，威脅分3/5）</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>(a) OD搶開學季前推學生方案(含免費抗藍光升級) (b) 6/24前夏季墨鏡卡位、預判眼鏡市場暑期接檔 (c) 續觀JINS台日價差公關借勢窗口</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>W27-週一</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/22（週一更新）</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>1. ⏰ 眼鏡市場【年中慶】6/24(三)截止剩2天，接檔暑期/開學檔機率高（到期雷達）
+2. 🆕 Klassic浮現名人聯名「坤達 Kunda BY KlassiC」（繼動漫IP聯名後加入藝人代言打法）；618 SALE延續
+3. 🟢 連續第三個±0安靜週（四品牌無展店，全台237間）；本期首度導入「促銷強度8週趨勢圖」視覺化（採顧問建議#4）
+門市數：OD 80 / Jins 101 / 眼鏡 37 / KC 19 = 237間（±0 vs 6/21）</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低→中（門市數全品牌±0、無展店；眼鏡市場年中慶6/24到期為關鍵轉折，威脅分3/5）</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>(a) 6/24前OD夏季墨鏡攔截眼鏡市場太陽眼鏡5折、6/25起緊盯接檔 (b) 開學季前持續推學生方案對標JINS暑期學生檔 (c) 觀察Klassic名人聯名（坤達）年輕客群熱度</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
         <is>
           <t>KlassiC</t>
         </is>
@@ -11664,7 +12563,7 @@
       </c>
       <c r="B1" s="17" t="inlineStr">
         <is>
-          <t>2026/06/18</t>
+          <t>2026/06/22</t>
         </is>
       </c>
     </row>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -5541,32 +5541,32 @@
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>檔期到期雷達+接檔推估</t>
+          <t>年中慶（進行中·檔期依百貨而異）</t>
         </is>
       </c>
       <c r="D77" s="17" t="inlineStr">
         <is>
-          <t>【年中慶】6/24(三)截止倒數2天；太陽眼鏡最高5折+滿額折</t>
+          <t>【年中慶】各百貨檔期時間不一、無統一結束日（更正先前6/24截止之誤）</t>
         </is>
       </c>
       <c r="E77" s="17" t="inlineStr">
         <is>
-          <t>2026/06/06</t>
+          <t>進行中</t>
         </is>
       </c>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>2026/06/24</t>
+          <t>依各百貨</t>
         </is>
       </c>
       <c r="G77" s="17" t="inlineStr">
         <is>
-          <t>年中慶進入最後2天（6/24截止）。接檔推估：高機率無縫接「暑期/開學檔」延續太陽眼鏡折扣（日本母集團6/26多店改裝，台灣端尚無對應）</t>
+          <t>年中慶仍在進行；本期未由官方頁面取得新檔期細節，無單一到期日</t>
         </is>
       </c>
       <c r="H77" s="17" t="inlineStr">
         <is>
-          <t>滿額折+指定太陽眼鏡最高50% OFF</t>
+          <t>依各百貨公告為準</t>
         </is>
       </c>
       <c r="I77" s="17" t="inlineStr">
@@ -5576,17 +5576,17 @@
       </c>
       <c r="J77" s="17" t="inlineStr">
         <is>
-          <t>⏰到期雷達：OD須在6/24截止前後卡位夏季墨鏡，並預判眼鏡市場暑期接檔</t>
+          <t>OD夏季墨鏡持續對標太陽眼鏡折扣，不以單一到期日設定節奏</t>
         </is>
       </c>
       <c r="K77" s="17" t="inlineStr">
         <is>
-          <t>🟠 中｜強度4/5</t>
+          <t>🟡 中｜未獨立核實檔期</t>
         </is>
       </c>
       <c r="L77" s="17" t="inlineStr">
         <is>
-          <t>6/24前OD夏季墨鏡強打；6/25起緊盯是否接暑期檔，提前備戰</t>
+          <t>夏季墨鏡持續卡位；檔期細節以官方公告為準</t>
         </is>
       </c>
       <c r="M77" s="17" t="inlineStr">
@@ -5608,32 +5608,32 @@
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>促銷（延續·暑期學生檔）</t>
+          <t>促銷（本期未確認）</t>
         </is>
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t>暑假學生優惠延續＋夏日節氣新品</t>
+          <t>本期無法由一手來源確認JINS促銷檔期</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>2026/06/21</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>暑假期間</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G78" s="17" t="inlineStr">
         <is>
-          <t>學生證現折$300＋升級濾藍光-$100延續；夏日節氣新品立夏/芒種$2,980持續；news無新展店訊號</t>
+          <t>官網news為JS動態頁、清單未於一般抓取渲染；先前「暑期學生檔」係WebSearch摘要、未經官方頁面證實，已撤除</t>
         </is>
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>學生證現折$300＋濾藍光-$100</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="17" t="inlineStr">
@@ -5643,17 +5643,17 @@
       </c>
       <c r="J78" s="17" t="inlineStr">
         <is>
-          <t>OD維持暑期學生/開學方案對標，凸顯一價全包＋免費鏡片升級（含抗藍光）</t>
+          <t>待以可渲染JS之瀏覽器工具補確認再對標</t>
         </is>
       </c>
       <c r="K78" s="17" t="inlineStr">
         <is>
-          <t>⚠️ 中｜強度3.5/5</t>
+          <t>⚪ 未確認</t>
         </is>
       </c>
       <c r="L78" s="17" t="inlineStr">
         <is>
-          <t>OD開學季前持續推學生方案（含免費抗藍光升級話術）</t>
+          <t>下次以Chrome等可渲染JS工具確認JINS news後再列</t>
         </is>
       </c>
       <c r="M78" s="17" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>618 SALE（延續）＋名人聯名</t>
+          <t>新品上架（已核實）</t>
         </is>
       </c>
       <c r="D79" s="17" t="inlineStr">
         <is>
-          <t>618延續＋坤達Kunda BY KlassiC名人代言聯名浮現</t>
+          <t>官網最新商品：新光學框ALEX/AURA/BAILEY/JAN/ENZO/LIZ＋IP聯名線</t>
         </is>
       </c>
       <c r="E79" s="17" t="inlineStr">
@@ -5695,12 +5695,12 @@
       </c>
       <c r="G79" s="17" t="inlineStr">
         <is>
-          <t>618 SALE摺疊墨鏡2件85折持續；本期浮現「坤達Kunda BY KlassiC」名人代言聯名線（繼DAN DA DAN/我獨自升級IP聯名後加入藝人代言打法）；無展店</t>
+          <t>新光學框$3,580多款上架；IP/聯名持續更新（我獨自升級、mEltEd potato、Baby Milo、BBC×ICECREAM、SUNSHINE HUNTER GAME等）。頁面無「618」字樣、無新墨鏡專案、坤達非現行新品</t>
         </is>
       </c>
       <c r="H79" s="17" t="inlineStr">
         <is>
-          <t>摺疊墨鏡2件85折</t>
+          <t>光學框$3,580起</t>
         </is>
       </c>
       <c r="I79" s="17" t="inlineStr">
@@ -5710,22 +5710,22 @@
       </c>
       <c r="J79" s="17" t="inlineStr">
         <is>
-          <t>Klassic由IP聯名擴及藝人代言；對OD直接威脅低，OD可評估在地藝人/KOL合作</t>
+          <t>Klassic維持高頻新品/IP聯名；OD評估年輕客群聯名/KOL策略</t>
         </is>
       </c>
       <c r="K79" s="17" t="inlineStr">
         <is>
-          <t>🟢 低｜強度2/5</t>
+          <t>🟢 低｜已核實</t>
         </is>
       </c>
       <c r="L79" s="17" t="inlineStr">
         <is>
-          <t>觀察名人聯名（坤達）年輕客群熱度</t>
+          <t>觀察新框與IP聯名年輕客群熱度</t>
         </is>
       </c>
       <c r="M79" s="17" t="inlineStr">
         <is>
-          <t>https://www.klassicglobal.com/pages/kunda-oshare</t>
+          <t>https://www.klassicglobal.com/categories/new-arrival</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -7607,53 +7607,6 @@
       <c r="I19" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/stores</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>2026/06/22</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>Klassic</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>名人代言聯名</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>坤達 Kunda BY KlassiC 聯名眼鏡墨鏡</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>本期浮現藝人坤達（Kunda）代言聯名線，主打年輕精緻設計眼鏡/墨鏡；繼DAN DA DAN、我獨自升級動漫IP聯名後，Klassic加入「藝人代言」獲客打法</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>坤達 Kunda</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>年輕潮流客群/藝人粉絲</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>Klassic獲客手法由動漫IP擴及藝人代言；OD可評估在地藝人/KOL合作切入年輕客群、強化社群聲量</t>
-        </is>
-      </c>
-      <c r="I20" s="37" t="inlineStr">
-        <is>
-          <t>https://www.klassicglobal.com/pages/kunda-oshare</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11269,7 @@
       </c>
       <c r="F75" s="17" t="inlineStr">
         <is>
-          <t>全台101間（±0，JINS 96+RIM 5）。news無新展店訊號（連續第三個±0週）</t>
+          <t>全台101間（±0，JINS 96+RIM 5）。news無新展店；促銷檔期本期未由一手來源確認</t>
         </is>
       </c>
       <c r="G75" s="17" t="inlineStr">
@@ -11353,7 +11306,7 @@
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>全台37間（±0）。年中慶6/24截止剩2天；日本母集團6/26多店改裝重開（台灣端無對應動作）</t>
+          <t>全台37間（±0）。年中慶進行中但各百貨檔期不一、無統一結束日（更正先前6/24截止之誤）</t>
         </is>
       </c>
       <c r="G76" s="17" t="inlineStr">
@@ -11390,7 +11343,7 @@
       </c>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>全台19間（±0）。浮現坤達Kunda名人代言聯名線；618 SALE持續</t>
+          <t>全台19間（±0）。官網新品為光學新框ALEX/AURA等$3,580＋IP聯名線；無618、無坤達於現行新品</t>
         </is>
       </c>
       <c r="G77" s="17" t="inlineStr">
@@ -12451,20 +12404,20 @@
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>1. ⏰ 眼鏡市場【年中慶】6/24(三)截止剩2天，接檔暑期/開學檔機率高（到期雷達）
-2. 🆕 Klassic浮現名人聯名「坤達 Kunda BY KlassiC」（繼動漫IP聯名後加入藝人代言打法）；618 SALE延續
-3. 🟢 連續第三個±0安靜週（四品牌無展店，全台237間）；本期首度導入「促銷強度8週趨勢圖」視覺化（採顧問建議#4）
+          <t>1. 🟢 連續第三個±0安靜週（四品牌無展店，全台237間）
+2. ✅ Klassic官網上架新光學框ALEX/AURA/BAILEY/JAN/ENZO/LIZ（$3,580）＋IP聯名線持續更新（已逐項核實）
+3. ⚠️ 資料校正：先前「眼鏡市場6/24截止」「JINS暑期學生檔」「Klassic 618墨鏡新品」均未能由一手來源證實，本期撤除/更正
 門市數：OD 80 / Jins 101 / 眼鏡 37 / KC 19 = 237間（±0 vs 6/21）</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>🟢 低→中（門市數全品牌±0、無展店；眼鏡市場年中慶6/24到期為關鍵轉折，威脅分3/5）</t>
+          <t>🟢 低（門市數全±0、無展店；本期嚴守一手來源口徑，未確認促銷不臆測，威脅分2/5）</t>
         </is>
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>(a) 6/24前OD夏季墨鏡攔截眼鏡市場太陽眼鏡5折、6/25起緊盯接檔 (b) 開學季前持續推學生方案對標JINS暑期學生檔 (c) 觀察Klassic名人聯名（坤達）年輕客群熱度</t>
+          <t>(a) OD夏季墨鏡持續對標眼鏡市場太陽眼鏡折扣（年中慶檔期依百貨而異、無單一到期日） (b) JINS促銷待以可渲染JS之瀏覽器工具確認後再對標 (c) 觀察Klassic新框與IP聯名年輕客群熱度</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr">

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="門市數量總覽" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每週摘要" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="門市分布（按縣市）" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="促銷到期日曆" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'促銷活動'!$A$1:$M$1</definedName>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -126,8 +127,12 @@
       <color rgb="000563C1"/>
       <u val="single"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -150,6 +155,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD6E4F0"/>
         <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000047BB"/>
       </patternFill>
     </fill>
   </fills>
@@ -188,7 +198,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -306,6 +316,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -585,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -5726,6 +5742,274 @@
       <c r="M79" s="17" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/categories/new-arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
+          <t>促銷（一手確認）</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="inlineStr">
+        <is>
+          <t>指定眼鏡限時8折起</t>
+        </is>
+      </c>
+      <c r="E80" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>官網news確認：5/14(四)-6/30(二)指定眼鏡超殺8折起；線上618年中慶持續</t>
+        </is>
+      </c>
+      <c r="H80" s="17" t="inlineStr">
+        <is>
+          <t>指定眼鏡8折起</t>
+        </is>
+      </c>
+      <c r="I80" s="17" t="inlineStr">
+        <is>
+          <t>全台門市/EC</t>
+        </is>
+      </c>
+      <c r="J80" s="17" t="inlineStr">
+        <is>
+          <t>補回上期JINS促銷未能一手確認之缺口；OD以一價全包＋免費升級對標總價優勢</t>
+        </is>
+      </c>
+      <c r="K80" s="17" t="inlineStr">
+        <is>
+          <t>🟠 中｜強度3/5｜已一手確認</t>
+        </is>
+      </c>
+      <c r="L80" s="17" t="inlineStr">
+        <is>
+          <t>月底前以總價優勢溝通，避免被單純標價折扣稀釋來客</t>
+        </is>
+      </c>
+      <c r="M80" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C81" s="17" t="inlineStr">
+        <is>
+          <t>一週年祭（再加碼）</t>
+        </is>
+      </c>
+      <c r="D81" s="17" t="inlineStr">
+        <is>
+          <t>【一週年祭】環球左營/新光三越高雄左營(雙店同慶)＋經國店</t>
+        </is>
+      </c>
+      <c r="E81" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/23</t>
+        </is>
+      </c>
+      <c r="F81" s="17" t="inlineStr">
+        <is>
+          <t>依門市</t>
+        </is>
+      </c>
+      <c r="G81" s="17" t="inlineStr">
+        <is>
+          <t>6/23新增兩檔一週年祭限定優惠，火力集中南高雄(左營×2)＋經國店；年中慶(太陽眼鏡最高5折)+夏日SALE(第二副折300)持續</t>
+        </is>
+      </c>
+      <c r="H81" s="17" t="inlineStr">
+        <is>
+          <t>一週年祭限定優惠+年中慶5折+第二副折300</t>
+        </is>
+      </c>
+      <c r="I81" s="17" t="inlineStr">
+        <is>
+          <t>指定門市</t>
+        </is>
+      </c>
+      <c r="J81" s="17" t="inlineStr">
+        <is>
+          <t>南高雄為本期火力點，OD高雄/左營門市留意客流分食</t>
+        </is>
+      </c>
+      <c r="K81" s="17" t="inlineStr">
+        <is>
+          <t>🟠 中｜強度4/5｜已一手確認</t>
+        </is>
+      </c>
+      <c r="L81" s="17" t="inlineStr">
+        <is>
+          <t>OD高雄/左營必要時加碼在地檔；夏季墨鏡持續卡位</t>
+        </is>
+      </c>
+      <c r="M81" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C82" s="17" t="inlineStr">
+        <is>
+          <t>促銷到期（一手確認）</t>
+        </is>
+      </c>
+      <c r="D82" s="17" t="inlineStr">
+        <is>
+          <t>指定眼鏡限時8折起（6/30止）</t>
+        </is>
+      </c>
+      <c r="E82" s="17" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="G82" s="17" t="inlineStr">
+        <is>
+          <t>官網news：5/14(四)-6/30(二) 指定眼鏡8折起，明日(6/30)為最後一天</t>
+        </is>
+      </c>
+      <c r="H82" s="17" t="inlineStr">
+        <is>
+          <t>指定眼鏡8折起</t>
+        </is>
+      </c>
+      <c r="I82" s="17" t="inlineStr">
+        <is>
+          <t>全台門市/EC</t>
+        </is>
+      </c>
+      <c r="J82" s="17" t="inlineStr">
+        <is>
+          <t>OD月底前以一價全包/免費升級總價優勢溝通；7/1起JINS此檔結束，留意接檔</t>
+        </is>
+      </c>
+      <c r="K82" s="17" t="inlineStr">
+        <is>
+          <t>🟠 中｜強度3/5｜已一手確認</t>
+        </is>
+      </c>
+      <c r="L82" s="17" t="inlineStr">
+        <is>
+          <t>把握6/30檔末與7/1空窗，凸顯OD總價穩定</t>
+        </is>
+      </c>
+      <c r="M82" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C83" s="17" t="inlineStr">
+        <is>
+          <t>年中慶（到期日曆）</t>
+        </is>
+      </c>
+      <c r="D83" s="17" t="inlineStr">
+        <is>
+          <t>年中慶第二波：5大遠百6/30-7/19</t>
+        </is>
+      </c>
+      <c r="E83" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="F83" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/19</t>
+        </is>
+      </c>
+      <c r="G83" s="17" t="inlineStr">
+        <is>
+          <t>一手確認news/182檔期表：遠百信義A13/板橋中山/桃園/新竹大遠百/台中大遠百 6/30(二)-7/19(日)；第一波多數百貨6/28已結束</t>
+        </is>
+      </c>
+      <c r="H83" s="17" t="inlineStr">
+        <is>
+          <t>滿6000折600(百貨)/滿5000折500(量販)+指定太陽眼鏡最高5折</t>
+        </is>
+      </c>
+      <c r="I83" s="17" t="inlineStr">
+        <is>
+          <t>指定百貨門市</t>
+        </is>
+      </c>
+      <c r="J83" s="17" t="inlineStr">
+        <is>
+          <t>年中慶火力由第一波轉向遠百系第二波(中北部+台中)，與OD大遠百商圈重疊；前次南高雄一週年祭續行</t>
+        </is>
+      </c>
+      <c r="K83" s="17" t="inlineStr">
+        <is>
+          <t>🟠 中｜強度4/5｜已一手確認</t>
+        </is>
+      </c>
+      <c r="L83" s="17" t="inlineStr">
+        <is>
+          <t>OD台中/桃園/新竹大遠百商圈7月留意遠百檔分食</t>
+        </is>
+      </c>
+      <c r="M83" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/182</t>
         </is>
       </c>
     </row>
@@ -8720,7 +9004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -11347,6 +11631,302 @@
         </is>
       </c>
       <c r="G77" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0）。新北18、屏東2</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C79" s="17" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D79" s="17" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E79" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F79" s="17" t="inlineStr">
+        <is>
+          <t>全台101間（±0，JINS 96+RIM 5）。新營醫院店傳6/26開幕，官網JS頁未一手確認、暫不計入</t>
+        </is>
+      </c>
+      <c r="G79" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E80" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>全台37間（±0）。本期動態在促銷面(6/23兩檔一週年祭)，無展店</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C81" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D81" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E81" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F81" s="17" t="inlineStr">
+        <is>
+          <t>全台19間（±0）。官網新品vs6/22無新增</t>
+        </is>
+      </c>
+      <c r="G81" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C82" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D82" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E82" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0；新北18、屏東2 已校正）</t>
+        </is>
+      </c>
+      <c r="G82" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C83" s="17" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D83" s="17" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E83" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F83" s="17" t="inlineStr">
+        <is>
+          <t>全台101間（±0，JINS 96+RIM 5）。store-tw為JS頁，沿用前期一手基準；6/30 8折檔末</t>
+        </is>
+      </c>
+      <c r="G83" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E84" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="inlineStr">
+        <is>
+          <t>全台37間（±0）。本期動態在促銷面：年中慶轉第二波(遠百)</t>
+        </is>
+      </c>
+      <c r="G84" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D85" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E85" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F85" s="17" t="inlineStr">
+        <is>
+          <t>全台19間（±0）。官網新品vs6/25無新增</t>
+        </is>
+      </c>
+      <c r="G85" s="17" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
@@ -11423,7 +12003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -12436,6 +13016,100 @@
         </is>
       </c>
       <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>W27-週四</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/25（週四更新）</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>1. ✅ JINS指定眼鏡5/14-6/30 8折起(一手確認，補回上期缺口) 2. ✅ 眼鏡市場6/23再加碼兩檔一週年祭(南高雄左營×2+經國) 3. 🔭 JINS新營醫院店傳6/26開幕(未一手確認、暫不計入)</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>🟡 低→中（門市數全±0連續第四個安靜週；動態集中促銷面，南高雄為熱點）</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>(a) OD月底前對標JINS 8折檔，以總價優勢溝通 (b) OD高雄/左營門市留意眼鏡市場一週年祭客流分食 (c) 下次以可渲染JS瀏覽器一手確認新營展店</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>W28-週一</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/29（週一更新）</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>1. 🟢 連續第五個±0安靜週（四品牌門市數全±0） 2. 🔴 JINS指定眼鏡8折檔6/30到期(明日最後一天) 3. 🟢 眼鏡市場年中慶轉第二波：5大遠百6/30-7/19</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>🟡 低→中（門市靜、促銷進入轉檔期：JINS折扣將收、眼鏡市場遠百系第二波接棒）</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>(a) OD把握6/30 JINS檔末與7/1空窗以總價優勢溝通 (b) OD台中/桃園/新竹大遠百商圈7月留意眼鏡市場遠百第二波 (c) 新增促銷到期日曆，掌握接招時點</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>KlassiC</t>
         </is>
@@ -12516,7 +13190,7 @@
       </c>
       <c r="B1" s="17" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/06/29</t>
         </is>
       </c>
     </row>
@@ -13079,4 +13753,286 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="18" min="1" max="1"/>
+    <col width="40" customWidth="1" style="18" min="2" max="2"/>
+    <col width="12" customWidth="1" style="18" min="3" max="3"/>
+    <col width="12" customWidth="1" style="18" min="4" max="4"/>
+    <col width="26" customWidth="1" style="18" min="5" max="5"/>
+    <col width="30" customWidth="1" style="18" min="6" max="6"/>
+    <col width="40" customWidth="1" style="18" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>品牌</t>
+        </is>
+      </c>
+      <c r="B1" s="41" t="inlineStr">
+        <is>
+          <t>檔期名稱</t>
+        </is>
+      </c>
+      <c r="C1" s="41" t="inlineStr">
+        <is>
+          <t>起</t>
+        </is>
+      </c>
+      <c r="D1" s="41" t="inlineStr">
+        <is>
+          <t>迄</t>
+        </is>
+      </c>
+      <c r="E1" s="41" t="inlineStr">
+        <is>
+          <t>狀態(2026/06/29)</t>
+        </is>
+      </c>
+      <c r="F1" s="41" t="inlineStr">
+        <is>
+          <t>OD 接招重點</t>
+        </is>
+      </c>
+      <c r="G1" s="41" t="inlineStr">
+        <is>
+          <t>資料來源URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="42" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="B2" s="42" t="inlineStr">
+        <is>
+          <t>指定眼鏡 8折起</t>
+        </is>
+      </c>
+      <c r="C2" s="42" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="D2" s="42" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="E2" s="42" t="inlineStr">
+        <is>
+          <t>🔴 即將結束（明日6/30最後一天）</t>
+        </is>
+      </c>
+      <c r="F2" s="42" t="inlineStr">
+        <is>
+          <t>6/30檔末＋7/1空窗以總價優勢溝通</t>
+        </is>
+      </c>
+      <c r="G2" s="42" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="42" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B3" s="42" t="inlineStr">
+        <is>
+          <t>年中慶 第一波（多數百貨/量販）</t>
+        </is>
+      </c>
+      <c r="C3" s="42" t="inlineStr">
+        <is>
+          <t>2026/06/04</t>
+        </is>
+      </c>
+      <c r="D3" s="42" t="inlineStr">
+        <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="E3" s="42" t="inlineStr">
+        <is>
+          <t>⬛ 已結束（昨日6/28）</t>
+        </is>
+      </c>
+      <c r="F3" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="42" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/182</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B4" s="42" t="inlineStr">
+        <is>
+          <t>年中慶 第二波（遠百信義A13/板橋中山/桃園/新竹/台中大遠百）</t>
+        </is>
+      </c>
+      <c r="C4" s="42" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr">
+        <is>
+          <t>2026/07/19</t>
+        </is>
+      </c>
+      <c r="E4" s="42" t="inlineStr">
+        <is>
+          <t>🟢 即將開跑（明日6/30）</t>
+        </is>
+      </c>
+      <c r="F4" s="42" t="inlineStr">
+        <is>
+          <t>OD遠百系商圈(台中/桃園/新竹)7月留意分食</t>
+        </is>
+      </c>
+      <c r="G4" s="42" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/182</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="inlineStr">
+        <is>
+          <t>年中慶 SOGO台北忠孝/新竹店</t>
+        </is>
+      </c>
+      <c r="C5" s="42" t="inlineStr">
+        <is>
+          <t>2026/06/04</t>
+        </is>
+      </c>
+      <c r="D5" s="42" t="inlineStr">
+        <is>
+          <t>2026/07/05</t>
+        </is>
+      </c>
+      <c r="E5" s="42" t="inlineStr">
+        <is>
+          <t>🟡 進行中</t>
+        </is>
+      </c>
+      <c r="F5" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="42" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/182</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="42" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B6" s="42" t="inlineStr">
+        <is>
+          <t>年中慶 誠品新店裕隆城店</t>
+        </is>
+      </c>
+      <c r="C6" s="42" t="inlineStr">
+        <is>
+          <t>2026/06/04</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="E6" s="42" t="inlineStr">
+        <is>
+          <t>🟡 進行中</t>
+        </is>
+      </c>
+      <c r="F6" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="42" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/182</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B7" s="42" t="inlineStr">
+        <is>
+          <t>2026夏日大作戰 第二副折300</t>
+        </is>
+      </c>
+      <c r="C7" s="42" t="inlineStr">
+        <is>
+          <t>2026/05/27</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
+        <is>
+          <t>未公告</t>
+        </is>
+      </c>
+      <c r="E7" s="42" t="inlineStr">
+        <is>
+          <t>🟡 進行中（官網無明確截止日）</t>
+        </is>
+      </c>
+      <c r="F7" s="42" t="inlineStr">
+        <is>
+          <t>OD夏季墨鏡持續對標</t>
+        </is>
+      </c>
+      <c r="G7" s="42" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/181</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -15,6 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每週摘要" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="門市分布（按縣市）" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="促銷到期日曆" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="促銷強度Rubric" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="閉環回看表" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'促銷活動'!$A$1:$M$1</definedName>
@@ -29,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -131,6 +133,16 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -198,7 +210,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -322,6 +334,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -601,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -6010,6 +6026,341 @@
       <c r="M83" s="17" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/182</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/02</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
+        <is>
+          <t>促銷（一手確認）</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="inlineStr">
+        <is>
+          <t>🎓學生限定優惠 憑學生證現折300</t>
+        </is>
+      </c>
+      <c r="E84" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/01</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="G84" s="17" t="inlineStr">
+        <is>
+          <t>官網news 7/1公告：7/1(三)-8/31(一)憑學生證配鏡現折300元；接續6/30到期之指定眼鏡8折</t>
+        </is>
+      </c>
+      <c r="H84" s="17" t="inlineStr">
+        <is>
+          <t>學生證現折300</t>
+        </is>
+      </c>
+      <c r="I84" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J84" s="17" t="inlineStr">
+        <is>
+          <t>窄眾(學生)非全店深折，強度低於前波8折；OD可同期主打開學季+免費升級對標</t>
+        </is>
+      </c>
+      <c r="K84" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低｜強度2/5｜已一手確認</t>
+        </is>
+      </c>
+      <c r="L84" s="17" t="inlineStr">
+        <is>
+          <t>OD搶開學季前推學生方案(含抗藍光升級)，以總價+服務對標</t>
+        </is>
+      </c>
+      <c r="M84" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/02</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
+        <is>
+          <t>新品/IP企劃（一手確認）</t>
+        </is>
+      </c>
+      <c r="D85" s="17" t="inlineStr">
+        <is>
+          <t>2026廢鏡新思 第5彈《動物友好樂園：魔法療癒森林》</t>
+        </is>
+      </c>
+      <c r="E85" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/07</t>
+        </is>
+      </c>
+      <c r="F85" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G85" s="17" t="inlineStr">
+        <is>
+          <t>官網news 6/26公告：7/7(二)登場，延續廢鏡回收ESG＋IP療癒敘事</t>
+        </is>
+      </c>
+      <c r="H85" s="17" t="inlineStr">
+        <is>
+          <t>ESG回收+IP系列</t>
+        </is>
+      </c>
+      <c r="I85" s="17" t="inlineStr">
+        <is>
+          <t>全通路</t>
+        </is>
+      </c>
+      <c r="J85" s="17" t="inlineStr">
+        <is>
+          <t>JINS持續以ESG+IP企劃獲客(第5彈)；OD可評估回收/公益敘事</t>
+        </is>
+      </c>
+      <c r="K85" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低｜品牌企劃｜已一手確認</t>
+        </is>
+      </c>
+      <c r="L85" s="17" t="inlineStr">
+        <is>
+          <t>觀察JINS ESG企劃年輕客群成效</t>
+        </is>
+      </c>
+      <c r="M85" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/02</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C86" s="17" t="inlineStr">
+        <is>
+          <t>閉店出清（一手確認）</t>
+        </is>
+      </c>
+      <c r="D86" s="17" t="inlineStr">
+        <is>
+          <t>宜蘭店 BYE BYE SALE</t>
+        </is>
+      </c>
+      <c r="E86" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="F86" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="G86" s="17" t="inlineStr">
+        <is>
+          <t>news/192一手：滿3000折300/滿5000折500/滿10000折1500＋指定商品最高5折出清</t>
+        </is>
+      </c>
+      <c r="H86" s="17" t="inlineStr">
+        <is>
+          <t>滿額折+指定最高5折</t>
+        </is>
+      </c>
+      <c r="I86" s="17" t="inlineStr">
+        <is>
+          <t>宜蘭店</t>
+        </is>
+      </c>
+      <c r="J86" s="17" t="inlineStr">
+        <is>
+          <t>閉店出清屬區域性、非全國檔；OD宜蘭門市可留意出清期客流與後續客源轉移</t>
+        </is>
+      </c>
+      <c r="K86" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中｜強度3/5｜已一手確認</t>
+        </is>
+      </c>
+      <c r="L86" s="17" t="inlineStr">
+        <is>
+          <t>OD宜蘭店把握眼鏡市場撤出後在地客源承接窗口</t>
+        </is>
+      </c>
+      <c r="M86" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/192</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C87" s="17" t="inlineStr">
+        <is>
+          <t>促銷（一手確認）</t>
+        </is>
+      </c>
+      <c r="D87" s="17" t="inlineStr">
+        <is>
+          <t>😎酷暑對策：配鏡升級調光變色鏡片享鏡片8折</t>
+        </is>
+      </c>
+      <c r="E87" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/03</t>
+        </is>
+      </c>
+      <c r="F87" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="G87" s="17" t="inlineStr">
+        <is>
+          <t>官網news 7/3公告：即日起~8/31(一)配鏡並升級調光變色鏡片，即享鏡片8折</t>
+        </is>
+      </c>
+      <c r="H87" s="17" t="inlineStr">
+        <is>
+          <t>升級調光變色鏡片→鏡片8折</t>
+        </is>
+      </c>
+      <c r="I87" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J87" s="17" t="inlineStr">
+        <is>
+          <t>JINS促銷火力回升（學生300窄眾＋調光8折雙檔並行）；OD調光/感光鏡片升級方案可同期對標，強調總價與免費升級</t>
+        </is>
+      </c>
+      <c r="K87" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中｜強度3/5｜已一手確認</t>
+        </is>
+      </c>
+      <c r="L87" s="17" t="inlineStr">
+        <is>
+          <t>OD夏季以調光鏡片對標，凸顯一價全包 vs JINS「配鏡+升級才8折」條件</t>
+        </is>
+      </c>
+      <c r="M87" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>促銷檔期明確化（一手確認）</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>2026 SUMMER SALE 第二彈 第二副現折300</t>
+        </is>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>news/194一手：第二彈即日起~7/22(三)第二副現折300；※屏東門市檔期7/13~7/22；※遠百及SOGO體系以年中慶檔期為主</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>第二副現折300；配到好1990起</t>
+        </is>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>全台門市（遠百/SOGO除外）</t>
+        </is>
+      </c>
+      <c r="J88" s="17" t="inlineStr">
+        <is>
+          <t>原「無明確截止日」之夏日大作戰已明確化為第二彈至7/22；與年中慶第二波(至7/19)雙檔疊加</t>
+        </is>
+      </c>
+      <c r="K88" s="17" t="inlineStr">
+        <is>
+          <t>🟠 中｜強度4/5維持｜已一手確認</t>
+        </is>
+      </c>
+      <c r="L88" s="17" t="inlineStr">
+        <is>
+          <t>OD 7/22前留意第二副需求分食，可用多副優惠/家庭配鏡對標</t>
+        </is>
+      </c>
+      <c r="M88" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/194</t>
         </is>
       </c>
     </row>
@@ -6087,13 +6438,295 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="18" min="1" max="1"/>
+    <col width="26" customWidth="1" style="18" min="2" max="2"/>
+    <col width="22" customWidth="1" style="18" min="3" max="3"/>
+    <col width="20" customWidth="1" style="18" min="4" max="4"/>
+    <col width="20" customWidth="1" style="18" min="5" max="5"/>
+    <col width="11" customWidth="1" style="18" min="6" max="6"/>
+    <col width="11" customWidth="1" style="18" min="7" max="7"/>
+    <col width="11" customWidth="1" style="18" min="8" max="8"/>
+    <col width="11" customWidth="1" style="18" min="9" max="9"/>
+    <col width="11" customWidth="1" style="18" min="10" max="10"/>
+    <col width="11" customWidth="1" style="18" min="11" max="11"/>
+    <col width="26" customWidth="1" style="18" min="12" max="12"/>
+    <col width="24" customWidth="1" style="18" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="43" t="inlineStr">
+        <is>
+          <t>閉環回看表（顧問#2/#14 兌現）— 只待貼數字，貼完即產出首筆ROI實證。建立日 2026/07/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="44" t="inlineStr">
+        <is>
+          <t>標的</t>
+        </is>
+      </c>
+      <c r="B3" s="44" t="inlineStr">
+        <is>
+          <t>觸發事件</t>
+        </is>
+      </c>
+      <c r="C3" s="44" t="inlineStr">
+        <is>
+          <t>OD 門市</t>
+        </is>
+      </c>
+      <c r="D3" s="44" t="inlineStr">
+        <is>
+          <t>比較期間(前)</t>
+        </is>
+      </c>
+      <c r="E3" s="44" t="inlineStr">
+        <is>
+          <t>比較期間(後)</t>
+        </is>
+      </c>
+      <c r="F3" s="44" t="inlineStr">
+        <is>
+          <t>來客數(前)</t>
+        </is>
+      </c>
+      <c r="G3" s="44" t="inlineStr">
+        <is>
+          <t>來客數(後)</t>
+        </is>
+      </c>
+      <c r="H3" s="44" t="inlineStr">
+        <is>
+          <t>業績(前)</t>
+        </is>
+      </c>
+      <c r="I3" s="44" t="inlineStr">
+        <is>
+          <t>業績(後)</t>
+        </is>
+      </c>
+      <c r="J3" s="44" t="inlineStr">
+        <is>
+          <t>客單價(前)</t>
+        </is>
+      </c>
+      <c r="K3" s="44" t="inlineStr">
+        <is>
+          <t>客單價(後)</t>
+        </is>
+      </c>
+      <c r="L3" s="44" t="inlineStr">
+        <is>
+          <t>對照組(建議)</t>
+        </is>
+      </c>
+      <c r="M3" s="44" t="inlineStr">
+        <is>
+          <t>判讀結論(填後自動可寫)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>屏東·開店衝擊</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>眼鏡市場屏東店 6/18 開幕</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OD 屏東店A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026/06/04–06/17</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026/06/18–07/01</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>OD 高雄同型店（無新競品開幕）</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>待填</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>屏東·開店衝擊</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>眼鏡市場屏東店 6/18 開幕</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OD 屏東店B</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026/06/04–06/17</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026/06/18–07/01</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>OD 高雄同型店（無新競品開幕）</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>待填</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>宜蘭·撤店承接</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>眼鏡市場宜蘭店 7/26 閉店</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>OD 宜蘭店</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026/07/12–07/25</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026/07/27–08/09</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>OD 花蓮店（無競品異動）</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>待填（7/27後可回看）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>台中·同館競爭</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Klassic 中港店開櫃（首見7/6）</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>OD 新光三越台中中港店</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026/06/22–07/05</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026/07/06–07/19</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>OD 台中大遠百店</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>待填（新增標的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>填表說明：1) 來客/業績/客單由 OD 內部 POS 匯出貼上 2) 對照組取同區型態相近門市 3) 判讀口徑：後期較對照組相對變化 ±5% 內視為無顯著影響</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -6958,6 +7591,63 @@
       <c r="K15" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/collections</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/02</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>IP/ESG企劃</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>廢鏡新思 第5彈《動物友好樂園：魔法療癒森林》</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/07</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>廢鏡回收ESG結合IP療癒森林主題，第5彈</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>全客群/年輕</t>
+        </is>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="17" t="inlineStr">
+        <is>
+          <t>JINS以ESG+IP高頻企劃獲客；OD可評估回收/公益敘事對標</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
         </is>
       </c>
     </row>
@@ -6990,7 +7680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -7891,6 +8581,100 @@
       <c r="I19" s="37" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/02</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>品牌肯定/PR</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>台灣服務業大評鑑 日企最快奪6金</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>7/1官網：JINS再獲台灣服務業大評鑑肯定，服務力主打客製化、分齡分眾</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>台灣服務業大評鑑</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>全客群</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>JINS以「服務力」為品牌敘事主軸(6金)；OD須持續強化驗光/服務差異化對標</t>
+        </is>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>EC檔期行銷</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>JINS官方商城 官網生日慶＋LINE Pay週週領券</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>7/2公告：官網生日慶開跑（人氣聯名/百萬熱銷/夏日限定優惠）；LINE Pay限定週週領80元券</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>LINE Pay</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>EC/全客群</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>JINS EC檔期高頻經營（618→生日慶接檔）；OD官網暑期檔期敘事可同步</t>
+        </is>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
         </is>
       </c>
     </row>
@@ -7928,7 +8712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -8975,6 +9759,194 @@
       <c r="I23" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場屏東店今日正式開幕，品牌首度進駐屏東（全台37間）。屏東原僅OWNDAYS 2間；OD屏東門市今起為客流觀測關鍵窗口，需強化在地驗光/服務/一價全包敘事</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>新開店（一手確認）</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>JINS 新光三越台北南西店一館店</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>台北市中山區 新光三越南西</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>JINS 南西商圈再加密（已有南西三館+RIM誠品南西）；前期以JS店頁未讀而漏登，本期Chrome一手補登。台北JINS 26→27，全台JINS 101→102</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>新開店（一手確認）</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>JINS 新營醫院店</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>台南市新營區</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>南部</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>JINS切入台南新營醫療商圈；前期漏登，本期補登。台南JINS 9→10，全台JINS 102→103。搭高齡換照配鏡新制敘事</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>閉店預告（一手確認）</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 宜蘭店（營業至7/26）</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>宜蘭</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>東部</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/26 閉店</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/192</t>
+        </is>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
+        <is>
+          <t>⚠️品牌首見閉店：「營運策略調整」，宜蘭店營業至7/26，客資轉統一時代台北店。眼鏡市場東部唯一據點撤出，37→36(7/26生效)。積極展店後首見收縮/往北部集中</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>新增（門市頁差異比對）</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC. 台中新光三越中港店</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>台中市西屯區臺灣大道三段301號B1（新光三越中港店B1F）</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>首見2026/07/06，開幕日未揭露</t>
+        </is>
+      </c>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>🔥 與OWNDAYS新光三越台中中港店同館競爭（SKM專櫃頁交叉確認 04-2254-9920）。Klassic 19→20、台中4→5，6/8台南撤櫃後首次淨增，展店重啟訊號</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -11927,6 +12899,302 @@
         </is>
       </c>
       <c r="G85" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/02</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C86" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D86" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E86" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F86" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0；新北18、屏東2 已校正）</t>
+        </is>
+      </c>
+      <c r="G86" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/02</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C87" s="17" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D87" s="17" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E87" s="17" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="F87" s="17" t="inlineStr">
+        <is>
+          <t>⚠️基準校正：Chrome讀JS店頁，補登前期漏計之新光三越台北南西一館店(6/25)＋新營醫院店(6/26)。JINS 98+RIM 5=103。101為未讀JS頁之過時基準</t>
+        </is>
+      </c>
+      <c r="G87" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/02</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>全台37間（±0）。⚠️宜蘭店7/26閉店→屆時36。動態在促銷面</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/02</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C89" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D89" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E89" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F89" s="17" t="inlineStr">
+        <is>
+          <t>全台19間（±0）。官網新品vs6/29無新增</t>
+        </is>
+      </c>
+      <c r="G89" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C90" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D90" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E90" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0；新北18、屏東2 已校正）</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C91" s="17" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D91" s="17" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E91" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F91" s="17" t="inlineStr">
+        <is>
+          <t>全台103間（±0）。✅顧問#16全22縣市逐店重算完成：JINS 98+RIM 5=103，與分布表逐縣市完全一致；RIM定案5家（台北3/台中1/台南1），「101沿用基準」歷史殘留清零</t>
+        </is>
+      </c>
+      <c r="G91" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C92" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D92" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E92" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F92" s="17" t="inlineStr">
+        <is>
+          <t>全台37間（±0）。宜蘭店7/26閉店倒數20天→屆時36</t>
+        </is>
+      </c>
+      <c r="G92" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C93" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D93" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E93" s="17" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="F93" s="17" t="inlineStr">
+        <is>
+          <t>🆕台中新光三越中港店首見於官網門市頁（B1F、暫無驗光服務；SKM專櫃頁交叉確認），與OD中港店同館。台中4→5</t>
+        </is>
+      </c>
+      <c r="G93" s="17" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
@@ -12003,7 +13271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -13110,6 +14378,102 @@
         </is>
       </c>
       <c r="I23" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>W28-週四</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/02（週四更新）</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>1. 🔴 基準校正：Chrome讀JS店頁，補登JINS前期漏計2店（新光三越台北南西一館6/25＋新營醫院6/26）→ JINS 101→103，全台 237→239。「連5週±0」部分屬未讀JS頁之量測假象
+2. ⚠️ 眼鏡市場首見閉店：宜蘭店營業至7/26(BYE BYE SALE 6/29-7/26，客資轉統一時代台北)，東部唯一據點撤出，37→36(7/26)
+3. 🎓 JINS 8折6/30到期→接學生現折300(7/1-8/31)；廢鏡第5彈《動物友好樂園》7/7上市</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>🟠 中→高（JINS展店實為進行式、非靜止；眼鏡市場首見收縮＝戰線調整訊號）</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>(a) 修正「安靜週」認知：JINS仍在展店，OD需以Chrome逐期一手清點店數 (b) OD宜蘭店把握眼鏡市場7/26撤出後在地客源承接窗口 (c) OD開學季對標JINS學生現折300，主打免費升級+服務</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>W29-週一</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/06（週一更新）</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>1. 🆕 Klassic台中新光三越中港店+1（19→20），與OWNDAYS中港店同館直面競爭，6/8台南撤櫃後首次淨增 2. ✅ 顧問#16兌現：JINS全22縣市逐店重算=103與分布表完全一致，RIM定案5家，基準殘留清零 3. 🔴 JINS 7/3新檔調光變色8折(~8/31)促銷回升2→3；眼鏡市場夏日第二彈明確化至7/22</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中（Klassic重啟展店且進OD同館；JINS促銷火力回升；眼鏡市場宜蘭7/26撤店倒數）</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>(a) OD新光三越台中中港店：Klassic同館開櫃（B1F），留意潮流/IP客群分食，強化驗光專業與一價全包差異 (b) OD以調光/感光升級方案對標JINS調光8折檔 (c) 宜蘭7/26承接窗口與屏東回看：閉環回看表已建妥待填數</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
         <is>
           <t>KlassiC</t>
         </is>
@@ -13190,7 +14554,7 @@
       </c>
       <c r="B1" s="17" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
     </row>
@@ -13237,7 +14601,7 @@
       </c>
       <c r="C4" s="32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D4" s="32" t="n">
@@ -13248,7 +14612,7 @@
       </c>
       <c r="F4" s="32" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -13399,12 +14763,14 @@
       <c r="D10" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="E10" s="32" t="n">
-        <v>4</v>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F10" s="32" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -13497,7 +14863,7 @@
       </c>
       <c r="C14" s="32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" s="32" t="n">
@@ -13510,7 +14876,7 @@
       </c>
       <c r="F14" s="32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -13683,7 +15049,7 @@
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="D21" s="34" t="inlineStr">
@@ -13693,12 +15059,12 @@
       </c>
       <c r="E21" s="34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F21" s="34" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>240</t>
         </is>
       </c>
     </row>
@@ -13761,7 +15127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="18" min="1" max="1"/>
@@ -13774,261 +15140,702 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="41" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>品牌</t>
         </is>
       </c>
-      <c r="B1" s="41" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>檔期名稱</t>
         </is>
       </c>
-      <c r="C1" s="41" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>起</t>
         </is>
       </c>
-      <c r="D1" s="41" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
         <is>
           <t>迄</t>
         </is>
       </c>
-      <c r="E1" s="41" t="inlineStr">
-        <is>
-          <t>狀態(2026/06/29)</t>
-        </is>
-      </c>
-      <c r="F1" s="41" t="inlineStr">
+      <c r="E1" s="17" t="inlineStr">
+        <is>
+          <t>狀態(自動續算@2026/07/06)</t>
+        </is>
+      </c>
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>OD 接招重點</t>
         </is>
       </c>
-      <c r="G1" s="41" t="inlineStr">
+      <c r="G1" s="17" t="inlineStr">
         <is>
           <t>資料來源URL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="42" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Jins</t>
         </is>
       </c>
-      <c r="B2" s="42" t="inlineStr">
-        <is>
-          <t>指定眼鏡 8折起</t>
-        </is>
-      </c>
-      <c r="C2" s="42" t="inlineStr">
-        <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="D2" s="42" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>🎓學生限定 現折300</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/01</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="E2" s="17" t="inlineStr">
+        <is>
+          <t>🟡 進行中</t>
+        </is>
+      </c>
+      <c r="F2" s="17" t="inlineStr">
+        <is>
+          <t>OD開學季對標，主打免費升級+服務</t>
+        </is>
+      </c>
+      <c r="G2" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>😎調光變色鏡片升級 鏡片8折</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/03</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>🟡 進行中</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>OD調光/感光升級方案對標，凸顯總價</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>廢鏡第5彈《動物友好樂園》上市</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/07</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>🟢 即將開跑（07/07上市，剩1天）</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>IP/ESG企劃，觀察年輕客群成效</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>年中慶 第二波（遠百A13/板橋中山/桃園/新竹/台中）</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>2026/06/30</t>
         </is>
       </c>
-      <c r="E2" s="42" t="inlineStr">
-        <is>
-          <t>🔴 即將結束（明日6/30最後一天）</t>
-        </is>
-      </c>
-      <c r="F2" s="42" t="inlineStr">
-        <is>
-          <t>6/30檔末＋7/1空窗以總價優勢溝通</t>
-        </is>
-      </c>
-      <c r="G2" s="42" t="inlineStr">
-        <is>
-          <t>https://www.jins.com/tw/news</t>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/19</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>🟡 進行中</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>OD台中/桃園/新竹大遠百商圈留意分食</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/182</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>年中慶 SOGO台北忠孝/新竹</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/04</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/05</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>⬛ 已結束</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>已收檔</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/182</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>年中慶 誠品新店裕隆城</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/04</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>🔴 今日最後一天</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>今日最後一天，檔末衝刺</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/182</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>宜蘭店 BYE BYE SALE（閉店出清）</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>🟡 進行中</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>OD宜蘭店承接撤出後在地客源</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/192</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>SUMMER SALE 第二彈 第二副折300（屏東7/13-7/22）</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>🟡 進行中</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>OD多副/家庭配鏡對標；7/22收檔</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/194</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="18" min="1" max="1"/>
+    <col width="10" customWidth="1" style="18" min="2" max="2"/>
+    <col width="12" customWidth="1" style="18" min="3" max="3"/>
+    <col width="14" customWidth="1" style="18" min="4" max="4"/>
+    <col width="12" customWidth="1" style="18" min="5" max="5"/>
+    <col width="10" customWidth="1" style="18" min="6" max="6"/>
+    <col width="52" customWidth="1" style="18" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="43" t="inlineStr">
+        <is>
+          <t>促銷強度評分 Rubric（1–5級，公開化定義）— 建立日 2026/07/02</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>強度分</t>
+        </is>
+      </c>
+      <c r="B2" s="44" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
+      <c r="C2" s="44" t="inlineStr">
+        <is>
+          <t>範例</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="42" t="inlineStr">
-        <is>
-          <t>眼鏡市場</t>
-        </is>
-      </c>
-      <c r="B3" s="42" t="inlineStr">
-        <is>
-          <t>年中慶 第一波（多數百貨/量販）</t>
-        </is>
-      </c>
-      <c r="C3" s="42" t="inlineStr">
-        <is>
-          <t>2026/06/04</t>
-        </is>
-      </c>
-      <c r="D3" s="42" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
-      <c r="E3" s="42" t="inlineStr">
-        <is>
-          <t>⬛ 已結束（昨日6/28）</t>
-        </is>
-      </c>
-      <c r="F3" s="42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G3" s="42" t="inlineStr">
-        <is>
-          <t>https://www.meganeichiba.com.tw/news/182</t>
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>全店/全品項深折(≤7折) 或 大型多重疊加(滿額+副數+IP)</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>週年慶全館7折</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="42" t="inlineStr">
-        <is>
-          <t>眼鏡市場</t>
-        </is>
-      </c>
-      <c r="B4" s="42" t="inlineStr">
-        <is>
-          <t>年中慶 第二波（遠百信義A13/板橋中山/桃園/新竹/台中大遠百）</t>
-        </is>
-      </c>
-      <c r="C4" s="42" t="inlineStr">
-        <is>
-          <t>2026/06/30</t>
-        </is>
-      </c>
-      <c r="D4" s="42" t="inlineStr">
-        <is>
-          <t>2026/07/19</t>
-        </is>
-      </c>
-      <c r="E4" s="42" t="inlineStr">
-        <is>
-          <t>🟢 即將開跑（明日6/30）</t>
-        </is>
-      </c>
-      <c r="F4" s="42" t="inlineStr">
-        <is>
-          <t>OD遠百系商圈(台中/桃園/新竹)7月留意分食</t>
-        </is>
-      </c>
-      <c r="G4" s="42" t="inlineStr">
-        <is>
-          <t>https://www.meganeichiba.com.tw/news/182</t>
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>指定大類別中折(7–8折) 或 年中慶/週年慶級多檔疊加</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>年中慶太陽眼鏡最高5折+滿額、一週年祭</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="inlineStr">
-        <is>
-          <t>眼鏡市場</t>
-        </is>
-      </c>
-      <c r="B5" s="42" t="inlineStr">
-        <is>
-          <t>年中慶 SOGO台北忠孝/新竹店</t>
-        </is>
-      </c>
-      <c r="C5" s="42" t="inlineStr">
-        <is>
-          <t>2026/06/04</t>
-        </is>
-      </c>
-      <c r="D5" s="42" t="inlineStr">
-        <is>
-          <t>2026/07/05</t>
-        </is>
-      </c>
-      <c r="E5" s="42" t="inlineStr">
-        <is>
-          <t>🟡 進行中</t>
-        </is>
-      </c>
-      <c r="F5" s="42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="42" t="inlineStr">
-        <is>
-          <t>https://www.meganeichiba.com.tw/news/182</t>
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>單一機制中度優惠(8–85折/第二副折300/閉店出清5折)</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>指定眼鏡8折、第二副折300、宜蘭閉店出清</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="42" t="inlineStr">
-        <is>
-          <t>眼鏡市場</t>
-        </is>
-      </c>
-      <c r="B6" s="42" t="inlineStr">
-        <is>
-          <t>年中慶 誠品新店裕隆城店</t>
-        </is>
-      </c>
-      <c r="C6" s="42" t="inlineStr">
-        <is>
-          <t>2026/06/04</t>
-        </is>
-      </c>
-      <c r="D6" s="42" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
-      <c r="E6" s="42" t="inlineStr">
-        <is>
-          <t>🟡 進行中</t>
-        </is>
-      </c>
-      <c r="F6" s="42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="42" t="inlineStr">
-        <is>
-          <t>https://www.meganeichiba.com.tw/news/182</t>
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>輕度/窄眾(學生/會員/滿額小折/現折300窄眾)</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>學生證現折300、會員日</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="42" t="inlineStr">
-        <is>
-          <t>眼鏡市場</t>
-        </is>
-      </c>
-      <c r="B7" s="42" t="inlineStr">
-        <is>
-          <t>2026夏日大作戰 第二副折300</t>
-        </is>
-      </c>
-      <c r="C7" s="42" t="inlineStr">
-        <is>
-          <t>2026/05/27</t>
-        </is>
-      </c>
-      <c r="D7" s="42" t="inlineStr">
-        <is>
-          <t>未公告</t>
-        </is>
-      </c>
-      <c r="E7" s="42" t="inlineStr">
-        <is>
-          <t>🟡 進行中（官網無明確截止日）</t>
-        </is>
-      </c>
-      <c r="F7" s="42" t="inlineStr">
-        <is>
-          <t>OD夏季墨鏡持續對標</t>
-        </is>
-      </c>
-      <c r="G7" s="42" t="inlineStr">
-        <is>
-          <t>https://www.meganeichiba.com.tw/news/181</t>
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>無實質折扣/純品牌或ESG企劃</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>廢鏡回收企劃、服務評鑑PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="45" t="inlineStr">
+        <is>
+          <t>促銷強度週趨勢（依已記錄強度分；W26前未建rubric）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="inlineStr">
+        <is>
+          <t>週次</t>
+        </is>
+      </c>
+      <c r="B10" s="44" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C10" s="44" t="inlineStr">
+        <is>
+          <t>JINS強度</t>
+        </is>
+      </c>
+      <c r="D10" s="44" t="inlineStr">
+        <is>
+          <t>眼鏡市場強度</t>
+        </is>
+      </c>
+      <c r="E10" s="44" t="inlineStr">
+        <is>
+          <t>Klassic強度</t>
+        </is>
+      </c>
+      <c r="F10" s="44" t="inlineStr">
+        <is>
+          <t>當週最高</t>
+        </is>
+      </c>
+      <c r="G10" s="44" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>W26-週一</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場屏東開幕+年中慶；JINS買2支$777</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>W27-週一</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>6/22</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>⚪未確認</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>JINS促銷未一手確認；眼鏡年中慶百貨</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>W27-週四</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>6/25</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>JINS 8折；眼鏡一週年祭×年中慶</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>W28-週一</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>JINS 8折到期；眼鏡年中慶第二波</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>W28-週四</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>7/2</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>JINS轉學生現折300(窄眾降至2)；眼鏡年中慶第二波+宜蘭出清5折</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>W29-週一</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>7/6</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>JINS調光8折7/3新檔回升2→3；眼鏡年中慶第二波+夏日第二彈疊加維持4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="46" t="inlineStr">
+        <is>
+          <t>讀法：JINS促銷強度2→3(調光8折新檔回升)；眼鏡市場穩定4(年中慶第二波+夏日第二彈疊加)，火力連5期領先JINS。Klassic靠IP聯名不打折(1)</t>
         </is>
       </c>
     </row>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -6361,6 +6361,73 @@
       <c r="M88" s="17" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/194</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C89" s="17" t="inlineStr">
+        <is>
+          <t>促銷（一手確認）</t>
+        </is>
+      </c>
+      <c r="D89" s="17" t="inlineStr">
+        <is>
+          <t>盛夏特惠 天天享第2支75折</t>
+        </is>
+      </c>
+      <c r="E89" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="F89" s="17" t="inlineStr">
+        <is>
+          <t>進行中（限時，未揭露截止）</t>
+        </is>
+      </c>
+      <c r="G89" s="17" t="inlineStr">
+        <is>
+          <t>官網news 7/8公告：盛夏特惠限時解鎖，天天享第2支75折</t>
+        </is>
+      </c>
+      <c r="H89" s="17" t="inlineStr">
+        <is>
+          <t>第2支75折</t>
+        </is>
+      </c>
+      <c r="I89" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J89" s="17" t="inlineStr">
+        <is>
+          <t>JINS促銷再加碼多副需求(第2支75折)，與調光8折(~8/31)、台北限定升級75折(7/1-8/31)三檔並行，火力回升3→4</t>
+        </is>
+      </c>
+      <c r="K89" s="17" t="inlineStr">
+        <is>
+          <t>🟠 中｜強度4/5｜已一手確認</t>
+        </is>
+      </c>
+      <c r="L89" s="17" t="inlineStr">
+        <is>
+          <t>OD以家庭配鏡/多副優惠對標JINS第2支75折，凸顯總價透明</t>
+        </is>
+      </c>
+      <c r="M89" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
         </is>
       </c>
     </row>
@@ -6537,179 +6604,179 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>屏東·開店衝擊</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場屏東店 6/18 開幕</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>OD 屏東店A</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>2026/06/04–06/17</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>2026/06/18–07/01</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr"/>
+      <c r="G4" s="17" t="inlineStr"/>
+      <c r="H4" s="17" t="inlineStr"/>
+      <c r="I4" s="17" t="inlineStr"/>
+      <c r="J4" s="17" t="inlineStr"/>
+      <c r="K4" s="17" t="inlineStr"/>
+      <c r="L4" s="17" t="inlineStr">
         <is>
           <t>OD 高雄同型店（無新競品開幕）</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="17" t="inlineStr">
         <is>
           <t>待填</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>屏東·開店衝擊</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場屏東店 6/18 開幕</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>OD 屏東店B</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>2026/06/04–06/17</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>2026/06/18–07/01</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr"/>
+      <c r="G5" s="17" t="inlineStr"/>
+      <c r="H5" s="17" t="inlineStr"/>
+      <c r="I5" s="17" t="inlineStr"/>
+      <c r="J5" s="17" t="inlineStr"/>
+      <c r="K5" s="17" t="inlineStr"/>
+      <c r="L5" s="17" t="inlineStr">
         <is>
           <t>OD 高雄同型店（無新競品開幕）</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="17" t="inlineStr">
         <is>
           <t>待填</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>宜蘭·撤店承接</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>眼鏡市場宜蘭店 7/26 閉店</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>OD 宜蘭店</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>2026/07/12–07/25</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>2026/07/27–08/09</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr"/>
+      <c r="G6" s="17" t="inlineStr"/>
+      <c r="H6" s="17" t="inlineStr"/>
+      <c r="I6" s="17" t="inlineStr"/>
+      <c r="J6" s="17" t="inlineStr"/>
+      <c r="K6" s="17" t="inlineStr"/>
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t>OD 花蓮店（無競品異動）</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="17" t="inlineStr">
         <is>
           <t>待填（7/27後可回看）</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>台中·同館競爭</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Klassic 中港店開櫃（首見7/6）</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>OD 新光三越台中中港店</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>2026/06/22–07/05</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>2026/07/06–07/19</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr"/>
+      <c r="G7" s="17" t="inlineStr"/>
+      <c r="H7" s="17" t="inlineStr"/>
+      <c r="I7" s="17" t="inlineStr"/>
+      <c r="J7" s="17" t="inlineStr"/>
+      <c r="K7" s="17" t="inlineStr"/>
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t>OD 台中大遠百店</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="17" t="inlineStr">
         <is>
           <t>待填（新增標的）</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>填表說明：1) 來客/業績/客單由 OD 內部 POS 匯出貼上 2) 對照組取同區型態相近門市 3) 判讀口徑：後期較對照組相對變化 ±5% 內視為無顯著影響</t>
         </is>
@@ -8712,7 +8779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -9947,6 +10014,53 @@
       <c r="I27" s="17" t="inlineStr">
         <is>
           <t>🔥 與OWNDAYS新光三越台中中港店同館競爭（SKM專櫃頁交叉確認 04-2254-9920）。Klassic 19→20、台中4→5，6/8台南撤櫃後首次淨增，展店重啟訊號</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>新開店預告（一手確認）</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>RIM 桃園統領廣場店</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>桃園統領廣場（桃園區中正路商圈）</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/09 開幕</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>🆕 RIM第6家、桃園首見RIM品牌店。JINS 103→104(7/9生效)、RIM 5→6。JINS以RIM副品牌向桃園年輕客群拓點；OD桃園商圈留意新店開幕聲量</t>
         </is>
       </c>
     </row>
@@ -9976,7 +10090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -13195,6 +13309,154 @@
         </is>
       </c>
       <c r="G93" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D94" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E94" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F94" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0；新北18、屏東2）</t>
+        </is>
+      </c>
+      <c r="G94" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C95" s="17" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D95" s="17" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E95" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F95" s="17" t="inlineStr">
+        <is>
+          <t>今日103（±0）；🔜RIM桃園統領廣場店7/9(四)開幕→屆時RIM6、JINS104。全22縣市已於7/6重算定案</t>
+        </is>
+      </c>
+      <c r="G95" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C96" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D96" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E96" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F96" s="17" t="inlineStr">
+        <is>
+          <t>全台37間（±0）；宜蘭店7/26閉店倒數18天→屆時36</t>
+        </is>
+      </c>
+      <c r="G96" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C97" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D97" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E97" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F97" s="17" t="inlineStr">
+        <is>
+          <t>全台20間（±0）；台中新光三越中港店與OD同館競爭持續；官網主打aeae聯名系列</t>
+        </is>
+      </c>
+      <c r="G97" s="17" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
@@ -13271,7 +13533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -14474,6 +14736,55 @@
         </is>
       </c>
       <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>W29-週三</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/08（週三 run now 即時更新）</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>1. 🔜 JINS RIM桃園統領廣場店7/9(四)開幕：RIM 5→6、JINS 103→104(7/9)，桃園首見RIM品牌店
+2. 🔴 JINS促銷再加碼：7/8「盛夏特惠 天天第2支75折」上線，與調光8折(~8/31)、台北限定升級75折(7/1-8/31)三檔並行，火力3→4
+3. 🟢 眼鏡市場37/Klassic20門市±0；宜蘭7/26撤店倒數18天</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>🟠 中→高（JINS展店+促銷雙升：桃園拓點且第2支75折直接對標多副需求）</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>(a) OD桃園商圈留意JINS RIM新店7/9開幕聲量 (b) OD以多副/家庭配鏡對標JINS第2支75折 (c) 宜蘭7/26承接窗口持續，閉環回看表待填數</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
         <is>
           <t>KlassiC</t>
         </is>
@@ -15127,7 +15438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="18" min="1" max="1"/>
@@ -15162,7 +15473,7 @@
       </c>
       <c r="E1" s="17" t="inlineStr">
         <is>
-          <t>狀態(自動續算@2026/07/06)</t>
+          <t>狀態(自動續算@2026/07/08)</t>
         </is>
       </c>
       <c r="F1" s="17" t="inlineStr">
@@ -15384,12 +15695,12 @@
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>🔴 今日最後一天</t>
+          <t>⬛ 已結束</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>今日最後一天，檔末衝刺</t>
+          <t>已收檔（7/6結束）</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
@@ -15469,6 +15780,117 @@
       <c r="G9" s="17" t="inlineStr">
         <is>
           <t>https://www.meganeichiba.com.tw/news/194</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>酷暑對策 調光變色鏡片8折</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/03</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>🟡 進行中</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>OD以調光/感光升級對標，凸顯一價全包</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>台北市限定 配鏡升級最高75折</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/01</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>🟡 進行中</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>OD台北門市對標，強調免費升級/總價</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>盛夏特惠 天天第2支75折</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>進行中(限時)</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>🟡 進行中</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>OD以多副/家庭配鏡對標</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
         </is>
       </c>
     </row>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -6426,6 +6426,73 @@
         </is>
       </c>
       <c r="M89" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/09</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C90" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D90" s="17" t="inlineStr">
+        <is>
+          <t>RIM桃園統領廣場店 開幕慶</t>
+        </is>
+      </c>
+      <c r="E90" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/09</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>開幕限定</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>RIM第6家桃園統領廣場店7/9開幕，來店就送、滿額再加碼（滿額贈RIM縫紉隔熱墊）</t>
+        </is>
+      </c>
+      <c r="H90" s="17" t="inlineStr">
+        <is>
+          <t>來店禮＋滿額贈</t>
+        </is>
+      </c>
+      <c r="I90" s="17" t="inlineStr">
+        <is>
+          <t>門市</t>
+        </is>
+      </c>
+      <c r="J90" s="17" t="inlineStr">
+        <is>
+          <t>OD桃園門市以驗光專業與一價全包對標，留意開幕期潮流客群分食</t>
+        </is>
+      </c>
+      <c r="K90" s="17" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L90" s="17" t="inlineStr">
+        <is>
+          <t>OD桃園商圈備開幕期對打腳本</t>
+        </is>
+      </c>
+      <c r="M90" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news</t>
         </is>
@@ -8779,7 +8846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -10061,6 +10128,53 @@
       <c r="I28" s="17" t="inlineStr">
         <is>
           <t>🆕 RIM第6家、桃園首見RIM品牌店。JINS 103→104(7/9生效)、RIM 5→6。JINS以RIM副品牌向桃園年輕客群拓點；OD桃園商圈留意新店開幕聲量</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/09</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>開幕確認（一手確認）</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>RIM 桃園統領廣場店</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>桃園統領廣場（桃園區中正路61號商圈）</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/09 開幕</t>
+        </is>
+      </c>
+      <c r="H29" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>✅ 7/8預告如期開幕：RIM第6家、桃園首見RIM品牌店正式營業。JINS 103→104、RIM 5→6(7/9生效)。開幕慶「來店就送＋滿額贈RIM縫紉隔熱墊」。同商圈已有KlassiC.桃園統領百貨店，桃園統領成多品牌眼鏡聚點；OD桃園門市留意開幕聲量與年輕潮流客群分食</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -13457,6 +13571,302 @@
         </is>
       </c>
       <c r="G97" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/09</t>
+        </is>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D98" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E98" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F98" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0；新北18、屏東2）</t>
+        </is>
+      </c>
+      <c r="G98" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/09</t>
+        </is>
+      </c>
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C99" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D99" s="17" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E99" s="17" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="F99" s="17" t="inlineStr">
+        <is>
+          <t>✅RIM桃園統領廣場店7/9如期開幕，RIM 5→6、JINS 103→104正式生效（全22縣市7/6已重算定案，本次+1為新店）</t>
+        </is>
+      </c>
+      <c r="G99" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/09</t>
+        </is>
+      </c>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C100" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D100" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E100" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F100" s="17" t="inlineStr">
+        <is>
+          <t>全台37間（±0）；宜蘭店7/26閉店倒數17天→屆時36</t>
+        </is>
+      </c>
+      <c r="G100" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/09</t>
+        </is>
+      </c>
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C101" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D101" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E101" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F101" s="17" t="inlineStr">
+        <is>
+          <t>全台20間（±0）；台中新光三越中港店與OD同館競爭持續；官網主打aeae聯名系列</t>
+        </is>
+      </c>
+      <c r="G101" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/13</t>
+        </is>
+      </c>
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C102" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D102" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E102" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F102" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0；新北18、屏東2）</t>
+        </is>
+      </c>
+      <c r="G102" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/13</t>
+        </is>
+      </c>
+      <c r="B103" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C103" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D103" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E103" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F103" s="17" t="inlineStr">
+        <is>
+          <t>全台104間（±0，含RIM 6）；7/10、7/11為例行營業時間調整公告（非新店）</t>
+        </is>
+      </c>
+      <c r="G103" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/13</t>
+        </is>
+      </c>
+      <c r="B104" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C104" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D104" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E104" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F104" s="17" t="inlineStr">
+        <is>
+          <t>全台37間（±0）；news最新貼文仍6/29；宜蘭店7/26閉店倒數13天→屆時36</t>
+        </is>
+      </c>
+      <c r="G104" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/13</t>
+        </is>
+      </c>
+      <c r="B105" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C105" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D105" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E105" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F105" s="17" t="inlineStr">
+        <is>
+          <t>全台20間（±0）；台中新光三越中港店與OD同館競爭持續；官網主打aeae聯名系列</t>
+        </is>
+      </c>
+      <c r="G105" s="17" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
@@ -13533,7 +13943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -14785,6 +15195,104 @@
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>W29-週四</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/09（週四更新）</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>1. ✅ JINS RIM桃園統領廣場店7/9如期開幕：RIM 5→6、JINS 103→104正式生效，桃園首見RIM品牌店（開幕慶滿額贈RIM縫紉隔熱墊）
+2. 🟢 眼鏡市場37/Klassic20門市±0；眼鏡市場最新貼文仍6/29，宜蘭7/26撤店倒數17天
+3. 🔎 桃園統領商圈成多品牌眼鏡聚點：RIM(JINS副牌)與KlassiC.桃園統領百貨店同商圈，年輕潮流客群競爭升溫</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>🟠 中→高（JINS桃園拓點正式落地；促銷四檔並行：第2支75折/調光8折/台北升級75折/RIM開幕慶）</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>(a) OD桃園門市留意RIM開幕期聲量與潮流客群分食，備開幕期對打腳本 (b) OD以多副/家庭配鏡對標JINS第2支75折 (c) 宜蘭7/26承接窗口持續，閉環回看表待填數</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>W30-週一</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/13（週一 run now 即時更新）</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>1. 🟢 安靜週開局：三家門市數全持平（JINS 104含RIM6/眼鏡市場37/Klassic20），無新開店、無撤店生效
+2. ⏳ 前瞻兩檔倒數：眼鏡市場「夏日大作戰第二副折300」7/22收檔倒數9天；宜蘭店7/26 BYE BYE SALE撤店倒數13天(37→36)
+3. 🔎 JINS 7/10、7/11為例行營業時間調整公告(非新店)；RIM維持6家；Klassic最新商品仍aeae聯名系列</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低（無新事件；焦點轉為到期日曆倒數與宜蘭承接窗口）</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>(a) OD把握7/22前「多副/家庭配鏡＋一價全包總價透明」對打JINS第2支75折×眼鏡市場第二副折300雙夾擊 (b) OD宜蘭店備妥7/26眼鏡市場撤出後在地客源承接，7/27後啟動回看 (c) 續推桃園統領商圈多品牌聚點小圖，供桃園門市當防禦地圖</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
         <is>
           <t>KlassiC</t>
         </is>
@@ -15438,7 +15946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="18" min="1" max="1"/>
@@ -15473,7 +15981,7 @@
       </c>
       <c r="E1" s="17" t="inlineStr">
         <is>
-          <t>狀態(自動續算@2026/07/08)</t>
+          <t>狀態(自動續算@2026/07/13)</t>
         </is>
       </c>
       <c r="F1" s="17" t="inlineStr">
@@ -15584,7 +16092,7 @@
       </c>
       <c r="E4" s="17" t="inlineStr">
         <is>
-          <t>🟢 即將開跑（07/07上市，剩1天）</t>
+          <t>🟢 已上市（07/07上市進行中）</t>
         </is>
       </c>
       <c r="F4" s="17" t="inlineStr">
@@ -15889,6 +16397,43 @@
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>RIM桃園統領廣場店 開幕慶（來店禮＋滿額贈RIM縫紉隔熱墊）</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/09</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>進行中(開幕限定)</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>🟢 開幕檔啟動(7/9)</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>OD桃園門市留意開幕聲量，以驗光專業/一價全包差異對打</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news</t>
         </is>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -6860,7 +6860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -7782,6 +7782,63 @@
       <c r="K16" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>聯名系列新品</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC. × aeae 聯名（摺疊墨鏡/扁方圓框/橢圓框/遮耳帽/T-shirt）</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>2026/07 上架</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>墨鏡/眼鏡 $2,480–$3,980；周邊 $1,580</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>潮流品牌 aeae 聯名：摺疊墨鏡$2,480、扁方圓框/橢圓框眼鏡與墨鏡$3,980，含遮耳帽/WEB LOGO T-shirt 周邊</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>年輕潮流/街頭客群</t>
+        </is>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="17" t="inlineStr">
+        <is>
+          <t>Klassic 以潮流品牌聯名擴年輕客群，價格帶 $2,480–3,980；OD 墨鏡/潮流線可檢視入門價格帶</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/new-arrival</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -8807,6 +8864,100 @@
         </is>
       </c>
       <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>IP/品牌聯名</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC. × aeae 聯名系列</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>官網最新商品主打 KlassiC.×aeae 潮流聯名：摺疊墨鏡$2,480、遮耳帽$1,580、WEB LOGO T-shirt$1,580、扁方圓框/橢圓框眼鏡與墨鏡$3,980（部分款已售完）</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>aeae（潮流品牌）</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>年輕潮流/街頭客群</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>Klassic 延續高頻 IP/品牌聯名獲客（Solo Leveling→aeae）；OD 可評估潮流品牌聯名或選品切入年輕客群</t>
+        </is>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/new-arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/09</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>名人代言/公益PR</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>廢鏡新思 第5彈 × 李珠珢 公益眼鏡義賣</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>7/9官網：李珠珢公益處女秀，眼鏡義賣募得10萬捐助浪浪（流浪動物），延續廢鏡回收ESG＋IP療癒森林敘事，衝年輕粉絲社群聲量</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>李珠珢（藝人）／廢鏡新思 ESG 企劃</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>年輕粉絲/潮流客群、ESG關注者</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="inlineStr">
+        <is>
+          <t>JINS 以「名人×公益×ESG」複合企劃衝年輕聲量；OD 可評估在地公益/回收敘事或 KOL 合作承接年輕客群</t>
+        </is>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news</t>
         </is>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -6495,6 +6495,73 @@
       <c r="M90" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/16</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C91" s="17" t="inlineStr">
+        <is>
+          <t>促銷/出清（一手確認）</t>
+        </is>
+      </c>
+      <c r="D91" s="17" t="inlineStr">
+        <is>
+          <t>狂夏出清☀️ 指定眼鏡7折起</t>
+        </is>
+      </c>
+      <c r="E91" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/01</t>
+        </is>
+      </c>
+      <c r="F91" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="G91" s="17" t="inlineStr">
+        <is>
+          <t>官網news 7/15公告：7/1(三)~8/31(一) 指定眼鏡7折起，暑期大型出清檔</t>
+        </is>
+      </c>
+      <c r="H91" s="17" t="inlineStr">
+        <is>
+          <t>指定鏡款7折起</t>
+        </is>
+      </c>
+      <c r="I91" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J91" s="17" t="inlineStr">
+        <is>
+          <t>JINS暑期促銷密度升至5檔並行(第2支75折/調光8折/台北75折/學生300/狂夏出清7折)，火力4→5；OD以全品項一價全包對打「指定款才7折」條件式折扣</t>
+        </is>
+      </c>
+      <c r="K91" s="17" t="inlineStr">
+        <is>
+          <t>🟠 中｜強度4/5｜已一手確認</t>
+        </is>
+      </c>
+      <c r="L91" s="17" t="inlineStr">
+        <is>
+          <t>OD凸顯全品項總價透明、不挑指定款 vs JINS指定眼鏡7折</t>
+        </is>
+      </c>
+      <c r="M91" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a56ef730c7b3</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -14018,6 +14085,154 @@
         </is>
       </c>
       <c r="G105" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/16</t>
+        </is>
+      </c>
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C106" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D106" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E106" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F106" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0；新北18、屏東2）</t>
+        </is>
+      </c>
+      <c r="G106" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/16</t>
+        </is>
+      </c>
+      <c r="B107" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C107" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D107" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E107" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F107" s="17" t="inlineStr">
+        <is>
+          <t>全台104間（±0，含RIM 6）；news最新為7/15「狂夏出清7折起」促銷(非新店)</t>
+        </is>
+      </c>
+      <c r="G107" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/16</t>
+        </is>
+      </c>
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C108" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D108" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E108" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F108" s="17" t="inlineStr">
+        <is>
+          <t>全台37間（±0）；news最新貼文仍6/29；宜蘭店7/26閉店倒數10天→屆時36</t>
+        </is>
+      </c>
+      <c r="G108" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/16</t>
+        </is>
+      </c>
+      <c r="B109" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C109" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D109" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E109" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F109" s="17" t="inlineStr">
+        <is>
+          <t>全台20間（±0，逐店實查20間）；台中新光三越中港店與OD同館競爭持續；官網主打Solo Leveling/aeae聯名</t>
+        </is>
+      </c>
+      <c r="G109" s="17" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
@@ -14094,7 +14309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -15444,6 +15659,55 @@
         </is>
       </c>
       <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>W30-週四</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/16（週四 run now 即時更新）</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>1. 🔴 JINS促銷密度升至5檔：7/15「狂夏出清☀️指定眼鏡7折起」(7/1-8/31)加入，與第2支75折/調光8折/台北升級75折/學生折300並行，暑期價格戰升溫
+2. ⏳ 到期倒數收緊：眼鏡市場「第二副折300」7/22收檔倒數6天；宜蘭店7/26 BYE BYE SALE撤店倒數10天(37→36)
+3. 🟢 三家門市數全持平(JINS 104含RIM6/眼鏡市場37/Klassic20逐店實查)；眼鏡市場news仍6/29、Klassic官網主打款(Solo Leveling/aeae/HANDMADE)均前期已登錄，無新聯名</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中（門市數全±0；但JINS促銷火力4→5檔、暑期折扣戰升溫；眼鏡市場第二副折300倒數6天為多副夾擊高峰）</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>(a) 【最急・倒數6天】多副夾擊最後防禦窗口：JINS第2支75折×眼鏡市場第二副折300(7/22收檔)，OD於7/22前以「多副/家庭配鏡＋一價全包總價透明」對打 (b) JINS狂夏出清「指定眼鏡才7折」為條件式折扣，OD以「全品項一價全包、不挑指定款」溝通對打 (c) 宜蘭7/26撤店倒數10天，OD宜蘭店備妥在地客源承接，7/27後啟動回看填數</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H29" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
         <is>
           <t>KlassiC</t>
         </is>
@@ -16097,7 +16361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="18" min="1" max="1"/>
@@ -16132,7 +16396,7 @@
       </c>
       <c r="E1" s="17" t="inlineStr">
         <is>
-          <t>狀態(自動續算@2026/07/13)</t>
+          <t>狀態(自動續算@2026/07/16)</t>
         </is>
       </c>
       <c r="F1" s="17" t="inlineStr">
@@ -16391,7 +16655,7 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>🟡 進行中</t>
+          <t>🟡 進行中（撤店倒數10天，7/26）</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
@@ -16428,7 +16692,7 @@
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>🟡 進行中</t>
+          <t>🟡 進行中（收檔倒數6天，7/22）</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
@@ -16576,7 +16840,7 @@
       </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
-          <t>🟢 開幕檔啟動(7/9)</t>
+          <t>🟢 開幕檔續行</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
@@ -16587,6 +16851,43 @@
       <c r="G13" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>狂夏出清 指定眼鏡7折起</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/01</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>🟡 進行中</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>OD以全品項一價全包對打「指定款才7折」條件式折扣</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a56ef730c7b3</t>
         </is>
       </c>
     </row>

--- a/競爭對手追蹤.xlsx
+++ b/競爭對手追蹤.xlsx
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="2"/>
@@ -6562,6 +6562,676 @@
       <c r="M91" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-6a56ef730c7b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C92" s="17" t="inlineStr">
+        <is>
+          <t>促銷（一手確認）</t>
+        </is>
+      </c>
+      <c r="D92" s="17" t="inlineStr">
+        <is>
+          <t>父親節SALE 配鏡第二副88折</t>
+        </is>
+      </c>
+      <c r="E92" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/23</t>
+        </is>
+      </c>
+      <c r="F92" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="G92" s="17" t="inlineStr">
+        <is>
+          <t>news/195一手：父親節配鏡第二副88折，7/23(四)-8/10(一)；接棒7/22收檔之「第二副折300」，多副折法由定額轉比例</t>
+        </is>
+      </c>
+      <c r="H92" s="17" t="inlineStr">
+        <is>
+          <t>第二副88折(省12%)</t>
+        </is>
+      </c>
+      <c r="I92" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J92" s="17" t="inlineStr">
+        <is>
+          <t>折法升級：第二副≥2,500元時折扣&gt;舊折300，往高價客單加碼；OD以一價全包/升級不加價/不需湊件對打</t>
+        </is>
+      </c>
+      <c r="K92" s="17" t="inlineStr">
+        <is>
+          <t>🟠 中｜強度4/5維持｜已一手確認</t>
+        </is>
+      </c>
+      <c r="L92" s="17" t="inlineStr">
+        <is>
+          <t>OD以多副/家庭配鏡對標，父親節/開學換季雙副溝通續打至8/10</t>
+        </is>
+      </c>
+      <c r="M92" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/195</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C93" s="17" t="inlineStr">
+        <is>
+          <t>促銷（一手確認）</t>
+        </is>
+      </c>
+      <c r="D93" s="17" t="inlineStr">
+        <is>
+          <t>SUMMER SALE 夏日大作戰 眼鏡第二副折300元</t>
+        </is>
+      </c>
+      <c r="E93" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="F93" s="17" t="inlineStr">
+        <is>
+          <t>進行中(限時)</t>
+        </is>
+      </c>
+      <c r="G93" s="17" t="inlineStr">
+        <is>
+          <t>news/202一手：夏日大作戰第二副折300元,8/7上線接棒父親節第二副88折(8/10收檔);多副折法由比例(88折)回到定額($300)</t>
+        </is>
+      </c>
+      <c r="H93" s="17" t="inlineStr">
+        <is>
+          <t>第二副折NT$300(定額)</t>
+        </is>
+      </c>
+      <c r="I93" s="17" t="inlineStr">
+        <is>
+          <t>全門市</t>
+        </is>
+      </c>
+      <c r="J93" s="17" t="inlineStr">
+        <is>
+          <t>OD以「每副同價、不需湊件、升級不加價」對打定額第二副折;定額折在高單價較不利、低單價較有感</t>
+        </is>
+      </c>
+      <c r="K93" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中</t>
+        </is>
+      </c>
+      <c r="L93" s="17" t="inlineStr">
+        <is>
+          <t>把握開學換季雙副需求,主打總價透明</t>
+        </is>
+      </c>
+      <c r="M93" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/202</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
+        <is>
+          <t>門市促銷（改裝重開）</t>
+        </is>
+      </c>
+      <c r="D94" s="17" t="inlineStr">
+        <is>
+          <t>改裝SALE 統一時代百貨台北店・SOGO忠孝店</t>
+        </is>
+      </c>
+      <c r="E94" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="F94" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G94" s="17" t="inlineStr">
+        <is>
+          <t>news/203一手：統一時代百貨台北店與SOGO忠孝店改裝SALE,滿額折+指定商品5折起,鎖定台北信義/東區精華百貨櫃點</t>
+        </is>
+      </c>
+      <c r="H94" s="17" t="inlineStr">
+        <is>
+          <t>滿額折+指定商品5折起</t>
+        </is>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
+        <is>
+          <t>統一時代台北店/SOGO忠孝店</t>
+        </is>
+      </c>
+      <c r="J94" s="17" t="inlineStr">
+        <is>
+          <t>OD台北信義/東區門市(新光三越信義/微風等)留意同商圈折扣分流,以服務體驗+當日取件穩客單</t>
+        </is>
+      </c>
+      <c r="K94" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中</t>
+        </is>
+      </c>
+      <c r="L94" s="17" t="inlineStr">
+        <is>
+          <t>台北精華櫃點對標,守服務差異</t>
+        </is>
+      </c>
+      <c r="M94" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/203</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C95" s="17" t="inlineStr">
+        <is>
+          <t>通路促銷</t>
+        </is>
+      </c>
+      <c r="D95" s="17" t="inlineStr">
+        <is>
+          <t>中元吉祥 量販店專屬優惠</t>
+        </is>
+      </c>
+      <c r="E95" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="F95" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G95" s="17" t="inlineStr">
+        <is>
+          <t>news/199一手：8/11上線中元檔,量販店(大全聯/愛買等)店型專屬優惠,鎖定量販客流</t>
+        </is>
+      </c>
+      <c r="H95" s="17" t="inlineStr">
+        <is>
+          <t>量販店專屬優惠</t>
+        </is>
+      </c>
+      <c r="I95" s="17" t="inlineStr">
+        <is>
+          <t>量販店型門市</t>
+        </is>
+      </c>
+      <c r="J95" s="17" t="inlineStr">
+        <is>
+          <t>量販店型客流非OD主戰場(OD以百貨/街邊為主),觀察即可</t>
+        </is>
+      </c>
+      <c r="K95" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低</t>
+        </is>
+      </c>
+      <c r="L95" s="17" t="inlineStr">
+        <is>
+          <t>觀察,非主戰場</t>
+        </is>
+      </c>
+      <c r="M95" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/199</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C96" s="17" t="inlineStr">
+        <is>
+          <t>促銷（一手確認）</t>
+        </is>
+      </c>
+      <c r="D96" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC.×DAN DA DAN 膽大黨 全系列買一送一</t>
+        </is>
+      </c>
+      <c r="E96" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="F96" s="17" t="inlineStr">
+        <is>
+          <t>進行中(限時)</t>
+        </is>
+      </c>
+      <c r="G96" s="17" t="inlineStr">
+        <is>
+          <t>優惠專區一手:膽大黨動漫IP全系列買一送一(BOGO),Klassic少見高強度買一送一,鎖動漫IP粉絲清庫轉化</t>
+        </is>
+      </c>
+      <c r="H96" s="17" t="inlineStr">
+        <is>
+          <t>全系列買一送一(BOGO)</t>
+        </is>
+      </c>
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>官網/門市</t>
+        </is>
+      </c>
+      <c r="J96" s="17" t="inlineStr">
+        <is>
+          <t>OD不打IP消耗戰;聯名配件BOGO非正面對打面,守中高階機能/鈦框+驗光專業</t>
+        </is>
+      </c>
+      <c r="K96" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低</t>
+        </is>
+      </c>
+      <c r="L96" s="17" t="inlineStr">
+        <is>
+          <t>觀察,非主戰場</t>
+        </is>
+      </c>
+      <c r="M96" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/promotions/dan-da-dan-bogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C97" s="17" t="inlineStr">
+        <is>
+          <t>門市週年促銷</t>
+        </is>
+      </c>
+      <c r="D97" s="17" t="inlineStr">
+        <is>
+          <t>桃園雙店一週年祭(大江+台茂購物中心店)</t>
+        </is>
+      </c>
+      <c r="E97" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="F97" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G97" s="17" t="inlineStr">
+        <is>
+          <t>news 209/210一手:大江+台茂購物中心店同日9/1一週年祭限定優惠;桃園4店叢集首屆週年轉留客期</t>
+        </is>
+      </c>
+      <c r="H97" s="17" t="inlineStr">
+        <is>
+          <t>一週年祭限定優惠</t>
+        </is>
+      </c>
+      <c r="I97" s="17" t="inlineStr">
+        <is>
+          <t>大江/台茂購物中心店</t>
+        </is>
+      </c>
+      <c r="J97" s="17" t="inlineStr">
+        <is>
+          <t>OD桃園門市對標,以驗光專業+當日取件承接外溢客流</t>
+        </is>
+      </c>
+      <c r="K97" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中</t>
+        </is>
+      </c>
+      <c r="L97" s="17" t="inlineStr">
+        <is>
+          <t>桃園門市留意週年檔加溫</t>
+        </is>
+      </c>
+      <c r="M97" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/209</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t>週年慶（一手確認）</t>
+        </is>
+      </c>
+      <c r="D98" s="17" t="inlineStr">
+        <is>
+          <t>JINS 週年暖身慶（台北市限定）</t>
+        </is>
+      </c>
+      <c r="E98" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="F98" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="G98" s="17" t="inlineStr">
+        <is>
+          <t>news一手:9/3(四)-9/16(三)週年暖身慶開跑(台北市限定),銜接全台逐店週年慶正檔一波/二波(9/4起滾動至Q4);8月四檔8/31到期後9月大檔快速回補</t>
+        </is>
+      </c>
+      <c r="H98" s="17" t="inlineStr">
+        <is>
+          <t>週年暖身慶(台北市限定)</t>
+        </is>
+      </c>
+      <c r="I98" s="17" t="inlineStr">
+        <is>
+          <t>台北市門市</t>
+        </is>
+      </c>
+      <c r="J98" s="17" t="inlineStr">
+        <is>
+          <t>OD以每副同價/不需湊件/升級不加價對打週年慶湊件邏輯,續承接開學配鏡</t>
+        </is>
+      </c>
+      <c r="K98" s="17" t="inlineStr">
+        <is>
+          <t>🟠 中｜週年慶大檔啟動</t>
+        </is>
+      </c>
+      <c r="L98" s="17" t="inlineStr">
+        <is>
+          <t>OD台北門市對標,守服務差異+透明總價</t>
+        </is>
+      </c>
+      <c r="M98" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a97c8c8d7a2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C99" s="17" t="inlineStr">
+        <is>
+          <t>促銷（一手確認）</t>
+        </is>
+      </c>
+      <c r="D99" s="17" t="inlineStr">
+        <is>
+          <t>配鏡升級舒壓鏡片85折(台北市限定)+RIM紅圓標85折+日本製濾藍光9折</t>
+        </is>
+      </c>
+      <c r="E99" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="F99" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/30</t>
+        </is>
+      </c>
+      <c r="G99" s="17" t="inlineStr">
+        <is>
+          <t>news一手:9/1-9/30三檔升級折並行—配鏡升級舒壓鏡片85折(台北市限定)、RIM指定光學紅圓標85折、日本製濾藍光鏡片9折</t>
+        </is>
+      </c>
+      <c r="H99" s="17" t="inlineStr">
+        <is>
+          <t>舒壓85折/紅圓標85折/濾藍光9折</t>
+        </is>
+      </c>
+      <c r="I99" s="17" t="inlineStr">
+        <is>
+          <t>台北市/RIM/全門市</t>
+        </is>
+      </c>
+      <c r="J99" s="17" t="inlineStr">
+        <is>
+          <t>OD以「升級不加價/一價全包」對打「升級才折」條件式優惠</t>
+        </is>
+      </c>
+      <c r="K99" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中</t>
+        </is>
+      </c>
+      <c r="L99" s="17" t="inlineStr">
+        <is>
+          <t>OD凸顯免費升級+透明總價</t>
+        </is>
+      </c>
+      <c r="M99" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a968fb48d551</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C100" s="17" t="inlineStr">
+        <is>
+          <t>促銷（一手確認）</t>
+        </is>
+      </c>
+      <c r="D100" s="17" t="inlineStr">
+        <is>
+          <t>【同遊享樂節】限定優惠活動</t>
+        </is>
+      </c>
+      <c r="E100" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="F100" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G100" s="17" t="inlineStr">
+        <is>
+          <t>news/207一手:同遊享樂節9/1起主題促銷檔,延續眼鏡市場9月促動能</t>
+        </is>
+      </c>
+      <c r="H100" s="17" t="inlineStr">
+        <is>
+          <t>同遊享樂節限定優惠</t>
+        </is>
+      </c>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>全台門市</t>
+        </is>
+      </c>
+      <c r="J100" s="17" t="inlineStr">
+        <is>
+          <t>OD觀察9月檔期節奏,以驗光專業+當日取件守客單</t>
+        </is>
+      </c>
+      <c r="K100" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中</t>
+        </is>
+      </c>
+      <c r="L100" s="17" t="inlineStr">
+        <is>
+          <t>觀察主題檔強度,守服務差異</t>
+        </is>
+      </c>
+      <c r="M100" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/207</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>促銷（一手確認）</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>KlassiC.×DAN DA DAN 膽大黨 限量福袋</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026/09</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>優惠專區:膽大黨DAN DA DAN限量福袋—4件組NT$2,800(最高值$5,700)/5件組NT$1,500(最高值$3,900);熱銷入門款KT系列$880(原$1,280)</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>福袋4件$2,800/5件$1,500;入門款$880</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>官網/門市</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Klassic以IP聯名福袋(膽大黨動漫客層)+入門款低價衝量;OD守中高階機能/鈦框+驗光專業,福袋非正面對打面</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>🟢 低</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>守中高階客單,聯名配件非對打面</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/sale</t>
         </is>
       </c>
     </row>
@@ -6927,7 +7597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -7906,6 +8576,561 @@
       <c r="K17" s="17" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/categories/new-arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/16</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>聯名科技新品</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>JINS × 攻殻機動隊 電子調光太陽眼鏡／光學款</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/16 開賣</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>電子調光太陽眼鏡 日本¥29,900（全球限量1,000副）／光學款 ¥19,900</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>JINS首款電子調光太陽眼鏡（液晶調光膜自動依環境光變色，鏡腳三段角度可調，附QRS造型眼鏡帶）；光學款鋁合金+不鏽鋼、黑/銀2色</t>
+        </is>
+      </c>
+      <c r="H18" s="17" t="inlineStr">
+        <is>
+          <t>科技/動漫/潮流客群</t>
+        </is>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="17" t="inlineStr">
+        <is>
+          <t>JINS首款電子調光技術＋科幻IP，話題型限量款（不支援度數/不可換片）；OD聚焦度數配鏡主戰場與一價全包</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>鏡框新品(夏日系列)</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>立夏 / 芒種 夏日新系列</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>2026/07</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>$2,980</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>兩系列各4型4色共16款，夏日節氣主題</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>全客群</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>進口設計師款(new-arrival)</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>AKILA TITAN / AKILA ECHO OPTIC / CHIMI Sally</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>2026/08 前排</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>$8,580–$8,680</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>進口設計師品牌鈦金屬/光學/墨鏡款前排上架，價位帶明顯高於前期自有款($3,580)</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>講究選品/高單價客群</t>
+        </is>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>Klassic以進口高單價設計師框拉高客單、形塑選品店定位，走向與OD/JINS平價全包路線區隔；OD台中中港同館維持驗光專業+一價全包差異化</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/new-arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>自有品牌新款(new-arrival)</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>ALEX / AURA / BAILEY / JAN</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>2026/08 前排</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>$3,580</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>自有品牌光學/墨鏡款,統一售價$3,580,補回主力價帶(前幾期在$8,580進口款與$2,480–3,980聯名款兩極輪替)</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>全客群/年輕潮流</t>
+        </is>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="17" t="inlineStr">
+        <is>
+          <t>Klassic把new-arrival曝光導回自家核心產品,價帶落OD中高框位</t>
+        </is>
+      </c>
+      <c r="K21" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/new-arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>鏡框新品(秋冬系列)</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>JINS 俐落摩登系列</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/06 上市</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>搶先解碼2026秋冬流行,高質感靜奢風;台北/新北限定8/1–8/31配鏡升級最高75折</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>全客群/型男質感客</t>
+        </is>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>JINS以季節新系列+雙北限定折扣連動,OD守日系設計+一價全包差異化</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a74020118f3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>鈦金屬機能款(自有品牌)</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC. AXIS 鈦金屬方框眼鏡</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>2026/08 上市</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>鈦金屬框(中高單價)</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>FOCUS IS THE NEW SHAPE;β-鈦緩衝+山形支撐+彈性連接三段式穩定結構、較同款輕約30%、1000種臉型實測黃金比例、窄方框</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="inlineStr">
+        <is>
+          <t>長時間專注/上班族/質感客</t>
+        </is>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
+        <is>
+          <t>OD鈦金屬/機能鏡框</t>
+        </is>
+      </c>
+      <c r="J23" s="17" t="inlineStr">
+        <is>
+          <t>Klassic以材質+工學訴求把new-arrival曝光導向自有款(非只靠聯名);價帶落OD中高鈦框對照區,台中中港同館對照#18</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/products/axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>形狀×機能自有款(new-arrival)</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC. SILENCE IS THE NEW SHAPE</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>2026/08 上架</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>自有款(中高單價)</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>延續AXIS「___ IS THE NEW SHAPE」語彙的形狀×機能自有產品線</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="inlineStr">
+        <is>
+          <t>質感/機能取向客群</t>
+        </is>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>OD機能/簡約鏡框</t>
+        </is>
+      </c>
+      <c r="J24" s="17" t="inlineStr">
+        <is>
+          <t>Klassic持續把new-arrival曝光導向材質+工學自有款而非只靠IP聯名</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/klassic-silence-is-the-new-shape</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>機能系列(自有款/眼鏡分類)</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC. FUTURE FLEX 機能系列</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>2026/08 上架</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>機能款(中高單價)</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>機能訴求自有系列，同步成為眼鏡「Future Flex機能系列」分類</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="inlineStr">
+        <is>
+          <t>機能/長時配戴客群</t>
+        </is>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>OD中高階機能/鈦框</t>
+        </is>
+      </c>
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>與AXIS鈦金屬同屬機能自有雙引擎，正面對照OD機能鏡框(顧問#18台中中港同館battlecard觀察點)</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/future-flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>潮流IP聯名(new-arrival)</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC. × Tokyo Vitamin</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>2026/08 上架</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>墨鏡$3,980 / 棒球帽$1,380</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>日系潮流IP聯名,aeae後的下一個合作,墨鏡+配件(棒球帽)橫向延伸,維持話題與年輕客群黏著</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>潮流/生活風格年輕客群</t>
+        </is>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
+        <is>
+          <t>OD中高階機能/鈦框(聯名配件非正面對打面)</t>
+        </is>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>Klassic以「日系潮流IP聯名(aeae→Tokyo Vitamin)+墨鏡/配件延伸」走生活風格零售路線;OD續以AXIS+FUTURE FLEX機能雙引擎對打其鏡框主力</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/new-arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>鏡片產品線(恢復販售)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>JINS 極薄鏡片(折射率1.76)恢復販售與保固更換</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026/09/04 公告</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>高折射率高階鏡片</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>折射率1.76極薄鏡片恢復供給+保固更換服務,補齊高度數薄鏡片戰力</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>高度數/追求輕薄客群</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>OD全度數同價(1.74標配,升級不加價)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>JINS恢復1.76高階薄鏡片=高度數客層對打點;OD以全度數同價/免費升級對打其高折射率加價模式</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-68b6bf112b8c9</t>
         </is>
       </c>
     </row>
@@ -7938,7 +9163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -9027,6 +10252,711 @@
       <c r="I23" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>IP聯名/科技新品</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>JINS × 攻殻機動隊《THE GHOST IN THE SHELL》聯名系列</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>7/14公告、7/16開賣：JINS首款電子調光太陽眼鏡（液晶調光膜自動變色）全球限量1,000副；另有賽博龐克風光學款2色（黑/銀）。含專屬收藏盒與聯名眼鏡帶（QRS插頭造型）</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>攻殻機動隊 THE GHOST IN THE SHELL</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>科技/動漫/潮流客群、賽博龐克粉絲</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="inlineStr">
+        <is>
+          <t>JINS以大型科幻IP＋首款電子調光技術搶科技聲量（繼Barbie/吉伊卡哇後）；OD以驗光專業＋一價全包差異化，聯名屬話題型限量非價格戰</t>
+        </is>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>促銷/檔期行銷</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>【父親節】配鏡第二副88折（7/23-8/10）</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>news/195一手：父親節SALE配鏡第二副88折，活動期間7/23(四)-8/10(一)，涵蓋日常鏡框/多焦眼鏡/家人一起配鏡升級；接棒已於7/22收檔的「第二副折300」</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>父親節</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>家庭配鏡/父親換鏡/多副客群</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="inlineStr">
+        <is>
+          <t>多副折法由「定額-300」轉「比例88折」：第二副≥2,500元時88折省的&gt;舊折300，眼鏡市場把多副折扣往高價客單加碼並延燒至8/10；OD以一價全包、升級不加價、不需湊件對打(見週報第5張深挖)</t>
+        </is>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/195</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>展店/開幕行銷</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 Mini G Mall 豐原店 8/7(五) 開幕</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>7/31公告：台中Mini G Mall 1F全新店8/7開幕，開幕慶8/7-9/7滿3000折300/滿5000折500，來店贈呦嘻百分百授權眼鏡布、消費滿2000贈授權手提袋(限量300)</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>呦嘻百分百</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>大台中/豐原消費者</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場7/26宜蘭閉店後即以豐原補回，展店動能未熄；OD大台中門市留意開幕期客流競爭</t>
+        </is>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/197</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>KOL/社群行銷</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>JINS「黃金比例2.0」人氣主播曬照</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>7/30官網：人氣主播體驗JINS「黃金比例2.0」，社群曬照引千讚（王顯瑜、鄧崴私服穿搭示範質感型男風），延續高頻KOL/社群獲客</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>人氣主播/KOL</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>年輕/型男客群</t>
+        </is>
+      </c>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
+          <t>併入本期深挖「JINS新品/聯名/代言節奏時間軸」(顧問#8)：JINS以IP+名人+產品線三軌高頻曝光；OD聚焦驗光專業+一價全包結構性差異</t>
+        </is>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a6b064a29f3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>商品企劃/聯名上架</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC.×aeae 聯名系列回到 new-arrival 前排</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>8/6一手：new-arrival前排由上期AKILA/CHIMI進口設計師款換回 KlassiC.×aeae 聯名系列（摺疊墨鏡$2,480、扁方圓框/橢圓框墨鏡·眼鏡$3,980、遮耳帽/WEB LOGO Tee$1,580）；同步「輕行者摺疊墨鏡兩件85折」續掛</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>aeae(潮流品牌)</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>年輕潮流/街頭客群</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="inlineStr">
+        <is>
+          <t>Klassic前排選品在「進口高單價設計師款」與「潮流聯名款」間輪替，客單策略在$3,580~8,680與$2,480~3,980聯名帶擺盪；OD維持驗光專業+一價全包差異化</t>
+        </is>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/new-arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>IP聯名</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 × HUNTER×HUNTER（獵人）聯名 campaign</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>首頁主打獵人(HUNTER×HUNTER)IP聯名campaign,搭MUV機能鏡片、色彩鏡片專頁</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER 獵人</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>動漫/年輕客群</t>
+        </is>
+      </c>
+      <c r="H29" s="17" t="inlineStr">
+        <is>
+          <t>三家同期押注動漫IP(眼鏡市場獵人/JINS攻殻機動隊/Klassic Solo Leveling)搶年輕聲量;OD守驗光專業+一價全包,不打IP話題戰</t>
+        </is>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>https://campaign.meganeichiba.com.tw/hunterxhunter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>商品企劃/聯名擴張</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>Klassic new-arrival新增自有款ALEX/AURA/BAILEY/JAN＋Solo Leveling·SUNSHINE HUNTER IP</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>8/10一手:new-arrival除aeae聯名前排續掛,新增自有品牌款ALEX/AURA/BAILEY/JAN($3,580)補回主力價帶;選單新增我獨自升級(Solo Leveling)、SUNSHINE HUNTER GAME兩檔IP</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>Solo Leveling我獨自升級/SUNSHINE HUNTER</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>年輕潮流/街頭客群</t>
+        </is>
+      </c>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>Klassic以$3,580自有款把new-arrival曝光導回核心產品(非只靠聯名話題),並密集IP聯名擴年輕客;價帶落OD中高框位,台中中港同館對照#18</t>
+        </is>
+      </c>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/new-arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>商品企劃/IP版圖擴張</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>Klassic new-arrival IP系列再擴＋鈦金屬AXIS雙引擎</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>8/14一手:new-arrival選單再擴,新增Berry Normal Day/THE LUCKY LINE/BLUE ERA/Kapsule/Billionaire Boys Club×ICECREAM等系列聯名;同期推自有鈦金屬AXIS,形成「鈦金屬機能自有款×密集IP聯名」雙引擎</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>BBC×ICECREAM/BLUE ERA/Kapsule等</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>潮流/Z世代/收藏客</t>
+        </is>
+      </c>
+      <c r="H31" s="17" t="inlineStr">
+        <is>
+          <t>Klassic以雙引擎維持new-arrival熱度;與眼鏡市場(獵人)、JINS(攻殼)形成三家IP押注同期競逐(見本期深挖橫向對照);OD不打IP消耗戰,守專業+透明總價</t>
+        </is>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/new-arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>商品企劃/自有產品線擴張</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>Klassic new-arrival新增SILENCE+FUTURE FLEX</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>8/17一手:new-arrival選單新增SILENCE IS THE NEW SHAPE與FUTURE FLEX機能系列(後者同為眼鏡分類)</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>自有款(SILENCE/FUTURE FLEX/AXIS鈦金屬)</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>質感/機能取向客群</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>Klassic以機能自有款把new-arrival熱度從IP聯名分散到材質+工學,OD可對照機能鏡框差異化</t>
+        </is>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/new-arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>促銷/IP聯名</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC.×DAN DA DAN(膽大黨)全系列買一送一</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>8/31一手優惠專區:膽大黨動漫IP全系列BOGO(買一送一),為Klassic少見高強度買一送一機制,搭配輕行者摺疊墨鏡兩件85折</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>DAN DA DAN 膽大黨(動漫IP)</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>動漫IP粉絲/年輕客群</t>
+        </is>
+      </c>
+      <c r="H33" s="17" t="inlineStr">
+        <is>
+          <t>Klassic以IP週邊BOGO維持年輕客流黏著;OD不打IP消耗戰,守專業驗光+透明總價+中高階機能鈦框</t>
+        </is>
+      </c>
+      <c r="I33" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/promotions/dan-da-dan-bogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>門市週年行銷</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>桃園雙店一週年祭(大江購物中心店+台茂購物中心店)</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>8/31一手news:大江(209)+台茂(210)購物中心店同日9/1一週年祭限定優惠;兩店同屆週年=桃園4店叢集(遠東桃園+大江+經國+台茂)2025秋批量進場後首屆週年,轉入留客/回購階段</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>桃園在地客群/回購客</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>OD桃園門市(統領/藝文特區)以驗光專業+當日取件承接眼鏡市場桃園週年促動能外溢</t>
+        </is>
+      </c>
+      <c r="I34" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>週年慶/大型促銷檔</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>JINS 週年慶啟動（暖身慶9/3-9/16+全台逐店一波/二波）</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>9/2一手:JINS週年暖身慶9/3(四)-9/16開跑(台北市限定),搭配週年慶正檔全台逐店一波/二波檔期自9/4起滾動至Q4(各店日期不同);同期配鏡升級舒壓鏡片85折/RIM紅圓標85折/日本製濾藍光9折(皆9/1-9/30)。8月四檔8/31到期後,9月新檔立即回補=promo cliff僅維持極短空窗</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>全客群/開學換季客</t>
+        </is>
+      </c>
+      <c r="H35" s="17" t="inlineStr">
+        <is>
+          <t>JINS以「週年慶大檔+舒壓鏡片升級折」把8月到期火力快速回補;OD以驗光專業+每副同價/不需湊件承接開學配鏡,不打湊件消耗戰</t>
+        </is>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-68b6bf112b8c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>主題促銷/門市改裝</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 同遊享樂節9/1 + SOGO台北忠孝店改裝9/1~9/20</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>9/1一手news:【同遊享樂節】限定優惠(207)9/1起主題檔;同日公告【改裝通知】SOGO百貨台北忠孝店9/1~9/20內部改裝(208),與統一時代台北店改裝(8/24~9/10)並行=台北雙館同時改裝(門市數維持38)</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>家庭/在地客群</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場9月以同遊享樂節主題檔延續促動能;台北雙館改裝期,OD台北信義/東區門市以當日取件承接外溢客流</t>
+        </is>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>產品線恢復/週年慶時程</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>JINS 1.76極薄鏡片恢復販售 + 週年慶全台逐店開檔時程公布</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>9/4一手:【重要公告】極薄鏡片(折射率1.76)恢復販售與保固更換服務;週年慶正檔全台逐店一波/二波時程完整公布(9/4三創起滾動至12月各店不同)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>高度數/高階客群+全客群</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>JINS補齊高折射率薄鏡片戰力(OD全度數同價/1.74標配需守);週年慶時程—折扣峰值9/25-10/22,OD對打人力集中9月下旬-10月中</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-68b6bf112b8c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>門市改裝完工</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>眼鏡市場 統一時代百貨台北店 9/11 REOPEN</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>9/4一手news:統一時代百貨台北店9/11(五)REOPEN(改裝8/24~9/10完工);SOGO忠孝店改裝中(~9/20)續行</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>家庭/在地客群</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>台北改裝外溢承接窗口收斂;OD台北信義/東區承接窗口剩SOGO忠孝一館(~9/20)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
         </is>
       </c>
     </row>
@@ -9064,7 +10994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="3"/>
@@ -10393,6 +12323,941 @@
       <c r="I29" s="17" t="inlineStr">
         <is>
           <t>✅ 7/8預告如期開幕：RIM第6家、桃園首見RIM品牌店正式營業。JINS 103→104、RIM 5→6(7/9生效)。開幕慶「來店就送＋滿額贈RIM縫紉隔熱墊」。同商圈已有KlassiC.桃園統領百貨店，桃園統領成多品牌眼鏡聚點；OD桃園門市留意開幕聲量與年輕潮流客群分食</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>新開店（8月開幕確認）</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>淡水英專店</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>新北市淡水區英專路33號1樓（淡江大學/英專路商圈）</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>2026/08（8月開幕）</t>
+        </is>
+      </c>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>開幕生效（認列）</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>JINS 淡水英專店</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>新北市淡水區英專路33號1樓（淡江大學/英專路商圈）</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>2026/08 開幕</t>
+        </is>
+      </c>
+      <c r="H31" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>✅ 7/30預告之淡水英專店本期認列開店生效：JINS 104→105、新北19→20。開幕慶淡水居民配鏡現折300至8/31+IG見面禮+滿額贈毛巾。直面OD淡水店，OD備開學季學生方案對打</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>新開店預告（一手確認）</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 Mini G Mall 豐原店</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>台中市豐原區 Mini G Mall 1F</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/07 開幕</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/197</t>
+        </is>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
+        <is>
+          <t>🆕 7/31公告8/7(五)開幕，開幕慶8/7-9/7滿3000折300/滿5000折500，來店贈呦嘻眼鏡布、滿2000贈手提袋(限量300)。7/26宜蘭閉店後隨即以豐原補回；官網門市頁(/45)尚未上架，開店後營運36→37。OD大台中留意客源競爭</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>⚠️資料校正（既有門市非新開店）</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>JINS 淡水英專店</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>新北市淡水區英專路33號1樓（淡江大學/英專路商圈）</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>2024/08/05 開幕（既有）</t>
+        </is>
+      </c>
+      <c r="H33" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-66b046b0b4c16</t>
+        </is>
+      </c>
+      <c r="I33" s="17" t="inlineStr">
+        <is>
+          <t>⚠️一手複查：官方唯一淡水英專店開店新聞原文日期為2024.08.05，2026 JINS news feed無任何淡水新開店公告。7/30~8/3以「8月新開店」認列(+1→105)係2024舊聞被搜尋誤帶為當期，本期回正JINS 105→104、新北20→19。此店為長期既有門市，理應早已在roster；待Howard對照官方門市頁最終核對</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>新開店(明日生效)</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 Mini G Mall 豐原店</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>台中市豐原區 Mini G Mall 1F(社皮里大社街8號)</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/07 開幕</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/197</t>
+        </is>
+      </c>
+      <c r="I34" s="17" t="inlineStr">
+        <is>
+          <t>明日8/7(五)開幕，今日官網門市頁/45仍未上架、營運維持36；明日生效後營運36→37。開幕慶8/7-9/7滿3000折300/滿5000折500。OD大台中留意客源競爭</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>新開店預告（一手確認）</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>JINS 誠品生活480店</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>台中市西屯區市政路480號B1（誠品生活480/台中七期）</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/15 開幕</t>
+        </is>
+      </c>
+      <c r="H35" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-689ac3cfad673</t>
+        </is>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>🆕 官方news明列8/15(五)新開幕＝JINS主品牌(非RIM)真新店,落台中七期精華商圈。今日未開,主品牌維持98;8/15生效98→99、JINS104→105。開幕滿$3000贈皮革收納盒</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>新開店（副品牌RIM,已生效）</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>RIM BY JINS 台北京站店</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>台北市信義區忠孝東路五段68號2F（京站時尚廣場）</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/01 開幕</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-689a8d5940fd3</t>
+        </is>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>RIM京站8/1正式開幕,繼LaLaport台中/南港·誠品南西·統領桃園後再落一子,首度與JINS同商場。計入既有RIM6(JINS卡片98+6=104不變);建議RIM獨立追蹤軸#21+官方roster閉合#28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>開幕生效＋閉店移除（門市數定錨）</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 Mini G Mall 豐原店 / 宜蘭店移除</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>台中市豐原區社皮里大社街8號 Mini G Mall 1F</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/07 開幕（宜蘭7/26閉店已移除）</t>
+        </is>
+      </c>
+      <c r="H37" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>✅豐原/45已由「未上架」轉為官網門市頁「8/7 NEW OPEN」正式上架,宜蘭已自門市頁移除→逐店清點乾淨37(掛牌=營運,消除35/36/37三值)。淨展店:宜蘭關1豐原開1,8月淨+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>新開店（一手確認生效）</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>JINS 誠品生活480店</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>台中市西屯區市政路480號B1（誠品生活480/台中七期商圈）</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/15 開幕</t>
+        </is>
+      </c>
+      <c r="H38" s="17" t="inlineStr">
+        <is>
+          <t>https://store-tw.jins.com/b/jins_tw/info/85091/</t>
+        </is>
+      </c>
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>✅上期倒數店，已於官方門市搜尋上架(info/85091)＝主品牌真新店生效；OD七期/西屯門市強化一價全包+當日取件對打</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>新開店（一手確認生效）</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>JINS 水湳愛買店</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>台中市西屯區中清路二段1199號B1（水湳經貿園區/量販型）</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/15 前後上架</t>
+        </is>
+      </c>
+      <c r="H39" s="17" t="inlineStr">
+        <is>
+          <t>https://store-tw.jins.com/b/jins_tw/attr/?t=attr&amp;area_cd=middle&amp;shop_type=1</t>
+        </is>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>✅官方門市搜尋已上架，與誠品480同期在台中雙商圈布局；台中主品牌含此兩店=14家(逐區加總權威閉合)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>新開店預告（官網一手）</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 台北大巨蛋店</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>台北市（台北大巨蛋 / 松山信義娛樂型商圈）</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/22 開幕</t>
+        </is>
+      </c>
+      <c r="H40" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>⏳官網news 8/17公告8/22(六)OPEN。今日門市頁未上架,營運維持37;週六生效37→38 pending(台北市megane 6→7)。繼南紡3/25→嘉義5/29→屏東6/18→豐原8/7後再展店,首度切入台北大巨蛋高流量商圈;OD松山/信義門市開幕檔攔截</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>門市計數口徑閉合（roster定錨）</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>Klassic 全台逐店 roster（21 storefront）</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>北11/中5/南5（官方門市頁逐店）</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+      <c r="I41" s="17" t="inlineStr">
+        <is>
+          <t>✅兌現顧問#32:官方門市頁列21 storefront=18主品牌驗光+3副品牌暫無驗光(Klassroom/SON&amp;SUN忠孝SOGO/SON&amp;SUN南西誠品)。追蹤20→21(台北8→9,先前少計1副品牌櫃);比照JINS#28逐區口徑,三家新銳計數統一。副品牌軸可比照RIM#21獨立追蹤</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>新開店（一手確認生效）</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 台北大巨蛋店</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>台北市（台北大巨蛋 / 松山信義娛樂型商圈）</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/22 開幕</t>
+        </is>
+      </c>
+      <c r="H42" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>✅上期pending兌現:官網門市頁已上架【8/22 NEW OPEN】台北大巨蛋店,營運37→38,台北市megane 6→7。繼南紡3/25→嘉義5/29→屏東6/18→豐原8/7後再展店,首度切入台北大巨蛋高流量娛樂型商圈;OD松山/信義門市開幕檔以當日取件+升級不加價攔截,並列第5個閉環回看窗口</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>新開店（一手確認生效）</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC. SOGO大巨蛋店</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>台北市信義區光復南路105號B1（SOGO大巨蛋/台北大巨蛋娛樂型商圈）</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>2026/08（門市頁已上架）</t>
+        </is>
+      </c>
+      <c r="H43" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>🟣新發現:官方門市頁新增KlassiC. SOGO大巨蛋店(暫無驗光,主品牌零售櫃)→Klassic 21→22(北11→12)。與眼鏡市場台北大巨蛋店(8/22)同一大巨蛋商圈,大巨蛋成雙競品同址戰場;OD松山/信義門市開幕檔以當日取件+升級不加價+驗光專業攔截</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>改裝暫停（暫時性,門市數不變）</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 統一時代百貨台北店</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>台北市信義區忠孝東路五段8號（統一時代百貨台北店）</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/24~09/10 改裝</t>
+        </is>
+      </c>
+      <c r="H44" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+      <c r="I44" s="17" t="inlineStr">
+        <is>
+          <t>🟠官網news 8/24公告內部改裝修整8/24~9/10,暫時性關櫃整修,門市數維持38;9/10完工後留意重開檔促銷</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>新開店預告（官網一手）</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>JINS 蘆洲佳瑪店</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>新北市蘆洲區（佳瑪量販型商圈）</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/04 開幕</t>
+        </is>
+      </c>
+      <c r="H45" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a968aa30e515</t>
+        </is>
+      </c>
+      <c r="I45" s="17" t="inlineStr">
+        <is>
+          <t>⏳官網news 9/1公告9/4(五)盛大開幕。今日未生效,JINS維持104;9/4生效後104→105 pending(新北量販型據點)。OD新北門市留意開幕檔客流</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>新開店預告（官網一手）</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>JINS 秀泰台東店</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>台東縣（秀泰影城/購物中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>東部</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/10 開幕</t>
+        </is>
+      </c>
+      <c r="H46" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a968c2b27ffc</t>
+        </is>
+      </c>
+      <c r="I46" s="17" t="inlineStr">
+        <is>
+          <t>⏳官網news 9/1公告9/10(四)盛大開幕=JINS繼花蓮後東部再插旗(東部2→3 pending);105→106 pending。台東OD僅1店,eyewear東部密度低區,留意JINS東部布局</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>門市淨減（官方頁下架）</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>Klassic 台北櫃點-1（官方門市頁台北 10→9）</t>
+        </is>
+      </c>
+      <c r="E47" s="17" t="inlineStr">
+        <is>
+          <t>台北（官方門市頁逐店清點）</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+      <c r="I47" s="17" t="inlineStr">
+        <is>
+          <t>🔻官方門市頁逐店清點由8/27-8/31的22減為21(北11/中5/南5);台北storefront 10→9,SOGO大巨蛋店仍在,另一台北櫃點自官方頁移除。競品門市首次淨減-1;待下期覆核屬撤櫃或頁面暫時調整。競品164→163、全台244→243、八品牌1,017→1,016</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>新開店（一手確認生效）</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>JINS 蘆洲佳瑪店</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>新北市蘆洲區（佳瑪量販型商圈）</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026/09/04 開幕（已生效）</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-68b6bf112b8c9</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>✅9/4開幕日已過(今日9/7),計入門市數104→105,新北jins 19→20(主品牌98→99+RIM6)。OD新北門市(18店)留意量販型開幕檔客流外溢</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>改裝完工重開（門市數不變）</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>眼鏡市場 統一時代百貨台北店</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>台北市信義區（統一時代百貨台北店）</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026/09/11 REOPEN</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>🟠改裝8/24~9/10完工,門市頁標【9/11 REOPEN】,9/11(五)重開確認;門市數維持38。台北改裝承接窗口收斂,剩SOGO忠孝(~9/20)一館</t>
         </is>
       </c>
     </row>
@@ -10422,7 +13287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -14233,6 +17098,2058 @@
         </is>
       </c>
       <c r="G109" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C110" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D110" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E110" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F110" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0；新北18、屏東2）</t>
+        </is>
+      </c>
+      <c r="G110" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="B111" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C111" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D111" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E111" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F111" s="17" t="inlineStr">
+        <is>
+          <t>全台104間（±0，含RIM 6）；7/16起JINS×攻殻機動隊聯名系列開賣（電子調光太陽眼鏡全球限量1,000副）</t>
+        </is>
+      </c>
+      <c r="G111" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="B112" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C112" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D112" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E112" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F112" s="17" t="inlineStr">
+        <is>
+          <t>全台37間（±0）；news最新貼文仍6/29；宜蘭店7/26閉店倒數6天→屆時36</t>
+        </is>
+      </c>
+      <c r="G112" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="B113" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C113" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D113" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E113" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F113" s="17" t="inlineStr">
+        <is>
+          <t>全台20間（±0，逐店實查20間）；台中新光三越中港店與OD同館競爭持續</t>
+        </is>
+      </c>
+      <c r="G113" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="B114" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C114" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D114" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E114" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F114" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0；新北18、屏東2）</t>
+        </is>
+      </c>
+      <c r="G114" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="B115" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C115" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D115" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E115" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F115" s="17" t="inlineStr">
+        <is>
+          <t>全台104間（±0，含RIM 6）；news無新增門市/新事件；攻殻機動隊聯名(7/16開賣)為前期已登錄；狂夏出清7折續行</t>
+        </is>
+      </c>
+      <c r="G115" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="B116" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C116" s="17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D116" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E116" s="17" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F116" s="17" t="inlineStr">
+        <is>
+          <t>宜蘭店7/26已閉店(37→36)；官網門市頁今日仍列36含宜蘭(未即時移除)，實際營運將降至35待下期一手複查；父親節第二副88折(7/23-8/10)接棒折300</t>
+        </is>
+      </c>
+      <c r="G116" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="B117" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C117" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D117" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E117" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F117" s="17" t="inlineStr">
+        <is>
+          <t>全台20間（±0，逐店實查20間）；台中新光三越中港店與OD同館競爭持續；輕行者摺疊墨鏡兩件85折上架</t>
+        </is>
+      </c>
+      <c r="G117" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="B118" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C118" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D118" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E118" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F118" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0；新北18、屏東2）</t>
+        </is>
+      </c>
+      <c r="G118" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="B119" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C119" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D119" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E119" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F119" s="17" t="inlineStr">
+        <is>
+          <t>全台104間（±0，含RIM 6）；🆕 淡水英專店（新北市淡水區英專路33號1樓）8月開幕確認，開幕日起至8/31淡水居民配鏡現折300，開店後→新北+1/JINS 105；🆕 立夏/芒種夏日新系列（各4型4色共16款，$2,980）</t>
+        </is>
+      </c>
+      <c r="G119" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="B120" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C120" s="17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D120" s="17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E120" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F120" s="17" t="inlineStr">
+        <is>
+          <t>逐店定錨完成（兌現顧問#25）：官網門市頁掛牌37間（含已閉店宜蘭店/25，官網尚未移除）、實際營運中36間；永久消除35/36/37三值並存。父親節第二副88折(7/23-8/10)續行</t>
+        </is>
+      </c>
+      <c r="G120" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="B121" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C121" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D121" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E121" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F121" s="17" t="inlineStr">
+        <is>
+          <t>全台20間（±0，逐店實查20間）；new-arrival前排新增ALEX/AURA/BAILEY/JAN($3,580)＋aeae全系列(已登錄)；輕行者兩件85折續行</t>
+        </is>
+      </c>
+      <c r="G121" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B122" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C122" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D122" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E122" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F122" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0；新北18、屏東2）</t>
+        </is>
+      </c>
+      <c r="G122" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B123" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C123" s="17" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D123" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E123" s="17" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="F123" s="17" t="inlineStr">
+        <is>
+          <t>🆕 淡水英專店（新北市淡水區英專路33號1F，淡江大學/英專路商圈）開幕生效，開幕慶淡水居民配鏡現折300至8/31；JINS 104→105（99一般+RIM6；新北19→20）。🆕 台北/新北限定8/1-8/31配鏡升級最高75折新檔上線；狂夏出清7折(7/1-8/31)續行</t>
+        </is>
+      </c>
+      <c r="G123" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B124" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C124" s="17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D124" s="17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E124" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F124" s="17" t="inlineStr">
+        <is>
+          <t>營運中36（掛牌37含未移除之宜蘭/25）；🆕 Mini G Mall豐原店(台中)8/7(五)開幕確認，開店後營運36→37(待生效)；父親節第二副88折(7/23-8/10)續行</t>
+        </is>
+      </c>
+      <c r="G124" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="B125" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C125" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D125" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E125" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F125" s="17" t="inlineStr">
+        <is>
+          <t>全台20間（±0）；new-arrival前排換上進口設計師品牌AKILA TITAN/AKILA ECHO OPTIC/CHIMI Sally($8,580-8,680)，價位帶高於前期自有款</t>
+        </is>
+      </c>
+      <c r="G125" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B126" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C126" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D126" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E126" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F126" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0；新北18、屏東2）</t>
+        </is>
+      </c>
+      <c r="G126" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B127" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C127" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D127" s="17" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="E127" s="17" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F127" s="17" t="inlineStr">
+        <is>
+          <t>⚠️資料校正回正：淡水英專店經一手複查為【2024.08.05開幕之既有門市】（官方原文 news-66b046b0b4c16 日期2024.08.05），2026年JINS news feed無任何淡水新開店公告。8/3認列為「新開店」(104→105)係2024舊聞被搜尋誤帶為當期，本期回正 JINS 105→104（98一般+RIM6，新北20→19）。待Howard對照官方門市頁最終核對</t>
+        </is>
+      </c>
+      <c r="G127" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-66b046b0b4c16</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B128" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C128" s="17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D128" s="17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E128" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F128" s="17" t="inlineStr">
+        <is>
+          <t>營運中36（掛牌37含未移除之宜蘭/25）；🆕 Mini G Mall豐原店(台中)明日8/7(五)開幕，開店後營運36→37（明日生效，官網門市頁/45今日仍未上架）；父親節第二副88折(7/23-8/10)續行</t>
+        </is>
+      </c>
+      <c r="G128" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B129" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C129" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D129" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E129" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F129" s="17" t="inlineStr">
+        <is>
+          <t>全台20間（±0）；new-arrival前排換回 KlassiC.×aeae 聯名系列（摺疊墨鏡$2,480／扁方圓框·橢圓框墨鏡·眼鏡$3,980／遮耳帽·WEB LOGO Tee$1,580），取代上期前排之AKILA/CHIMI進口款；輕行者摺疊墨鏡兩件85折續行</t>
+        </is>
+      </c>
+      <c r="G129" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/new-arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B130" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C130" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D130" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E130" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F130" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（±0；新北18、屏東2）</t>
+        </is>
+      </c>
+      <c r="G130" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B131" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C131" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D131" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E131" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F131" s="17" t="inlineStr">
+        <is>
+          <t>±0（98一般＋RIM6）。🆕誠品生活480店（台中西屯市政路480號B1）8/15(五)新開幕＝主品牌真新店，8/15生效98→99、JINS→105 pending；RIM台北京站店8/1已開幕（計入既有RIM6，首度與JINS同商場）。暑期五檔折扣至8/31續行</t>
+        </is>
+      </c>
+      <c r="G131" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-689ac3cfad673</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B132" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C132" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D132" s="17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E132" s="17" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="F132" s="17" t="inlineStr">
+        <is>
+          <t>🆕豐原店(Mini G Mall /45)8/7已開幕並上架官網門市頁、宜蘭店已自門市頁移除→逐店清點乾淨37（掛牌＝營運，永久消除35/36/37三值歧義，兌現顧問#25閉合；台中7→8）</t>
+        </is>
+      </c>
+      <c r="G132" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="B133" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C133" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D133" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E133" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F133" s="17" t="inlineStr">
+        <is>
+          <t>全台20間（±0）；new-arrival新增自有款ALEX/AURA/BAILEY/JAN（$3,580）＋Solo Leveling/SUNSHINE HUNTER IP聯名，aeae前排續掛</t>
+        </is>
+      </c>
+      <c r="G133" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/new-arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="B134" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C134" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D134" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="E134" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F134" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（新北18、屏東2）；基準未變</t>
+        </is>
+      </c>
+      <c r="G134" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw/shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="B135" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C135" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D135" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E135" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F135" s="17" t="inlineStr">
+        <is>
+          <t>含RIM6；誠品480店(台中西屯)8/15明日開幕＝主品牌真新店(生效後104→105 pending)；俐落摩登8/6上市續；雙北升級最高75折8/1–8/31</t>
+        </is>
+      </c>
+      <c r="G135" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="B136" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C136" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D136" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E136" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F136" s="17" t="inlineStr">
+        <is>
+          <t>維持37(豐原8/7已計入,本週無新開/關)；促銷三連發：中元量販8/11+改裝SALE統一時代台北/SOGO忠孝8/7+SUMMER第二副折$300</t>
+        </is>
+      </c>
+      <c r="G136" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="B137" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C137" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D137" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E137" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F137" s="17" t="inlineStr">
+        <is>
+          <t>維持20；AXIS鈦金屬方框新旗艦上市(β-鈦三段式結構、輕30%,FOCUS IS THE NEW SHAPE)＋new-arrival IP系列再擴(BBC×ICECREAM/BLUE ERA/Kapsule等)</t>
+        </is>
+      </c>
+      <c r="G137" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/new-arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="B138" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C138" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D138" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E138" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F138" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（新北18、屏東2）；基準未變</t>
+        </is>
+      </c>
+      <c r="G138" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="B139" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C139" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D139" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E139" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F139" s="17" t="inlineStr">
+        <is>
+          <t>✅官方逐區加總權威閉合(北62+中17+南23+東2=104；主品牌98+RIM6)。誠品480(8/15開幕)+水湳愛買均已上架台中；先前預估104→105未成立(人工基數回正)</t>
+        </is>
+      </c>
+      <c r="G139" s="17" t="inlineStr">
+        <is>
+          <t>https://store-tw.jins.com/b/jins_tw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="B140" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C140" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D140" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E140" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F140" s="17" t="inlineStr">
+        <is>
+          <t>維持37；本週無新開/關店、無新促銷(既有檔期續行)</t>
+        </is>
+      </c>
+      <c r="G140" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="B141" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C141" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D141" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E141" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F141" s="17" t="inlineStr">
+        <is>
+          <t>暫維持20；官方門市頁現列21 storefront(含SON&amp;SUN/Klassroom副品牌與暫無驗光櫃點)待下期釐清；new-arrival新增SILENCE IS THE NEW SHAPE+FUTURE FLEX機能系列</t>
+        </is>
+      </c>
+      <c r="G141" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="B142" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C142" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D142" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E142" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F142" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（新北18、屏東2）；基準未變</t>
+        </is>
+      </c>
+      <c r="G142" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="B143" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C143" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D143" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E143" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F143" s="17" t="inlineStr">
+        <is>
+          <t>維持104(主品牌98+RIM6)；本週官網news無新開店/RIM拓點,8月促銷續行(第2支75折8/17-8/31、雙北最高75折8/1-8/31、俐落摩登8/6上市)</t>
+        </is>
+      </c>
+      <c r="G143" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="B144" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C144" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D144" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E144" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F144" s="17" t="inlineStr">
+        <is>
+          <t>今日營運37；⏳台北大巨蛋店8/22(六)OPEN開幕倒數(官網news 8/17公告),週六生效37→38 pending(下次排程回補繪點)</t>
+        </is>
+      </c>
+      <c r="G144" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="B145" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C145" s="17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D145" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E145" s="17" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="F145" s="17" t="inlineStr">
+        <is>
+          <t>✅roster閉合(兌現#32):官方門市頁21 storefront(北11/中5/南5)=18主品牌驗光+3副品牌暫無驗光(Klassroom/SON&amp;SUN忠孝SOGO/SON&amp;SUN南西誠品);追蹤20係台北少計1副品牌櫃,定錨21(台北8→9)。new-arrival無新產品線</t>
+        </is>
+      </c>
+      <c r="G145" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="B146" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C146" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D146" s="17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E146" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F146" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（新北18、屏東2）；基準未變</t>
+        </is>
+      </c>
+      <c r="G146" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="B147" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C147" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D147" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E147" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F147" s="17" t="inlineStr">
+        <is>
+          <t>維持104(主品牌98+RIM6)；官網news自8/17起無新開店/RIM拓點,8月促銷四檔續行+官方商城NEW LIFE新生活提案(8/11)</t>
+        </is>
+      </c>
+      <c r="G147" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="B148" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C148" s="17" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D148" s="17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E148" s="17" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="F148" s="17" t="inlineStr">
+        <is>
+          <t>✅大巨蛋店8/22已開幕生效：官網門市頁上架【8/22 NEW OPEN】台北大巨蛋店,兌現上期pending 37→38(台北市megane 6→7);2026展店節奏再落一站(南紡→嘉義→屏東→豐原→大巨蛋),首入雙北旗艦娛樂商圈</t>
+        </is>
+      </c>
+      <c r="G148" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="B149" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C149" s="17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D149" s="17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E149" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F149" s="17" t="inlineStr">
+        <is>
+          <t>維持21(北11/中5/南5);🟣new-arrival新增聯名產品線KlassiC.×Tokyo Vitamin(墨鏡$3,980/棒球帽$1,380);資料校正:台中中港店現標示暫無驗光,主品牌驗光/無驗光拆分18+3→17+4,storefront總數不變</t>
+        </is>
+      </c>
+      <c r="G149" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/new-arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B150" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C150" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D150" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="E150" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F150" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（新北18、屏東2）；基準未變</t>
+        </is>
+      </c>
+      <c r="G150" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B151" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C151" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D151" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E151" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F151" s="17" t="inlineStr">
+        <is>
+          <t>維持104(主品牌98+RIM6)；官網news最新仍8/17(第2支75折),自8/17起無新開店/RIM拓點,8月促銷四檔+NEW LIFE提案續行(安靜週)</t>
+        </is>
+      </c>
+      <c r="G151" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B152" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C152" s="17" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D152" s="17" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E152" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F152" s="17" t="inlineStr">
+        <is>
+          <t>維持38(北12/桃4/竹3/中8/彰1/嘉1/南3/高5/屏1);官網news新增【改裝通知】統一時代百貨台北店8/24~9/10內部改裝(暫時性,門市數不變);大巨蛋8/22已生效</t>
+        </is>
+      </c>
+      <c r="G152" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="B153" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C153" s="17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D153" s="17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E153" s="17" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="F153" s="17" t="inlineStr">
+        <is>
+          <t>🟣新增KlassiC. SOGO大巨蛋店(台北信義區光復南路105號B1,暫無驗光,主品牌零售櫃)→21→22(北11→12);與眼鏡市場大巨蛋同商圈,大巨蛋成雙競品戰場。new-arrival無新產品線(Tokyo Vitamin/aeae/house款續在)</t>
+        </is>
+      </c>
+      <c r="G153" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B154" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C154" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D154" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="E154" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F154" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（新北18、屏東2）；基準未變</t>
+        </is>
+      </c>
+      <c r="G154" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B155" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C155" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D155" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E155" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F155" s="17" t="inlineStr">
+        <is>
+          <t>維持104(主品牌98+RIM6)；官網news最新仍8/17,無新開店/RIM拓點;本期焦點=8月促銷四檔今日8/31集體到期(promo cliff),9月換季檔前瞻</t>
+        </is>
+      </c>
+      <c r="G155" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B156" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C156" s="17" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D156" s="17" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E156" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F156" s="17" t="inlineStr">
+        <is>
+          <t>維持38(北12/桃4/竹3/中8/彰1/嘉1/南3/高5/屏1);news新增桃園雙店一週年祭(大江/台茂 9/1);統一時代台北店改裝8/24~9/10續行(暫時性,數不變)</t>
+        </is>
+      </c>
+      <c r="G156" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/location</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="B157" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C157" s="17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D157" s="17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E157" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F157" s="17" t="inlineStr">
+        <is>
+          <t>維持22(逐店清點含SON&amp;SUN×2/Klassroom/SOGO大巨蛋等無驗光零售櫃);優惠專區新見膽大黨DAN DA DAN全系列買一送一+輕行者摺疊墨鏡兩件85折;new-arrival無新產品線</t>
+        </is>
+      </c>
+      <c r="G157" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="B158" s="17" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C158" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D158" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="E158" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F158" s="17" t="inlineStr">
+        <is>
+          <t>全台80間（新北18、屏東2）；基準未變</t>
+        </is>
+      </c>
+      <c r="G158" s="17" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="B159" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C159" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D159" s="17" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E159" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F159" s="17" t="inlineStr">
+        <is>
+          <t>維持104(主品牌98+RIM6)。🔴promo cliff已回補:8月四檔8/31到期後,9月新檔即上—週年暖身慶9/3-9/16+舒壓鏡片85折/RIM紅圓標85折/日本製濾藍光9折(皆9/1-9/30);週年慶正檔一波/二波9/4起滾動至Q4。⏳兩店開幕倒數:蘆洲佳瑪店9/4(五)+秀泰台東店9/10(四)→104→106 pending(台東為東部拓點,僅次花蓮)。#36修補:改抓news文章頁底部「其他消息」清單繞過/news JS動態,一手直讀鏈修復</t>
+        </is>
+      </c>
+      <c r="G159" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-68b6bf112b8c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="B160" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C160" s="17" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D160" s="17" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E160" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F160" s="17" t="inlineStr">
+        <is>
+          <t>維持38(北12/桃4/竹3/中8/彰1/嘉1/南3/高5/屏1)。news新增【同遊享樂節】限定優惠(9/1起,207)+【改裝通知】SOGO百貨台北忠孝店9/1~9/20內部改裝(208,新增,與統一時代改裝8/24~9/10並行=台北雙館同時改裝);桃園雙店週年祭(大江/台茂9/1)續行</t>
+        </is>
+      </c>
+      <c r="G160" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="B161" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C161" s="17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D161" s="17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E161" s="17" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F161" s="17" t="inlineStr">
+        <is>
+          <t>🔻競品門市首次淨減:官方門市頁逐店清點21(北11/中5/南5),vs 8/27-8/31的22少1。台北storefront由10減為9—SOGO大巨蛋店仍在,另一台北櫃點自官方門市頁移除(待確認為撤櫃或頁面調整)。促銷:膽大黨DAN DA DAN全系列BOGO+輕行者摺疊墨鏡兩件85折續行;new-arrival無新產品線(Tokyo Vitamin/aeae/house款續在)</t>
+        </is>
+      </c>
+      <c r="G161" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>80</v>
+      </c>
+      <c r="D162" t="n">
+        <v>80</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>全台80間（新北18、屏東2）；基準未變</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.owndays.com/tw/zh_tw</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>🔴蘆洲佳瑪店9/4(五)開幕已生效(日期已過)→104→105(主品牌98→99+RIM6),新北jins 19→20。秀泰台東店9/10(四)仍倒數→106 pending(東部拓點)。新增9/4極薄鏡片(1.76)恢復販售與保固更換;週年慶全台逐店開檔時程完整公布(9/4三創起滾動至12月)+暖身慶9/3-9/16/舒壓·RIM紅圓標85折·濾藍光9折(9/1-9/30)續行</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-68b6bf112b8c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>維持38(北12/桃4/竹3/中8/彰1/嘉1/南3/高5/屏1)。統一時代百貨台北店9/11(五)REOPEN確認(改裝8/24~9/10完工);SOGO忠孝店改裝中(~9/20)續行;同遊享樂節/桃園雙店週年祭續行</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>維持21(北11/中5/南5)。台北storefront覆核穩定於9(上期-1=撤櫃屬性穩定,非頁面暫時調整;兌現顧問#37台北逐店快照存檔,未再變動);新促銷膽大黨DAN DA DAN限量福袋(4件組$2,800/5件組$1,500)上架;house新款ALEX/AURA/BAILEY $3,580</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
         <is>
           <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
@@ -14309,7 +19226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="17" min="1" max="1"/>
@@ -15710,6 +20627,697 @@
       <c r="I29" s="17" t="inlineStr">
         <is>
           <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>W31-週一</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/20（週一 run now 即時更新）</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>1. 🆕 JINS×攻殻機動隊《THE GHOST IN THE SHELL》聯名系列7/16開賣：JINS首款電子調光太陽眼鏡全球限量1,000副（日本建議售價¥29,900）＋光學款（¥19,900）。 2. 【最急・倒數2天】多副夾擊最後窗口：眼鏡市場第二副折300（7/22收檔）×JINS第2支75折×狂夏出清7折三方夾擊。 3. 眼鏡市場宜蘭店撤店倒數6天（7/26）→屆時37→36。三家門市數全持平（JINS104含RIM6/眼鏡市場37/Klassic20）。</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中（門市數全±0；JINS以大型IP聯名（攻殻機動隊）搶科技/潮流聲量；多副折扣戰進入最後2天收檔窗口）</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>(a)【最急・倒數2天】本期交付「多副夾擊三方對照」，OD於7/22前以「一價全包、雙副總價透明、家庭配鏡」對打JINS第2支75折×眼鏡市場第二副折300。 (b) 對JINS攻殻機動隊聯名：OD以驗光專業＋一價全包差異化，聯名屬話題型限量、非價格戰。 (c) 宜蘭7/26撤店，OD宜蘭門市把握在地客源承接窗口，7/27後啟動回看填數。</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>W32-週一</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/27（週一 run now 即時更新）</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>1. 🏳️ 眼鏡市場宜蘭店7/26已閉店(37→36)：閉店日已過，官網門市頁尚未移除(今日仍列36含宜蘭)，實際營運降至35待複查；OD宜蘭承接窗口正式開啟
+2. 🆕 眼鏡市場【父親節】配鏡第二副88折(7/23-8/10)接棒已於7/22收檔的「第二副折300」——多副折法由「定額-300」升級為「比例88折」，高價第二副折扣更深、壓力延燒至8/10
+3. 🟢 JINS 104(含RIM6)/Klassic 20門市±0；JINS狂夏出清7折(7/1-8/31)續行、攻殻機動隊聯名無新事件；Klassic輕行者摺疊墨鏡兩件85折上架</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中（門市數眼鏡市場-1宜蘭閉店；多副折扣戰由7/22短窗延長為8/10父親節長檔，多副壓力升級加碼高價客單）</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>(a) 多副對打續打至8/10：OD以「一價全包、每副總價透明、鏡片升級不加價、不需湊件」對打眼鏡市場父親節第二副88折×JINS第2支75折，綁定父親節/開學換季 (b) 宜蘭承接啟動：眼鏡市場宜蘭7/26撤出後OD宜蘭店承接在地客源，進入閉環回看填數(第5窗口) (c) 本期交付深挖：眼鏡市場「第二副」折法演進(折300→88折)＋OD對打(週報第5張)</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H31" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>W32-週四</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/30（週四 run now 即時更新）</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>1. 🆕 JINS淡水英專店8月開幕確認：重返北海岸淡水（淡江大學商圈），新北市淡水區英專路33號1樓，開幕日起至8/31淡水居民配鏡現折300；開店後JINS新北+1（104→105）
+2. ✅ 兌現顧問#25：眼鏡市場門市數一次逐店定錨——官網掛牌37間(含已閉店宜蘭/25未移除)、實際營運中36間，永久消除35/36/37三值並存的計數模糊
+3. 🟢 眼鏡市場36(營運)/JINS104(含RIM6)/Klassic20門市±0；眼鏡市場news最新仍父親節88折(7/20貼)無新事件；Klassic new-arrival前排新增ALEX/AURA/BAILEY/JAN</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中（JINS淡水拓點鎖定大學/北海岸客源，直面OD淡水；門市數本期營運±0；深挖交付眼鏡市場展店→收縮淨門市數趨勢線）</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>(a) 淡水防禦：JINS淡水英專店8月開幕鎖定淡江大學生+在地客，OD淡水店備妥開學季對打（學生免費升級、一價全包），對標JINS淡水居民折300
+(b) 多副對打續打至8/10：OD以「一價全包、每副總價透明、鏡片升級不加價、不需湊件」對打眼鏡市場父親節第二副88折×JINS第2支75折
+(c) 本期交付深挖：眼鏡市場「展店→收縮」淨門市數趨勢線（兌現顧問#17/#1）——密集展店(嘉義5/29、屏東6/18)後宜蘭7/26首個收縮事件，供OD評估收縮商圈承接</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>W33-週一</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/03（週一 run now 即時更新）</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>1. 🆕 JINS淡水英專店開幕生效：JINS全台104→105（新北19→20，99+RIM6），開幕慶淡水居民配鏡現折300至8/31，直面OD淡水店
+2. 🆕 眼鏡市場Mini G Mall豐原店(台中)8/7(五)開幕確認：7/26宜蘭閉店後隨即以豐原補回，展店動能未熄，開店後營運36→37
+3. 🆕 JINS台北/新北限定8/1-8/31配鏡升級最高75折新檔上線；三家「當前」營運門市：JINS105/眼鏡市場36/Klassic20</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中（JINS淡水拓點生效+雙北暑期折扣加碼；眼鏡市場豐原8/7再展店；門市競爭雙北與大台中同時升溫）</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>(a) 淡水防禦：OD淡水店以開學季學生方案（免費升級、一價全包）對標JINS淡水居民折300，守淡江大學/北海岸換季客源
+(b) 多副對打續至8/10：OD以「一價全包、每副總價透明、升級不加價、不需湊件」對打眼鏡市場父親節第二副88折×JINS天天第2支75折
+(c) 本期交付深挖：JINS新品/聯名/代言節奏時間軸（兌現顧問#8）——攻殻機動隊(7/16)/李珠珢公益(7/9)/主播KOL(7/30)/立夏芒種產品線，OD聚焦驗光專業+一價全包結構性差異，避開高熱IP撞期</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H33" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I33" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>W33-週四</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/06（週四 run now 即時更新）</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>1. ⚠️【資料校正】JINS淡水英專店經一手複查為2024.08.05開幕之既有門市（官方原文日期2024.08.05；2026 news feed無淡水新開店公告）——8/3認列之「新開店+1」係舊聞誤帶，本期回正 JINS 105→104（新北20→19，98+RIM6）
+2. 🆕 眼鏡市場Mini G Mall豐原店(台中)明日8/7(五)開幕在即：今日仍營運36/掛牌37，明日8/7生效營運36→37；父親節第二副88折(7/23-8/10)續行
+3. 🆕 Klassic new-arrival前排換回 KlassiC.×aeae 聯名系列（摺疊墨鏡$2,480／扁方圓框·橢圓框$3,980／周邊$1,580），取代上期AKILA/CHIMI進口款；三家當前營運門市 JINS104(校正)/眼鏡市場36/Klassic20</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低偏中（門市數校正回正、無實質新開店；豐原8/7明日才生效；本期為情報校正＋展店在即的過渡週）</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>(a) 校正透明化：本報告最重要價值＝抓出並回正8/3的淡水誤認列，維持計數紀律；提醒Howard以官方門市頁做最終數字核對（淡水英專店應早已在roster內）
+(b) 大台中備戰豐原8/7：OD大台中門市留意豐原Mini G Mall開幕期(8/7-9/7滿額折)客流競爭，明日生效後回填眼鏡市場營運37
+(c) 本期交付深挖：淡水 OD vs JINS英專店 迷你battlecard（兌現顧問#26）——兩店距離/客群/優惠對照，把「淡水對打」由口號變可執行對照
+(d) 多副對打續至8/10：OD以一價全包對打眼鏡市場父親節88折×JINS天天第2支75折</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I34" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>W34-週一</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/10（週一 run now 即時更新）</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>1. 🆕【展店】JINS誠品生活480店(台中西屯)8/15(五)新開幕＝主品牌真新店(98→99 pending)＋RIM京站8/1已開 2. 🆕 眼鏡市場豐原8/7已生效上架、宜蘭下架→門市數乾淨定錨37(35/36/37三值消除,兌現#25) 3. 🆕 Klassic new-arrival新增自有款ALEX/AURA/BAILEY＋Solo Leveling IP</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中（雙品牌展店活絡：JINS大台中主品牌新店+眼鏡市場豐原生效，大台中成三家交火熱區；三家同期押注動漫IP拉年輕客）</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>(a)大台中防禦：OD七期/西屯門市(新光三越中港/大遠百)強化一價全包+當日取件,迎8/15 JINS誠品480開幕 (b)豐原衛星商圈OD無店,評估線上導流/選址訊號 (c)父親節第二副88折今日(8/10)收檔,OD把握換季開學雙副需求 (d)本期深挖大台中battlecard兌現#2/#17</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H35" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>W34-週四</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/14（週四排程順延 run now 即時更新）</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>1. ⏳ JINS誠品生活480店(台中西屯)明日8/15(五)開幕倒數1日＝主品牌真新店(104→105 pending) 2. 🆕 眼鏡市場促銷三連發：中元量販8/11+改裝SALE統一時代台北/SOGO忠孝8/7+SUMMER第二副折$300(接棒父親節88折) 3. 🆕 Klassic AXIS鈦金屬方框新旗艦上市＋IP版圖再擴</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中（門市數±0；促銷/新品活絡：眼鏡市場台北雙館改裝SALE+多副折、Klassic鈦金屬機能款+密集IP、JINS誠品480明日開幕；三家同期押注IP拉年輕客）</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>(a)8/15誠品480開幕後首跑一手回填(98→99/104→105/台中jins14→15)並繪點 (b)台北信義/東區門市留意眼鏡市場改裝SALE(統一時代台北/SOGO忠孝)同商圈分流 (c)雙副戰場：以「每副同價/不需湊件/升級不加價」對打眼鏡市場第二副折$300+JINS第2支75折 (d)本期深挖三家IP聯名橫向對照,兌現#30/#3</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I36" s="17" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>W35-週一</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/17（週一 run now 即時更新）</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>1. ✅JINS官方逐區roster權威閉合(#28)：北62+中17+南23+東2=104(主品牌98+RIM6)，誠品480(8/15)+水湳愛買已上架台中，先前104→105推估回正 2. 🟠眼鏡市場37±0本週無新促銷 3. 🟣Klassic新增SILENCE IS THE NEW SHAPE+FUTURE FLEX機能系列；官方門市頁現列21(vs20)待釐清</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低偏中（門市數淨±0、以官方口徑閉合計數不確定；競品促銷平台期無新火力；Klassic產品線持續擴張）</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>(a)以官方逐區表定錨JINS=104(98+6)，未來新開以此+1不帶歷史誤差 (b)同法建立Klassic逐店名冊釐清21vs20 (c)台中七期/西屯門市對打誠品480+水湳愛買開幕攻勢(一價全包+當日取件) (d)開學換season雙副主戰場續打透明總價</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>JINS 門市搜尋</t>
+        </is>
+      </c>
+      <c r="H37" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>W35-週四</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/20（週四排程 run now 即時更新）</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>1. ⏳眼鏡市場台北大巨蛋店8/22(六)OPEN開幕倒數(官網news 8/17公告)＝繼豐原(8/7)後再落雙北旗艦娛樂型商圈,今日營運37,週六生效37→38 pending(台北市megane 6→7)
+2. 🔎深挖:Klassic逐店roster權威閉合(兌現#32)—官方門市頁21 storefront=18主品牌驗光+3副品牌暫無驗光,追蹤20→21定錨(台北8→9),三家新銳計數口徑統一
+3. 🔴JINS 104(98+RIM6)±0無新開店,8月促銷四檔續行;🟣Klassic new-arrival前排維持aeae聯名+house款,無新產品線(誠實標示)</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中偏低（門市數本週淨±0但眼鏡市場8/22大巨蛋展店在即＝雙北實體布局升溫；Klassic roster閉合為基準建設；競品促銷平台期無新火力）</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>(a)大巨蛋開幕攔截:OD松山/信義門市於8/22開幕檔以當日取件+升級不加價攔截嚐鮮客流,開店後首跑回補眼鏡市場37→38繪點 (b)三家計數口徑統一後,未來以官方頁+1乾淨增補 (c)雙副戰場續打:每副同價/不需湊件對打眼鏡第二副折$300×JINS第2支75折 (d)Klassic副品牌軸(SON&amp;SUN/Klassroom無驗光零售櫃)可比照RIM#21建獨立追蹤</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H38" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>W36-週一</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/24（週一 run now 即時更新）</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>1. ✅眼鏡市場台北大巨蛋店8/22(六)已開幕生效：官網門市頁上架【8/22 NEW OPEN】,兌現上期pending 37→38(台北市megane 6→7),2026展店節奏再落一站,首入雙北旗艦娛樂型商圈
+2. 🟣Klassic新聯名產品線KlassiC.×Tokyo Vitamin(墨鏡$3,980/棒球帽$1,380)本週首見,補回上期「產品端平台期」判讀
+3. 🔎深挖:RIM+Klassic副品牌獨立追蹤軸(兌現#21)—JINS RIM 6(驗光型,含於104)+Klassic副品牌3(SON&amp;SUN×2/Klassroom,零售型無驗光)=副品牌線9個櫃/店;🔴JINS 104±0無新開店,Klassic門市21±0</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中偏低（門市數淨+1(大巨蛋生效)＝眼鏡市場雙北旗艦布局落地；Klassic以Tokyo Vitamin新聯名維持話題;JINS促銷平台期無新火力）</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>(a)大巨蛋開幕攔截:OD松山/信義門市於開幕檔以當日取件+升級不加價攔截周邊嚐鮮客流,並列為第5個閉環回看窗口 (b)副品牌軸建立:xlsx新增分頁獨立列RIM6+Klassic副品牌3,主品牌門市數不再混入 (c)雙副戰場續打:每副同價對打眼鏡第二副折$300×JINS第2支75折 (d)潮流聯名非OD正面對打面,續以中高階機能/鈦框(AXIS+FUTURE FLEX)對照Klassic鏡框主力</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H39" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 location</t>
+        </is>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC new-arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>W36-週四</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/27（週四排程 run now 即時更新）</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>1. 🟣【展店/新發現】Klassic新增KlassiC. SOGO大巨蛋店(台北信義,暫無驗光,主品牌零售櫃)→21→22(北11→12);與眼鏡市場台北大巨蛋店(8/22)同一娛樂型商圈,大巨蛋自本期起成「眼鏡市場+Klassic」雙競品戰場
+2. 🟠【動態】眼鏡市場統一時代百貨台北店8/24~9/10內部改裝(官網news 8/24公告),暫時性,門市數維持38
+3. 🔴JINS 104(98+RIM6)±0,官網news最新仍8/17(安靜週),8月促銷四檔+NEW LIFE提案續行;🟣Klassic new-arrival無新產品線(Tokyo Vitamin/aeae/house款續在,誠實標示)</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中偏低（門市數淨+1(Klassic大巨蛋)＝競品雙北旗艦娛樂商圈布局再加碼,大巨蛋同址雙競品交火;眼鏡市場台北雙館改裝檔;JINS促銷平台期無新火力）</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>(a)大巨蛋雙競品攔截升級:OD松山/信義門市於大巨蛋商圈同時面對眼鏡市場+Klassic兩競品,以「當日取件+升級不加價+驗光專業」攔截娛樂型商圈嚐鮮客流,列為第5個閉環回看窗口 (b)本期深挖:大巨蛋商圈雙競品同址對打分析(眼鏡市場大巨蛋vs Klassic SOGO大巨蛋,同娛樂商圈型態) (c)雙副戰場續打:每副同價/不需湊件/升級不加價對打眼鏡市場第二副折$300×JINS第2支75折 (d)前瞻鉤子(兌現#34):各家下一倒數事件掃描—本期無明確下一展店/聯名倒數,眼鏡市場統一時代改裝9/10完工可留意</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H40" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>W37-週一</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31（週一排程 run now 即時更新）</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>1. 🟢三家門市數全持平:JINS 104(98+RIM6)/眼鏡市場38/Klassic22,競品164±0/全台244±0;本期無門市異動,焦點轉促銷檔期
+2. 🔴JINS 8月促銷四檔今日8/31集體到期(第2支75折8/17-8/31/雙北最高75折8/1-8/31/夏日三好康至8/31)=promo cliff,9月換季檔為下一倒數事件(前瞻鉤子#34)
+3. 🟠眼鏡市場桃園雙店一週年祭(大江購物中心店+台茂購物中心店,9/1):桃園4店叢集2025秋批量進場後首屆週年,轉留客期;統一時代台北店改裝8/24~9/10續行(9/10完工)
+4. 🟣Klassic優惠專區新見膽大黨DAN DA DAN全系列買一送一(BOGO)+輕行者摺疊墨鏡兩件85折
+5. 🔎深挖:眼鏡市場2026展店節奏線(南紡3/25→嘉義5/29→屏東6/18→豐原8/7=社區量販衛星型4波,8/22大巨蛋=都會旗艦娛樂型),由衛星鋪點升級為都會地標插旗</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>🟢 低偏中（三家門市數全持平、無展店異動；競品火力集中促銷檔期:JINS換檔空窗+眼鏡市場桃園週年+Klassic IP BOGO；無新實體布局）</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>(a)搶JINS換檔空窗:8月四檔今日到期、9月新檔未上,OD以「每副同價/不需湊件」承接開學配鏡,不必等對手新檔 (b)桃園留客對打:OD桃園門市(統領/藝文特區)留意眼鏡市場桃園4店週年檔加溫,以驗光專業+當日取件承接外溢 (c)大巨蛋雙競品續守:延續上期,OD松山/信義於大巨蛋商圈同時面對眼鏡市場+Klassic,列第5個閉環回看窗口 (d)IP BOGO非OD正面對打面:Klassic膽大黨買一送一鎖動漫粉,OD守中高階機能/鈦框+驗光專業</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H41" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I41" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC 優惠專區</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>W37-週四</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/03（週四排程 run now 即時更新）</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>1. 🔴JINS促銷cliff回補+雙店開幕倒數:8月四檔8/31到期後9月新檔即上—週年暖身慶9/3(四)-9/16+舒壓鏡片85折/RIM紅圓標85折/日本製濾藍光9折(皆9/1-9/30台北市/指定),週年慶正檔一波/二波9/4起滾動至Q4;蘆洲佳瑪店9/4+秀泰台東店9/10開幕→104→106 pending(台東東部拓點)。兌現前瞻鉤子#34(換季檔如期到來)+#36(news JS繞道成功)
+2. 🔻Klassic門市首次淨減22→21:官方門市頁台北storefront 10→9(SOGO大巨蛋仍在,另一台北櫃點下架),競品合計164→163、全台244→243、八品牌1,017→1,016
+3. 🟠眼鏡市場38±0:同遊享樂節9/1+SOGO台北忠孝店改裝9/1~9/20(新增,與統一時代改裝8/24~9/10並行=台北雙館同時改裝);桃園雙店週年祭續行
+4. 🔎深挖:同商圈競品密度清單(兌現顧問#35)—建OD門市周邊競品數排序表,標高密度攔截優先點</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>🟡 中（JINS促銷cliff快速回補+週年慶啟動+雙店開幕倒數=火力重返;Klassic門市首次淨減-1;眼鏡市場台北雙館同時改裝;競品實體端一減一增待觀察）</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>(a)搶JINS換檔仍以透明總價:JINS週年慶暖身+舒壓鏡片85折上架,OD以「每副同價/不需湊件/升級不加價」對打湊件/指定款折扣,續承接開學配鏡
+(b)東部拓點留意:JINS秀泰台東店9/10開幕=繼花蓮後東部再插旗,OD東部布局(宜蘭/花蓮/台東各1)可評估承接;蘆洲佳瑪9/4=新北量販型
+(c)台北雙館改裝期承接:眼鏡市場統一時代(~9/10)+SOGO忠孝(~9/20)同時改裝,OD台北信義/東區門市以當日取件承接改裝期外溢
+(d)Klassic門市-1追蹤:確認台北櫃點下架屬撤櫃或頁面調整,下期覆核;OD守中高階機能/鈦框+驗光專業</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H42" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>W38-週一</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026/09/07（週一排程 run now 即時更新）</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1. 🔴JINS 104→105:蘆洲佳瑪店9/4(五)開幕已生效(新北jins 19→20,主品牌98→99+RIM6);秀泰台東店9/10(四)仍倒數→106 pending(東部拓點,繼花蓮後再插旗)。新增9/4極薄鏡片(1.76)恢復販售與保固更換;週年慶全台逐店開檔時程完整公布(9/4三創起滾動至12月)
+2. 🟠眼鏡市場38±0:統一時代百貨台北店9/11(五)REOPEN確認(改裝8/24~9/10完工),台北改裝承接窗口收斂剩SOGO忠孝(~9/20)一館
+3. 🟣Klassic 21±0:台北storefront覆核穩定於9(上期-1=撤櫃屬性穩定,非頁面暫時;兌現#37台北逐店快照);新促銷膽大黨DAN DA DAN限量福袋(4件組$2,800/5件組$1,500)
+4. 🔎深挖:JINS週年慶全台逐店開檔時間軸—折扣峰值9/25-10/22,台北信義/東區(密度Top1)10/2-10/22面對JINS最強折扣密集期</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>🟡 中（JINS實體+火力雙升:蘆洲生效104→105、台東9/10倒數、1.76高階鏡片恢復、週年慶全台鋪檔;眼鏡市場統一時代9/11重開;Klassic門市穩定-1後未再減,促銷福袋化）</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>(a)對打JINS週年慶檔期節奏:折扣峰值9/25-10/22,OD對打人力/優惠集中9月下旬-10月中,台北信義/東區10/2-10/22最需以「每副同價/升級不加價/當日取件」正面攔截
+(b)守高度數薄鏡片:JINS 1.76恢復販售,OD以全度數同價/1.74標配/免費升級對打其高折射率加價
+(c)東部拓點續追:JINS台東9/10開幕→106 pending,OD東部(宜蘭/花蓮/台東各1)評估承接;新北蘆洲量販型開幕檔留意
+(d)台北改裝收斂:統一時代9/11重開,OD承接窗口剩SOGO忠孝(~9/20);Klassic膽大黨福袋鎖動漫粉,OD守中高階機能/鈦框+驗光專業</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>JINS news</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>眼鏡市場 news</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>KlassiC stores</t>
         </is>
       </c>
     </row>
@@ -16361,7 +21969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="18" min="1" max="1"/>
@@ -16396,7 +22004,7 @@
       </c>
       <c r="E1" s="17" t="inlineStr">
         <is>
-          <t>狀態(自動續算@2026/07/16)</t>
+          <t>狀態(自動續算@2026/09/07)</t>
         </is>
       </c>
       <c r="F1" s="17" t="inlineStr">
@@ -16433,12 +22041,12 @@
       </c>
       <c r="E2" s="17" t="inlineStr">
         <is>
-          <t>🟡 進行中</t>
+          <t>⬛ 已到期(8/31收檔,promo cliff)</t>
         </is>
       </c>
       <c r="F2" s="17" t="inlineStr">
         <is>
-          <t>OD開學季對標，主打免費升級+服務</t>
+          <t>已收檔(promo cliff);9月週年慶新檔接棒</t>
         </is>
       </c>
       <c r="G2" s="17" t="inlineStr">
@@ -16470,12 +22078,12 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>🟡 進行中</t>
+          <t>⬛ 已到期(8/31收檔,promo cliff)</t>
         </is>
       </c>
       <c r="F3" s="17" t="inlineStr">
         <is>
-          <t>OD調光/感光升級方案對標，凸顯總價</t>
+          <t>已收檔(promo cliff);9月週年慶新檔接棒</t>
         </is>
       </c>
       <c r="G3" s="17" t="inlineStr">
@@ -16544,12 +22152,12 @@
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>🟡 進行中</t>
+          <t>⬛ 已結束（7/19收檔）</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>OD台中/桃園/新竹大遠百商圈留意分食</t>
+          <t>已收檔</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
@@ -16655,12 +22263,12 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>🟡 進行中（撤店倒數10天，7/26）</t>
+          <t>⬛ 已結束（7/26閉店收檔）</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>OD宜蘭店承接撤出後在地客源</t>
+          <t>OD宜蘭店承接撤出後在地客源，已進入閉環回看填數(第5窗口)</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
@@ -16692,12 +22300,12 @@
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>🟡 進行中（收檔倒數6天，7/22）</t>
+          <t>⚪ 已收檔（7/22）｜由父親節第二副88折(7/23-8/10)接棒</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>OD多副/家庭配鏡對標；7/22收檔</t>
+          <t>已收檔；多副對打轉父親節88折檔</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
@@ -16729,12 +22337,12 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>🟡 進行中</t>
+          <t>⬛ 已到期(8/31收檔,promo cliff)</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>OD以調光/感光升級對標，凸顯一價全包</t>
+          <t>已收檔(promo cliff);9月週年慶新檔接棒</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
@@ -16766,12 +22374,12 @@
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>🟡 進行中</t>
+          <t>⬛ 已到期(8/31收檔,promo cliff)</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>OD台北門市對標，強調免費升級/總價</t>
+          <t>已收檔(promo cliff);9月週年慶新檔接棒</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
@@ -16877,17 +22485,794 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>🟡 進行中</t>
+          <t>⬛ 已到期(8/31收檔,promo cliff)</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>OD以全品項一價全包對打「指定款才7折」條件式折扣</t>
+          <t>已收檔(promo cliff);9月週年慶新檔接棒</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
           <t>https://www.jins.com/tw/news/news-6a56ef730c7b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>父親節SALE 配鏡第二副88折</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>2026/07/23</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>⚫ 已收檔（8/10結束,由SUMMER第二副折$300接棒）</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>已收檔；多副對打轉SUMMER第二副折$300</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/195</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>輕行者摺疊墨鏡系列 兩件85折</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>進行中(限時)</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>🟣 進行中</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>OD夏季墨鏡/多副墨鏡需求留意；Klassic以多件折攻太陽眼鏡多副</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/categories/sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>淡水英專店 開幕慶（淡水居民配鏡現折300＋滿額贈＋IG見面禮）</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>2026/08</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>⬛ 已到期(8/31收檔,promo cliff)</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>已收檔(promo cliff);9月週年慶新檔接棒</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>台北/新北市限定 配鏡升級最高75折</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/01</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>⬛ 已到期(8/31收檔,promo cliff)</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>已收檔(promo cliff);9月週年慶新檔接棒</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a6c1c97ac146</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Mini G Mall豐原店 開幕慶（滿3000折300/滿5000折500+來店贈品）</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>🟢 開幕檔（8/7開幕至9/7）</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>OD大台中留意豐原開幕聲量，以驗光專業/一價全包差異對打</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/197</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>誠品生活480店(台中西屯) 開幕見面禮（滿$3000贈皮革收納盒＋IG贈提袋）</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/15</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>贈完為止</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>🟢 已開幕(8/15生效,見面禮贈完為止)</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>OD台中七期/西屯門市對標開幕攻勢,強調一價全包+當日取件+升級不加價</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-689ac3cfad673</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>SUMMER SALE 夏日大作戰 眼鏡第二副折300元</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>進行中(限時)</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>🟠 進行中（8/7接棒父親節88折）</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>OD以每副同價/不需湊件/升級不加價對打定額第二副折</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/202</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>改裝SALE 統一時代台北/SOGO忠孝(滿額折+指定5折起)</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>🟠 進行中（台北雙館改裝檔）</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>OD台北信義/東區門市留意同商圈分流,守服務差異</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/203</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>中元吉祥 量販店專屬優惠</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>🟠 進行中（中元檔,量販店型）</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>量販客流非OD主戰場,觀察即可</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/199</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>【改裝通知】統一時代百貨台北店 內部改裝修整</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/10</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>🔧 改裝中(8/24~9/10暫停營業)</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>OD台北信義/東區門市留意統一時代改裝期客流外溢,守服務差異;9/10完工留意重開檔</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>大江購物中心店 一週年祭 限定優惠</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>🟠 進行中（桃園週年檔,9/1起）</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>OD桃園門市留意眼鏡市場桃園4店叢集週年檔加溫,以驗光專業+當日取件承接外溢客流</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/209</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>台茂購物中心店 一週年祭 限定優惠</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>🟠 進行中（桃園週年檔,9/1起）</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>同上;桃園南崁/蘆竹商圈,OD桃園門市對標</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/210</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>KlassiC.×DAN DA DAN 膽大黨 全系列買一送一(BOGO)</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>進行中(限時)</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>🟣 進行中（動漫IP全系列BOGO）</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>動漫IP粉絲客群清庫轉化,非OD正面對打面;OD守中高階機能/鈦框+驗光專業</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/promotions/dan-da-dan-bogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>🎉 JINS 週年暖身慶（台北市限定）</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>🎉 進行中（9/3-9/16暖身,週年慶正檔一波/二波9/4起滾動至Q4）</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>OD以「每副同價/不需湊件/升級不加價」對打湊件/指定折;承接開學配鏡</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a97c8c8d7a2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>台北市限定 配鏡升級舒壓鏡片85折</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/30</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>🟡 進行中（9/1-9/30台北市）</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>OD台北門市對標,凸顯免費升級/一價全包</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a968fb48d551</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>RIM BY JINS 指定光學眼鏡 紅圓標85折</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/30</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>🟡 進行中（9/1-9/30 RIM）</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>RIM副品牌促銷,OD守驗光專業/透明總價</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a968effbc59b</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>配鏡升級 日本製濾藍光鏡片9折</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/30</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>🟡 進行中（9/1-9/30）</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>OD以濾藍光/一價全包對標,凸顯升級不加價</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a94dcc3e6799</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>【同遊享樂節】限定優惠活動</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>🟠 進行中（9/1起,同遊主題檔）</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>OD觀察眼鏡市場9月檔期節奏,守服務差異</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/207</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>【改裝通知】SOGO百貨台北忠孝店 內部改裝</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>2026/09/20</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>🔧 改裝中(9/1~9/20,與統一時代改裝並行)</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>OD台北信義/東區門市承接台北雙館(統一時代~9/10+SOGO忠孝~9/20)改裝期外溢</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news/208</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>JINS週年暖身慶（台北市限定）</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>🟡 進行中（9/3-9/16台北市）</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>OD以每副同價/升級不加價對打週年慶湊件邏輯,承接開學配鏡</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-6a97c8c8d7a2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>統一時代百貨台北店改裝→9/11 REOPEN</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026/09/11</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>✅ 9/11完工重開(改裝結束)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>改裝完工=競品火力回補時效點;OD台北承接窗口收斂</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.meganeichiba.com.tw/news</t>
         </is>
       </c>
     </row>
